--- a/risk/Risk_Analysis_T3_100yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_Breaches.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>1961.91</v>
+        <v>28278.63</v>
       </c>
       <c r="C4" t="n">
-        <v>585648</v>
+        <v>5172552</v>
       </c>
       <c r="D4" t="n">
-        <v>460152</v>
+        <v>4064148</v>
       </c>
       <c r="E4" t="n">
-        <v>145800</v>
+        <v>1602900</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>6900</v>
+        <v>84150</v>
       </c>
       <c r="H4" t="n">
-        <v>240</v>
+        <v>7560</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>21150</v>
+        <v>176850</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3615.93</v>
+        <v>24330.6</v>
       </c>
       <c r="C5" t="n">
-        <v>673344</v>
+        <v>4136328</v>
       </c>
       <c r="D5" t="n">
-        <v>529056</v>
+        <v>3249972</v>
       </c>
       <c r="E5" t="n">
-        <v>142200</v>
+        <v>1090800</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>8970</v>
+        <v>68460</v>
       </c>
       <c r="H5" t="n">
-        <v>90</v>
+        <v>5100</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20580</v>
+        <v>151200</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>4064.04</v>
+        <v>21914.19</v>
       </c>
       <c r="C6" t="n">
-        <v>518112</v>
+        <v>3563784</v>
       </c>
       <c r="D6" t="n">
-        <v>407088</v>
+        <v>2800116</v>
       </c>
       <c r="E6" t="n">
-        <v>79200</v>
+        <v>762300</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>8040</v>
+        <v>62040</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>7530</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>22110</v>
+        <v>146520</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>3215.52</v>
+        <v>31061.7</v>
       </c>
       <c r="C7" t="n">
-        <v>291312</v>
+        <v>4585392</v>
       </c>
       <c r="D7" t="n">
-        <v>228888</v>
+        <v>3602808</v>
       </c>
       <c r="E7" t="n">
-        <v>46800</v>
+        <v>939600</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>5730</v>
+        <v>81090</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>12360</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>15450</v>
+        <v>188490</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1686.51</v>
+        <v>30611.52</v>
       </c>
       <c r="C8" t="n">
-        <v>99288</v>
+        <v>2971080</v>
       </c>
       <c r="D8" t="n">
-        <v>78012</v>
+        <v>2334420</v>
       </c>
       <c r="E8" t="n">
-        <v>20700</v>
+        <v>384300</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2340</v>
+        <v>72840</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>4260</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>5610</v>
+        <v>160410</v>
       </c>
     </row>
     <row r="9">
@@ -10033,37 +10027,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>792.45</v>
+        <v>24835.41</v>
       </c>
       <c r="C9" t="n">
-        <v>38808</v>
+        <v>1934856</v>
       </c>
       <c r="D9" t="n">
-        <v>30492</v>
+        <v>1520244</v>
       </c>
       <c r="E9" t="n">
-        <v>11700</v>
+        <v>155700</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1170</v>
+        <v>35760</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1080</v>
+        <v>90780</v>
       </c>
     </row>
     <row r="10">
@@ -10071,22 +10065,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>451.62</v>
+        <v>17857.44</v>
       </c>
       <c r="C10" t="n">
-        <v>12096</v>
+        <v>1140048</v>
       </c>
       <c r="D10" t="n">
-        <v>9504</v>
+        <v>895752</v>
       </c>
       <c r="E10" t="n">
-        <v>1800</v>
+        <v>73800</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>690</v>
+        <v>32610</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10095,13 +10089,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>690</v>
+        <v>46950</v>
       </c>
     </row>
     <row r="11">
@@ -10109,25 +10103,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>291.78</v>
+        <v>3314.25</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>227304</v>
       </c>
       <c r="D11" t="n">
-        <v>1188</v>
+        <v>178596</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>5010</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>14760</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>164.25</v>
+        <v>525.24</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>60480</v>
       </c>
       <c r="D12" t="n">
-        <v>1584</v>
+        <v>47520</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>1650</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>128.97</v>
+        <v>189.72</v>
       </c>
       <c r="C13" t="n">
-        <v>504</v>
+        <v>15120</v>
       </c>
       <c r="D13" t="n">
-        <v>396</v>
+        <v>11880</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10200,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>142.56</v>
+        <v>158.94</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>3024</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>2376</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>270</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>6.39</v>
+        <v>16.47</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>930</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>1.62</v>
+        <v>15.48</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>13.23</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>5.94</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19">
@@ -10413,7 +10407,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>3.6</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10428,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10443,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
     </row>
     <row r="20">
@@ -10451,13 +10445,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3564</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10466,7 +10460,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3690</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -10492,10 +10486,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1627.17</v>
+        <v>10948.77</v>
       </c>
       <c r="C5" t="n">
-        <v>370339.2</v>
+        <v>2274980.4</v>
       </c>
       <c r="D5" t="n">
-        <v>175117.54</v>
+        <v>1075740.73</v>
       </c>
       <c r="E5" t="n">
-        <v>15684.66</v>
+        <v>120315.24</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>32.4</v>
+        <v>1836</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4321.8</v>
+        <v>31752</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3251.23</v>
+        <v>17531.35</v>
       </c>
       <c r="C6" t="n">
-        <v>466300.8</v>
+        <v>3207405.6</v>
       </c>
       <c r="D6" t="n">
-        <v>206393.62</v>
+        <v>1419658.81</v>
       </c>
       <c r="E6" t="n">
-        <v>13384.8</v>
+        <v>128828.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="G6" t="n">
-        <v>402</v>
+        <v>3102</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4292.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>8180.7</v>
+        <v>54212.4</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>3054.74</v>
+        <v>29508.62</v>
       </c>
       <c r="C7" t="n">
-        <v>291312</v>
+        <v>4585392</v>
       </c>
       <c r="D7" t="n">
-        <v>146030.54</v>
+        <v>2298591.5</v>
       </c>
       <c r="E7" t="n">
-        <v>9954.360000000001</v>
+        <v>199852.92</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>859.5</v>
+        <v>12163.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>9022.799999999999</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>9270</v>
+        <v>113094</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1686.51</v>
+        <v>30611.52</v>
       </c>
       <c r="C8" t="n">
-        <v>99288</v>
+        <v>2971080</v>
       </c>
       <c r="D8" t="n">
-        <v>57416.83</v>
+        <v>1718133.12</v>
       </c>
       <c r="E8" t="n">
-        <v>5077.71</v>
+        <v>94268.78999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G8" t="n">
-        <v>1521</v>
+        <v>47346</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3621</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3983.1</v>
+        <v>113891.1</v>
       </c>
     </row>
     <row r="9">
@@ -11897,37 +11891,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>792.45</v>
+        <v>24835.41</v>
       </c>
       <c r="C9" t="n">
-        <v>38808</v>
+        <v>1934856</v>
       </c>
       <c r="D9" t="n">
-        <v>24485.08</v>
+        <v>1220755.93</v>
       </c>
       <c r="E9" t="n">
-        <v>3132.09</v>
+        <v>41680.89</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>994.5</v>
+        <v>30396</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>510</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>874.8</v>
+        <v>73531.8</v>
       </c>
     </row>
     <row r="10">
@@ -11935,22 +11929,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>451.62</v>
+        <v>17857.44</v>
       </c>
       <c r="C10" t="n">
-        <v>12096</v>
+        <v>1140048</v>
       </c>
       <c r="D10" t="n">
-        <v>8268.48</v>
+        <v>779304.24</v>
       </c>
       <c r="E10" t="n">
-        <v>522</v>
+        <v>21402</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>690</v>
+        <v>32610</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11959,13 +11953,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>614.1</v>
+        <v>41785.5</v>
       </c>
     </row>
     <row r="11">
@@ -11973,25 +11967,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>291.78</v>
+        <v>3314.25</v>
       </c>
       <c r="C11" t="n">
-        <v>1512</v>
+        <v>227304</v>
       </c>
       <c r="D11" t="n">
-        <v>1067.42</v>
+        <v>160468.51</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>4425.84</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>180</v>
+        <v>5010</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>210</v>
+        <v>14760</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>164.25</v>
+        <v>525.24</v>
       </c>
       <c r="C12" t="n">
-        <v>2016</v>
+        <v>60480</v>
       </c>
       <c r="D12" t="n">
-        <v>1468.37</v>
+        <v>44051.04</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1290.6</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>1650</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>240</v>
+        <v>6360</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>128.97</v>
+        <v>189.72</v>
       </c>
       <c r="C13" t="n">
-        <v>504</v>
+        <v>15120</v>
       </c>
       <c r="D13" t="n">
-        <v>376</v>
+        <v>11280.06</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12064,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>540</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>142.56</v>
+        <v>158.94</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>3024</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>2309.47</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>270</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>6.39</v>
+        <v>16.47</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2733.19</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>930</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>1.62</v>
+        <v>15.48</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>13.23</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.44</v>
+        <v>5.94</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
     </row>
     <row r="19">
@@ -12277,7 +12271,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>3.6</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12307,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>630</v>
       </c>
     </row>
     <row r="20">
@@ -12315,13 +12309,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4536</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3564</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12330,7 +12324,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3690</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -12356,10 +12350,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>2520</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3579770.7</v>
+        <v>24087294</v>
       </c>
       <c r="C5" t="n">
-        <v>20368656</v>
+        <v>125123922</v>
       </c>
       <c r="D5" t="n">
-        <v>17744659.92</v>
+        <v>109004808.37</v>
       </c>
       <c r="E5" t="n">
-        <v>2889741.76</v>
+        <v>22166879.82</v>
       </c>
       <c r="F5" t="n">
-        <v>3333.36</v>
+        <v>16666.8</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8963.459999999999</v>
+        <v>507929.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>139999.2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>40711.36</v>
+        <v>299103.84</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>7152710.4</v>
+        <v>38568974.4</v>
       </c>
       <c r="C6" t="n">
-        <v>25646544</v>
+        <v>176407308</v>
       </c>
       <c r="D6" t="n">
-        <v>20913865.11</v>
+        <v>143854027.42</v>
       </c>
       <c r="E6" t="n">
-        <v>2466015.55</v>
+        <v>23735399.69</v>
       </c>
       <c r="F6" t="n">
-        <v>29166.9</v>
+        <v>70833.89999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>7437</v>
+        <v>57387</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1187409.46</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>174999</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>77062.19</v>
+        <v>510680.81</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>6720436.8</v>
+        <v>64918953</v>
       </c>
       <c r="C7" t="n">
-        <v>16022160</v>
+        <v>252196560</v>
       </c>
       <c r="D7" t="n">
-        <v>14797275.02</v>
+        <v>232916277.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1833991.29</v>
+        <v>36820901.98</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>50000.4</v>
       </c>
       <c r="G7" t="n">
-        <v>15900.75</v>
+        <v>225024.75</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2496157.62</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>87323.39999999999</v>
+        <v>1065345.48</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>3710322</v>
+        <v>67345344</v>
       </c>
       <c r="C8" t="n">
-        <v>5460840</v>
+        <v>163409400</v>
       </c>
       <c r="D8" t="n">
-        <v>5818047.59</v>
+        <v>174098429.05</v>
       </c>
       <c r="E8" t="n">
-        <v>935517.29</v>
+        <v>17368081.87</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>79167.3</v>
       </c>
       <c r="G8" t="n">
-        <v>28138.5</v>
+        <v>875901</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1001749.65</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>49583.05</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>37520.8</v>
+        <v>1072854.16</v>
       </c>
     </row>
     <row r="9">
@@ -12829,37 +12823,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1743390</v>
+        <v>54637902</v>
       </c>
       <c r="C9" t="n">
-        <v>2134440</v>
+        <v>106417080</v>
       </c>
       <c r="D9" t="n">
-        <v>2481072.75</v>
+        <v>123699198.59</v>
       </c>
       <c r="E9" t="n">
-        <v>577056.26</v>
+        <v>7679287.17</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>18398.25</v>
+        <v>562326</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>141091.5</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>110832.7</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8240.620000000001</v>
+        <v>692669.5600000001</v>
       </c>
     </row>
     <row r="10">
@@ -12867,22 +12861,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>993564</v>
+        <v>39286368</v>
       </c>
       <c r="C10" t="n">
-        <v>665280</v>
+        <v>62702640</v>
       </c>
       <c r="D10" t="n">
-        <v>837845.08</v>
+        <v>78966898.64</v>
       </c>
       <c r="E10" t="n">
-        <v>96173.28</v>
+        <v>3943104.48</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12765</v>
+        <v>603285</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12891,13 +12885,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>116666</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>5784.82</v>
+        <v>393619.41</v>
       </c>
     </row>
     <row r="11">
@@ -12905,25 +12899,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>641916</v>
+        <v>7291350</v>
       </c>
       <c r="C11" t="n">
-        <v>83160</v>
+        <v>12501720</v>
       </c>
       <c r="D11" t="n">
-        <v>108161.47</v>
+        <v>16260273.71</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>815416.76</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3330</v>
+        <v>92685</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1978.2</v>
+        <v>139039.2</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>361350</v>
+        <v>1155528</v>
       </c>
       <c r="C12" t="n">
-        <v>110880</v>
+        <v>3326400</v>
       </c>
       <c r="D12" t="n">
-        <v>148789.73</v>
+        <v>4463691.88</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>237780.14</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>30525</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2260.8</v>
+        <v>59911.2</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>283734</v>
+        <v>417384</v>
       </c>
       <c r="C13" t="n">
-        <v>27720</v>
+        <v>831600</v>
       </c>
       <c r="D13" t="n">
-        <v>38100.28</v>
+        <v>1143008.48</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12996,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>9990</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>34477.2</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>313632</v>
+        <v>349668</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>166320</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>234018.8</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>4995</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>12717</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>14058</v>
+        <v>36234</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>276954.35</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>2220</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>8760.6</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>3564</v>
+        <v>34056</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3108.6</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>29106</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1110</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>3168</v>
+        <v>13068</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3330</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>4521.6</v>
       </c>
     </row>
     <row r="19">
@@ -13209,7 +13203,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>7920</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -13224,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3885</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13239,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>5934.6</v>
       </c>
     </row>
     <row r="20">
@@ -13247,13 +13241,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>249480</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>361140.12</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13262,7 +13256,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>68265</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -13288,10 +13282,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>138600</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>200633.4</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>28278.63</v>
+        <v>38603.07</v>
       </c>
       <c r="C4" t="n">
-        <v>5172552</v>
+        <v>4061232</v>
       </c>
       <c r="D4" t="n">
-        <v>4064148</v>
+        <v>3190968</v>
       </c>
       <c r="E4" t="n">
-        <v>1602900</v>
+        <v>1124100</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>84150</v>
+        <v>117210</v>
       </c>
       <c r="H4" t="n">
-        <v>7560</v>
+        <v>14880</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>176850</v>
+        <v>372540</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>24330.6</v>
+        <v>13630.32</v>
       </c>
       <c r="C5" t="n">
-        <v>4136328</v>
+        <v>887040</v>
       </c>
       <c r="D5" t="n">
-        <v>3249972</v>
+        <v>696960</v>
       </c>
       <c r="E5" t="n">
-        <v>1090800</v>
+        <v>258300</v>
       </c>
       <c r="F5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G5" t="n">
-        <v>68460</v>
+        <v>35340</v>
       </c>
       <c r="H5" t="n">
-        <v>5100</v>
+        <v>3180</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>151200</v>
+        <v>124980</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>21914.19</v>
+        <v>1353.69</v>
       </c>
       <c r="C6" t="n">
-        <v>3563784</v>
+        <v>117432</v>
       </c>
       <c r="D6" t="n">
-        <v>2800116</v>
+        <v>92268</v>
       </c>
       <c r="E6" t="n">
-        <v>762300</v>
+        <v>34200</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>62040</v>
+        <v>4920</v>
       </c>
       <c r="H6" t="n">
-        <v>7530</v>
+        <v>390</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>146520</v>
+        <v>21630</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>31061.7</v>
+        <v>174.15</v>
       </c>
       <c r="C7" t="n">
-        <v>4585392</v>
+        <v>30240</v>
       </c>
       <c r="D7" t="n">
-        <v>3602808</v>
+        <v>23760</v>
       </c>
       <c r="E7" t="n">
-        <v>939600</v>
+        <v>3600</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>81090</v>
+        <v>1050</v>
       </c>
       <c r="H7" t="n">
-        <v>12360</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>188490</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>30611.52</v>
+        <v>15.57</v>
       </c>
       <c r="C8" t="n">
-        <v>2971080</v>
+        <v>1512</v>
       </c>
       <c r="D8" t="n">
-        <v>2334420</v>
+        <v>1188</v>
       </c>
       <c r="E8" t="n">
-        <v>384300</v>
+        <v>900</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>72840</v>
+        <v>270</v>
       </c>
       <c r="H8" t="n">
-        <v>4260</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>160410</v>
+        <v>720</v>
       </c>
     </row>
     <row r="9">
@@ -13761,37 +13755,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>24835.41</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>1934856</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1520244</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>155700</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>35760</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>90780</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -13799,22 +13793,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>17857.44</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1140048</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>895752</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>73800</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>32610</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13823,13 +13817,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>46950</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,25 +13831,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>3314.25</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>227304</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>178596</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>10800</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5010</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -13867,7 +13861,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>14760</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>525.24</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>60480</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>47520</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>189.72</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15120</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>11880</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3660</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>158.94</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>16.47</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>15.48</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>13.23</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14103,13 +14097,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>5.94</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14141,7 +14135,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -14156,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -14171,7 +14165,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -14179,13 +14173,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4536</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14194,7 +14188,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3690</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -14220,10 +14214,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>10948.77</v>
+        <v>6133.64</v>
       </c>
       <c r="C5" t="n">
-        <v>2274980.4</v>
+        <v>487872</v>
       </c>
       <c r="D5" t="n">
-        <v>1075740.73</v>
+        <v>230693.76</v>
       </c>
       <c r="E5" t="n">
-        <v>120315.24</v>
+        <v>28490.49</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4</v>
+        <v>0.24</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1836</v>
+        <v>1144.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>31752</v>
+        <v>26245.8</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>17531.35</v>
+        <v>1082.95</v>
       </c>
       <c r="C6" t="n">
-        <v>3207405.6</v>
+        <v>105688.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1419658.81</v>
+        <v>46779.88</v>
       </c>
       <c r="E6" t="n">
-        <v>128828.7</v>
+        <v>5779.8</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>3102</v>
+        <v>246</v>
       </c>
       <c r="H6" t="n">
-        <v>4292.1</v>
+        <v>222.3</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>54212.4</v>
+        <v>8003.1</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>29508.62</v>
+        <v>165.44</v>
       </c>
       <c r="C7" t="n">
-        <v>4585392</v>
+        <v>30240</v>
       </c>
       <c r="D7" t="n">
-        <v>2298591.5</v>
+        <v>15158.88</v>
       </c>
       <c r="E7" t="n">
-        <v>199852.92</v>
+        <v>765.72</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>12163.5</v>
+        <v>157.5</v>
       </c>
       <c r="H7" t="n">
-        <v>9022.799999999999</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>113094</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>30611.52</v>
+        <v>15.57</v>
       </c>
       <c r="C8" t="n">
-        <v>2971080</v>
+        <v>1512</v>
       </c>
       <c r="D8" t="n">
-        <v>1718133.12</v>
+        <v>874.37</v>
       </c>
       <c r="E8" t="n">
-        <v>94268.78999999999</v>
+        <v>220.77</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>47346</v>
+        <v>175.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3621</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>113891.1</v>
+        <v>511.2</v>
       </c>
     </row>
     <row r="9">
@@ -14693,37 +14687,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>24835.41</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>1934856</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>1220755.93</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>41680.89</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>30396</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>73531.8</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="10">
@@ -14731,22 +14725,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>17857.44</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1140048</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>779304.24</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>21402</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>32610</v>
+        <v>30</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14755,13 +14749,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>41785.5</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,25 +14763,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>3314.25</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>227304</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>160468.51</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4425.84</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>5010</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -14799,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>14760</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>525.24</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>60480</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>44051.04</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1290.6</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1650</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>189.72</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15120</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>11280.06</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3660</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>158.94</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>2309.47</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>16.47</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>2733.19</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>930</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>15.48</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>330</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>13.23</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15035,13 +15029,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>5.94</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15073,7 +15067,7 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -15088,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -15103,7 +15097,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -15111,13 +15105,13 @@
         <v>800</v>
       </c>
       <c r="B20" t="n">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>4536</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>3564</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15126,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>3690</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -15152,10 +15146,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>2520</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1980</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>24087294</v>
+        <v>13494016.8</v>
       </c>
       <c r="C5" t="n">
-        <v>125123922</v>
+        <v>26832960</v>
       </c>
       <c r="D5" t="n">
-        <v>109004808.37</v>
+        <v>23376198.7</v>
       </c>
       <c r="E5" t="n">
-        <v>22166879.82</v>
+        <v>5249087.88</v>
       </c>
       <c r="F5" t="n">
-        <v>16666.8</v>
+        <v>10000.08</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>507929.4</v>
+        <v>316708.92</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>139999.2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>299103.84</v>
+        <v>247235.44</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>38568974.4</v>
+        <v>2382494.4</v>
       </c>
       <c r="C6" t="n">
-        <v>176407308</v>
+        <v>5812884</v>
       </c>
       <c r="D6" t="n">
-        <v>143854027.42</v>
+        <v>4740204.84</v>
       </c>
       <c r="E6" t="n">
-        <v>23735399.69</v>
+        <v>1064870.35</v>
       </c>
       <c r="F6" t="n">
-        <v>70833.89999999999</v>
+        <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>57387</v>
+        <v>4551</v>
       </c>
       <c r="H6" t="n">
-        <v>1187409.46</v>
+        <v>61499.29</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>174999</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>510680.81</v>
+        <v>75389.2</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>64918953</v>
+        <v>363973.5</v>
       </c>
       <c r="C7" t="n">
-        <v>252196560</v>
+        <v>1663200</v>
       </c>
       <c r="D7" t="n">
-        <v>232916277.1</v>
+        <v>1536049.31</v>
       </c>
       <c r="E7" t="n">
-        <v>36820901.98</v>
+        <v>141076.25</v>
       </c>
       <c r="F7" t="n">
-        <v>50000.4</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>225024.75</v>
+        <v>2913.75</v>
       </c>
       <c r="H7" t="n">
-        <v>2496157.62</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1065345.48</v>
+        <v>19329.84</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>67345344</v>
+        <v>34254</v>
       </c>
       <c r="C8" t="n">
-        <v>163409400</v>
+        <v>83160</v>
       </c>
       <c r="D8" t="n">
-        <v>174098429.05</v>
+        <v>88599.71000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>17368081.87</v>
+        <v>40674.66</v>
       </c>
       <c r="F8" t="n">
-        <v>79167.3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>875901</v>
+        <v>3246.75</v>
       </c>
       <c r="H8" t="n">
-        <v>1001749.65</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1072854.16</v>
+        <v>4815.5</v>
       </c>
     </row>
     <row r="9">
@@ -15625,37 +15619,37 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>54637902</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>106417080</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>123699198.59</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>7679287.17</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>562326</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
-        <v>141091.5</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>110832.7</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>692669.5600000001</v>
+        <v>457.81</v>
       </c>
     </row>
     <row r="10">
@@ -15663,22 +15657,22 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>39286368</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>62702640</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>78966898.64</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>3943104.48</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>603285</v>
+        <v>555</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15687,13 +15681,13 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>116666</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>393619.41</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,25 +15695,25 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>7291350</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>12501720</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>16260273.71</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>815416.76</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>92685</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>139039.2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1155528</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3326400</v>
-      </c>
-      <c r="D12" t="n">
-        <v>4463691.88</v>
-      </c>
-      <c r="E12" t="n">
-        <v>237780.14</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>30525</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>59911.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>417384</v>
-      </c>
-      <c r="C13" t="n">
-        <v>831600</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1143008.48</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>9990</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>34477.2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>349668</v>
-      </c>
-      <c r="C14" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D14" t="n">
-        <v>234018.8</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>4995</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>12717</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>36234</v>
-      </c>
-      <c r="C15" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D15" t="n">
-        <v>276954.35</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>2220</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>8760.6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>34056</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3108.6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>29106</v>
-      </c>
-      <c r="C17" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D17" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1110</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>2826</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>13068</v>
-      </c>
-      <c r="C18" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3330</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>4521.6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>7920</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5934.6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>990</v>
-      </c>
-      <c r="C20" t="n">
-        <v>249480</v>
-      </c>
-      <c r="D20" t="n">
-        <v>361140.12</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>68265</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D21" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>138600</v>
-      </c>
-      <c r="D24" t="n">
-        <v>200633.4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>3691.26</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1094688</v>
-      </c>
-      <c r="D4" t="n">
-        <v>860112</v>
-      </c>
-      <c r="E4" t="n">
-        <v>385200</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13200</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4020</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>33540</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4595.13</v>
-      </c>
-      <c r="C5" t="n">
-        <v>977256</v>
-      </c>
-      <c r="D5" t="n">
-        <v>767844</v>
-      </c>
-      <c r="E5" t="n">
-        <v>229500</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16170</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2910</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>34980</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4484.61</v>
-      </c>
-      <c r="C6" t="n">
-        <v>592704</v>
-      </c>
-      <c r="D6" t="n">
-        <v>465696</v>
-      </c>
-      <c r="E6" t="n">
-        <v>123300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>13050</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1080</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>25710</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3770.37</v>
-      </c>
-      <c r="C7" t="n">
-        <v>335664</v>
-      </c>
-      <c r="D7" t="n">
-        <v>263736</v>
-      </c>
-      <c r="E7" t="n">
-        <v>59400</v>
-      </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4920</v>
-      </c>
-      <c r="H7" t="n">
-        <v>510</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>14730</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4199.85</v>
-      </c>
-      <c r="C8" t="n">
-        <v>270144</v>
-      </c>
-      <c r="D8" t="n">
-        <v>212256</v>
-      </c>
-      <c r="E8" t="n">
-        <v>47700</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3270</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>11370</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4080.96</v>
-      </c>
-      <c r="C9" t="n">
-        <v>200088</v>
-      </c>
-      <c r="D9" t="n">
-        <v>157212</v>
-      </c>
-      <c r="E9" t="n">
-        <v>29700</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3810</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>10020</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3195.99</v>
-      </c>
-      <c r="C10" t="n">
-        <v>126504</v>
-      </c>
-      <c r="D10" t="n">
-        <v>99396</v>
-      </c>
-      <c r="E10" t="n">
-        <v>11700</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3570</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8670</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2203.92</v>
-      </c>
-      <c r="C11" t="n">
-        <v>47880</v>
-      </c>
-      <c r="D11" t="n">
-        <v>37620</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>930</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1260.54</v>
-      </c>
-      <c r="C12" t="n">
-        <v>16128</v>
-      </c>
-      <c r="D12" t="n">
-        <v>12672</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>330</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>728.73</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E13" t="n">
-        <v>900</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>461.16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>356.67</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>310.23</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>406.71</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>182.79</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>792</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2067.81</v>
-      </c>
-      <c r="C5" t="n">
-        <v>537490.8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>254156.36</v>
-      </c>
-      <c r="E5" t="n">
-        <v>25313.85</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1047.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>7345.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>3587.69</v>
-      </c>
-      <c r="C6" t="n">
-        <v>533433.6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>236107.87</v>
-      </c>
-      <c r="E6" t="n">
-        <v>20837.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>652.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>615.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>9512.700000000001</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3581.85</v>
-      </c>
-      <c r="C7" t="n">
-        <v>335664</v>
-      </c>
-      <c r="D7" t="n">
-        <v>168263.57</v>
-      </c>
-      <c r="E7" t="n">
-        <v>12634.38</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>738</v>
-      </c>
-      <c r="H7" t="n">
-        <v>372.3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>8838</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>4199.85</v>
-      </c>
-      <c r="C8" t="n">
-        <v>270144</v>
-      </c>
-      <c r="D8" t="n">
-        <v>156220.42</v>
-      </c>
-      <c r="E8" t="n">
-        <v>11700.81</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2125.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>8072.7</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>4080.96</v>
-      </c>
-      <c r="C9" t="n">
-        <v>200088</v>
-      </c>
-      <c r="D9" t="n">
-        <v>126241.24</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7950.69</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3238.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>8116.2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>3195.99</v>
-      </c>
-      <c r="C10" t="n">
-        <v>126504</v>
-      </c>
-      <c r="D10" t="n">
-        <v>86474.52</v>
-      </c>
-      <c r="E10" t="n">
-        <v>3393</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3570</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>7716.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2203.92</v>
-      </c>
-      <c r="C11" t="n">
-        <v>47880</v>
-      </c>
-      <c r="D11" t="n">
-        <v>33801.57</v>
-      </c>
-      <c r="E11" t="n">
-        <v>737.64</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>930</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>1260.54</v>
-      </c>
-      <c r="C12" t="n">
-        <v>16128</v>
-      </c>
-      <c r="D12" t="n">
-        <v>11746.94</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>330</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>728.73</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2632.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>476.28</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>461.16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2694.38</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>356.67</v>
-      </c>
-      <c r="C15" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1561.82</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>310.23</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D16" t="n">
-        <v>792</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>406.71</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>182.79</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D18" t="n">
-        <v>792</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>39.69</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>4549178.7</v>
-      </c>
-      <c r="C5" t="n">
-        <v>29561994</v>
-      </c>
-      <c r="D5" t="n">
-        <v>25753664.36</v>
-      </c>
-      <c r="E5" t="n">
-        <v>4663823.72</v>
-      </c>
-      <c r="F5" t="n">
-        <v>7500.06</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>289818.54</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>17499.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>69197.44</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>7892913.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>29338848</v>
-      </c>
-      <c r="D6" t="n">
-        <v>23924810.67</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3839137.85</v>
-      </c>
-      <c r="F6" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>12071.25</v>
-      </c>
-      <c r="H6" t="n">
-        <v>170305.74</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>89609.63</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>7880073.3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>18461520</v>
-      </c>
-      <c r="D7" t="n">
-        <v>17050147.35</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2327758.17</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50000.4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>13653</v>
-      </c>
-      <c r="H7" t="n">
-        <v>102996.8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>83253.96000000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>9239670</v>
-      </c>
-      <c r="C8" t="n">
-        <v>14857920</v>
-      </c>
-      <c r="D8" t="n">
-        <v>15829814.75</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2155757.23</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>39321.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>76044.83</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>8978112</v>
-      </c>
-      <c r="C9" t="n">
-        <v>11004840</v>
-      </c>
-      <c r="D9" t="n">
-        <v>12792024.44</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1464835.13</v>
-      </c>
-      <c r="F9" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G9" t="n">
-        <v>59912.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>76454.60000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>7031178</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6957720</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8762463.109999999</v>
-      </c>
-      <c r="E10" t="n">
-        <v>625126.3199999999</v>
-      </c>
-      <c r="F10" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G10" t="n">
-        <v>66045</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>72687.55</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>4848624</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2633400</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3425113.09</v>
-      </c>
-      <c r="E11" t="n">
-        <v>135902.79</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>17205</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>21195</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2773188</v>
-      </c>
-      <c r="C12" t="n">
-        <v>887040</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1190317.84</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>6105</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>4804.2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>1603206</v>
-      </c>
-      <c r="C13" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D13" t="n">
-        <v>266701.98</v>
-      </c>
-      <c r="E13" t="n">
-        <v>87749.83</v>
-      </c>
-      <c r="F13" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1014552</v>
-      </c>
-      <c r="C14" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D14" t="n">
-        <v>273021.93</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>784674</v>
-      </c>
-      <c r="C15" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D15" t="n">
-        <v>158259.63</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>682506</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>894762</v>
-      </c>
-      <c r="C17" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D17" t="n">
-        <v>120380.04</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>402138</v>
-      </c>
-      <c r="C18" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D18" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>87318</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>47520</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>38603.07</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4061232</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3190968</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1124100</v>
-      </c>
-      <c r="F4" t="n">
-        <v>36</v>
-      </c>
-      <c r="G4" t="n">
-        <v>117210</v>
-      </c>
-      <c r="H4" t="n">
-        <v>14880</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>372540</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>13630.32</v>
-      </c>
-      <c r="C5" t="n">
-        <v>887040</v>
-      </c>
-      <c r="D5" t="n">
-        <v>696960</v>
-      </c>
-      <c r="E5" t="n">
-        <v>258300</v>
-      </c>
-      <c r="F5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>35340</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3180</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>124980</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1353.69</v>
-      </c>
-      <c r="C6" t="n">
-        <v>117432</v>
-      </c>
-      <c r="D6" t="n">
-        <v>92268</v>
-      </c>
-      <c r="E6" t="n">
-        <v>34200</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4920</v>
-      </c>
-      <c r="H6" t="n">
-        <v>390</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>21630</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>174.15</v>
-      </c>
-      <c r="C7" t="n">
-        <v>30240</v>
-      </c>
-      <c r="D7" t="n">
-        <v>23760</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1050</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3420</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E8" t="n">
-        <v>900</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>270</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6133.64</v>
-      </c>
-      <c r="C5" t="n">
-        <v>487872</v>
-      </c>
-      <c r="D5" t="n">
-        <v>230693.76</v>
-      </c>
-      <c r="E5" t="n">
-        <v>28490.49</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1144.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>26245.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>1082.95</v>
-      </c>
-      <c r="C6" t="n">
-        <v>105688.8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>46779.88</v>
-      </c>
-      <c r="E6" t="n">
-        <v>5779.8</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>246</v>
-      </c>
-      <c r="H6" t="n">
-        <v>222.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>8003.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>165.44</v>
-      </c>
-      <c r="C7" t="n">
-        <v>30240</v>
-      </c>
-      <c r="D7" t="n">
-        <v>15158.88</v>
-      </c>
-      <c r="E7" t="n">
-        <v>765.72</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2052</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>15.57</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D8" t="n">
-        <v>874.37</v>
-      </c>
-      <c r="E8" t="n">
-        <v>220.77</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>175.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>511.2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>48.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>90</v>
+        <v>847.8</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>13494016.8</v>
-      </c>
-      <c r="C5" t="n">
-        <v>26832960</v>
-      </c>
-      <c r="D5" t="n">
-        <v>23376198.7</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5249087.88</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10000.08</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>316708.92</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>247235.44</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2382494.4</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5812884</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4740204.84</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1064870.35</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4166.7</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4551</v>
-      </c>
-      <c r="H6" t="n">
-        <v>61499.29</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>75389.2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>363973.5</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1663200</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1536049.31</v>
-      </c>
-      <c r="E7" t="n">
-        <v>141076.25</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2913.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>19329.84</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>34254</v>
-      </c>
-      <c r="C8" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D8" t="n">
-        <v>88599.71000000001</v>
-      </c>
-      <c r="E8" t="n">
-        <v>40674.66</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3246.75</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4815.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>457.81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>555</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>847.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_100yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_Breaches.xlsx
@@ -538,7 +538,7 @@
         <v>63960</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>39</v>
@@ -576,7 +576,7 @@
         <v>53340</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
         <v>22</v>
@@ -614,7 +614,7 @@
         <v>43860</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>15</v>
@@ -652,7 +652,7 @@
         <v>47820</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>10</v>
@@ -690,7 +690,7 @@
         <v>30030</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>12</v>
@@ -728,7 +728,7 @@
         <v>13500</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>5</v>
@@ -766,7 +766,7 @@
         <v>3960</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
@@ -804,7 +804,7 @@
         <v>4140</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -842,7 +842,7 @@
         <v>5790</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -918,7 +918,7 @@
         <v>780</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         <v>2910</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -1736,7 +1736,7 @@
         <v>3570</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1774,7 +1774,7 @@
         <v>5730</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1850,7 +1850,7 @@
         <v>780</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>2910</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
         <v>5</v>
@@ -2668,7 +2668,7 @@
         <v>3570</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -2706,7 +2706,7 @@
         <v>5730</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -2782,7 +2782,7 @@
         <v>780</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -3562,7 +3562,7 @@
         <v>805051.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>367996.8</v>
       </c>
       <c r="J10" t="n">
         <v>291665</v>
@@ -3600,7 +3600,7 @@
         <v>987640.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>58333</v>
@@ -3638,7 +3638,7 @@
         <v>1585204.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J12" t="n">
         <v>58333</v>
@@ -3714,7 +3714,7 @@
         <v>215787</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>7560</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>5100</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
         <v>8</v>
@@ -9934,7 +9934,7 @@
         <v>7530</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>6</v>
@@ -9972,7 +9972,7 @@
         <v>12360</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>3</v>
@@ -10010,7 +10010,7 @@
         <v>4260</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -10048,7 +10048,7 @@
         <v>510</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -10124,7 +10124,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -10828,7 +10828,7 @@
         <v>19202.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="J5" t="n">
         <v>6.6</v>
@@ -10866,7 +10866,7 @@
         <v>25000.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>7.5</v>
@@ -10904,7 +10904,7 @@
         <v>34908.6</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>7</v>
@@ -10942,7 +10942,7 @@
         <v>25525.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>10.2</v>
@@ -10980,7 +10980,7 @@
         <v>13500</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="J9" t="n">
         <v>4.75</v>
@@ -11018,7 +11018,7 @@
         <v>3960</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J10" t="n">
         <v>10</v>
@@ -11056,7 +11056,7 @@
         <v>4140</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>5</v>
@@ -11094,7 +11094,7 @@
         <v>5790</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
@@ -11170,7 +11170,7 @@
         <v>780</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>1836</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J5" t="n">
         <v>2.4</v>
@@ -11798,7 +11798,7 @@
         <v>4292.1</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -11836,7 +11836,7 @@
         <v>9022.799999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
         <v>2.1</v>
@@ -11874,7 +11874,7 @@
         <v>3621</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
@@ -11912,7 +11912,7 @@
         <v>510</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>1.9</v>
@@ -11988,7 +11988,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -12692,7 +12692,7 @@
         <v>507929.4</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>287497.5</v>
       </c>
       <c r="J5" t="n">
         <v>139999.2</v>
@@ -12730,7 +12730,7 @@
         <v>1187409.46</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>174999</v>
@@ -12768,7 +12768,7 @@
         <v>2496157.62</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>122499.3</v>
@@ -12806,7 +12806,7 @@
         <v>1001749.65</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>49583.05</v>
@@ -12844,7 +12844,7 @@
         <v>141091.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>110832.7</v>
@@ -12920,7 +12920,7 @@
         <v>8299.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -13586,7 +13586,7 @@
         <v>14880</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>5</v>
@@ -16420,7 +16420,7 @@
         <v>5312343.96</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>402496.5</v>
       </c>
       <c r="J5" t="n">
         <v>384997.8</v>
@@ -16458,7 +16458,7 @@
         <v>6916305.33</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>437497.5</v>
@@ -16496,7 +16496,7 @@
         <v>9657464.189999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>421663</v>
       </c>
       <c r="J7" t="n">
         <v>408331</v>
@@ -16534,7 +16534,7 @@
         <v>7061629.57</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>594996.6</v>
@@ -16572,7 +16572,7 @@
         <v>3734775</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>674660.8</v>
       </c>
       <c r="J9" t="n">
         <v>277081.75</v>
@@ -16610,7 +16610,7 @@
         <v>1095534</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>367996.8</v>
       </c>
       <c r="J10" t="n">
         <v>583330</v>
@@ -16648,7 +16648,7 @@
         <v>1145331</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>766660</v>
       </c>
       <c r="J11" t="n">
         <v>291665</v>
@@ -16686,7 +16686,7 @@
         <v>1601803.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J12" t="n">
         <v>116666</v>
@@ -16762,7 +16762,7 @@
         <v>215787</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -17314,7 +17314,7 @@
         <v>2640</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -17352,7 +17352,7 @@
         <v>5220</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
@@ -17504,7 +17504,7 @@
         <v>8280</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -18284,7 +18284,7 @@
         <v>1879.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
@@ -18436,7 +18436,7 @@
         <v>8280</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="J9" t="n">
         <v>1.9</v>
@@ -19216,7 +19216,7 @@
         <v>519880.68</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>34999.8</v>
@@ -19368,7 +19368,7 @@
         <v>2290662</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>337330.4</v>
       </c>
       <c r="J9" t="n">
         <v>110832.7</v>
@@ -20110,7 +20110,7 @@
         <v>16080</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>12</v>
@@ -20148,7 +20148,7 @@
         <v>22860</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>8</v>
@@ -21080,7 +21080,7 @@
         <v>8229.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>2.4</v>
@@ -22012,7 +22012,7 @@
         <v>2276718.84</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>139999.2</v>

--- a/risk/Risk_Analysis_T3_100yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_Breaches.xlsx
@@ -544,7 +544,7 @@
         <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1173</v>
       </c>
       <c r="L4" t="n">
         <v>1466700</v>
@@ -582,7 +582,7 @@
         <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="L5" t="n">
         <v>920070</v>
@@ -620,7 +620,7 @@
         <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L6" t="n">
         <v>575640</v>
@@ -658,7 +658,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>457</v>
       </c>
       <c r="L7" t="n">
         <v>534420</v>
@@ -696,7 +696,7 @@
         <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>388</v>
       </c>
       <c r="L8" t="n">
         <v>466110</v>
@@ -734,7 +734,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="L9" t="n">
         <v>397500</v>
@@ -772,7 +772,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="L10" t="n">
         <v>330330</v>
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="L11" t="n">
         <v>210240</v>
@@ -848,7 +848,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="L12" t="n">
         <v>157290</v>
@@ -886,7 +886,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L13" t="n">
         <v>124080</v>
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L14" t="n">
         <v>50910</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L15" t="n">
         <v>25170</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>10110</v>
@@ -1038,7 +1038,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>3810</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>1860</v>
@@ -1476,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L4" t="n">
         <v>17280</v>
@@ -1514,7 +1514,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
         <v>19830</v>
@@ -1552,7 +1552,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="L6" t="n">
         <v>19170</v>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L7" t="n">
         <v>23460</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L8" t="n">
         <v>34470</v>
@@ -1666,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L9" t="n">
         <v>41010</v>
@@ -1704,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
         <v>45960</v>
@@ -1742,7 +1742,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
         <v>48030</v>
@@ -1780,7 +1780,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L12" t="n">
         <v>82200</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L13" t="n">
         <v>86430</v>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L14" t="n">
         <v>39570</v>
@@ -1894,7 +1894,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L15" t="n">
         <v>18960</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>8730</v>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>3120</v>
@@ -2008,7 +2008,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>1260</v>
@@ -2446,7 +2446,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="L5" t="n">
         <v>4164.3</v>
@@ -2484,7 +2484,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="L6" t="n">
         <v>7092.9</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>15.58</v>
       </c>
       <c r="L7" t="n">
         <v>14076</v>
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>15.3</v>
       </c>
       <c r="L8" t="n">
         <v>24473.7</v>
@@ -2598,7 +2598,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L9" t="n">
         <v>33218.1</v>
@@ -2636,7 +2636,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
         <v>40904.4</v>
@@ -2674,7 +2674,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L11" t="n">
         <v>48030</v>
@@ -2712,7 +2712,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L12" t="n">
         <v>82200</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L13" t="n">
         <v>86430</v>
@@ -2788,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L14" t="n">
         <v>39570</v>
@@ -2826,7 +2826,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L15" t="n">
         <v>18960</v>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>8730</v>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>3120</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>1260</v>
@@ -3378,7 +3378,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>71682.24000000001</v>
       </c>
       <c r="L5" t="n">
         <v>39227.71</v>
@@ -3416,7 +3416,7 @@
         <v>29166.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>249607.8</v>
       </c>
       <c r="L6" t="n">
         <v>66815.12</v>
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>332383.72</v>
       </c>
       <c r="L7" t="n">
         <v>132595.92</v>
@@ -3492,7 +3492,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>326410.2</v>
       </c>
       <c r="L8" t="n">
         <v>230542.25</v>
@@ -3530,7 +3530,7 @@
         <v>55416.35</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>426680</v>
       </c>
       <c r="L9" t="n">
         <v>312914.5</v>
@@ -3568,7 +3568,7 @@
         <v>291665</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>554684</v>
       </c>
       <c r="L10" t="n">
         <v>385319.45</v>
@@ -3606,7 +3606,7 @@
         <v>58333</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>533350</v>
       </c>
       <c r="L11" t="n">
         <v>452442.6</v>
@@ -3644,7 +3644,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>746690</v>
       </c>
       <c r="L12" t="n">
         <v>774324</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>853360</v>
       </c>
       <c r="L13" t="n">
         <v>814170.6</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>512016</v>
       </c>
       <c r="L14" t="n">
         <v>372749.4</v>
@@ -3758,7 +3758,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>277342</v>
       </c>
       <c r="L15" t="n">
         <v>178603.2</v>
@@ -3796,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L16" t="n">
         <v>82236.60000000001</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L17" t="n">
         <v>29390.4</v>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L18" t="n">
         <v>11869.2</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L4" t="n">
         <v>153690</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L5" t="n">
         <v>62910</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>12810</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>3270</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>13.02</v>
       </c>
       <c r="L5" t="n">
         <v>13211.1</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
         <v>4739.7</v>
@@ -5318,7 +5318,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="L7" t="n">
         <v>1962</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>277768.68</v>
       </c>
       <c r="L5" t="n">
         <v>124448.56</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>27734.2</v>
       </c>
       <c r="L6" t="n">
         <v>44647.97</v>
@@ -6250,7 +6250,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>17493.88</v>
       </c>
       <c r="L7" t="n">
         <v>18482.04</v>
@@ -7068,7 +7068,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="L4" t="n">
         <v>150240</v>
@@ -7106,7 +7106,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="L5" t="n">
         <v>53730</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L6" t="n">
         <v>16650</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L7" t="n">
         <v>4620</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2520</v>
@@ -8038,7 +8038,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>23.94</v>
       </c>
       <c r="L5" t="n">
         <v>11283.3</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L6" t="n">
         <v>6160.5</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="L7" t="n">
         <v>2772</v>
@@ -8152,7 +8152,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
         <v>1789.2</v>
@@ -8970,7 +8970,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>510735.96</v>
       </c>
       <c r="L5" t="n">
         <v>106288.69</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>138671</v>
       </c>
       <c r="L6" t="n">
         <v>58031.91</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>52481.64</v>
       </c>
       <c r="L7" t="n">
         <v>26112.24</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>38401.2</v>
       </c>
       <c r="L8" t="n">
         <v>16854.26</v>
@@ -9864,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="L4" t="n">
         <v>176850</v>
@@ -9902,7 +9902,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="L5" t="n">
         <v>151200</v>
@@ -9940,7 +9940,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="L6" t="n">
         <v>146520</v>
@@ -9978,7 +9978,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="L7" t="n">
         <v>188490</v>
@@ -10016,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="L8" t="n">
         <v>160410</v>
@@ -10054,7 +10054,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L9" t="n">
         <v>90780</v>
@@ -10092,7 +10092,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L10" t="n">
         <v>46950</v>
@@ -10130,7 +10130,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L11" t="n">
         <v>14760</v>
@@ -10168,7 +10168,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
         <v>6360</v>
@@ -10396,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>480</v>
@@ -10834,7 +10834,7 @@
         <v>6.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>274.26</v>
       </c>
       <c r="L5" t="n">
         <v>193214.7</v>
@@ -10872,7 +10872,7 @@
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="L6" t="n">
         <v>212986.8</v>
@@ -10910,7 +10910,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>374.74</v>
       </c>
       <c r="L7" t="n">
         <v>320652</v>
@@ -10948,7 +10948,7 @@
         <v>10.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>349.2</v>
       </c>
       <c r="L8" t="n">
         <v>330938.1</v>
@@ -10986,7 +10986,7 @@
         <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="L9" t="n">
         <v>321975</v>
@@ -11024,7 +11024,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="L10" t="n">
         <v>293993.7</v>
@@ -11062,7 +11062,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="L11" t="n">
         <v>210240</v>
@@ -11100,7 +11100,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="L12" t="n">
         <v>157290</v>
@@ -11138,7 +11138,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L13" t="n">
         <v>124080</v>
@@ -11176,7 +11176,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L14" t="n">
         <v>50910</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L15" t="n">
         <v>25170</v>
@@ -11252,7 +11252,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
         <v>10110</v>
@@ -11290,7 +11290,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L17" t="n">
         <v>3810</v>
@@ -11328,7 +11328,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>1860</v>
@@ -11766,7 +11766,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>70.14</v>
       </c>
       <c r="L5" t="n">
         <v>31752</v>
@@ -11804,7 +11804,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>84.5</v>
       </c>
       <c r="L6" t="n">
         <v>54212.4</v>
@@ -11842,7 +11842,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>162.36</v>
       </c>
       <c r="L7" t="n">
         <v>113094</v>
@@ -11880,7 +11880,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>142.2</v>
       </c>
       <c r="L8" t="n">
         <v>113891.1</v>
@@ -11918,7 +11918,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="L9" t="n">
         <v>73531.8</v>
@@ -11956,7 +11956,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="L10" t="n">
         <v>41785.5</v>
@@ -11994,7 +11994,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L11" t="n">
         <v>14760</v>
@@ -12032,7 +12032,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
         <v>6360</v>
@@ -12260,7 +12260,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="n">
         <v>480</v>
@@ -12698,7 +12698,7 @@
         <v>139999.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1496366.76</v>
       </c>
       <c r="L5" t="n">
         <v>299103.84</v>
@@ -12736,7 +12736,7 @@
         <v>174999</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1802723</v>
       </c>
       <c r="L6" t="n">
         <v>510680.81</v>
@@ -12774,7 +12774,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3463788.24</v>
       </c>
       <c r="L7" t="n">
         <v>1065345.48</v>
@@ -12812,7 +12812,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3033694.8</v>
       </c>
       <c r="L8" t="n">
         <v>1072854.16</v>
@@ -12850,7 +12850,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2112066</v>
       </c>
       <c r="L9" t="n">
         <v>692669.5600000001</v>
@@ -12888,7 +12888,7 @@
         <v>116666</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1280040</v>
       </c>
       <c r="L10" t="n">
         <v>393619.41</v>
@@ -12926,7 +12926,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>298676</v>
       </c>
       <c r="L11" t="n">
         <v>139039.2</v>
@@ -12964,7 +12964,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L12" t="n">
         <v>59911.2</v>
@@ -13192,7 +13192,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L18" t="n">
         <v>4521.6</v>
@@ -13592,7 +13592,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="L4" t="n">
         <v>372540</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
         <v>124980</v>
@@ -13668,7 +13668,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>21630</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>14.28</v>
       </c>
       <c r="L5" t="n">
         <v>26245.8</v>
@@ -14600,7 +14600,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="L6" t="n">
         <v>8003.1</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>304649.52</v>
       </c>
       <c r="L5" t="n">
         <v>247235.44</v>
@@ -15532,7 +15532,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>13867.1</v>
       </c>
       <c r="L6" t="n">
         <v>75389.2</v>
@@ -16426,7 +16426,7 @@
         <v>384997.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>5851062.84</v>
       </c>
       <c r="L5" t="n">
         <v>1820082.47</v>
@@ -16464,7 +16464,7 @@
         <v>437497.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5546840</v>
       </c>
       <c r="L6" t="n">
         <v>2006335.66</v>
@@ -16502,7 +16502,7 @@
         <v>408331</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>7994703.16</v>
       </c>
       <c r="L7" t="n">
         <v>3020541.84</v>
@@ -16540,7 +16540,7 @@
         <v>594996.6</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>7449832.8</v>
       </c>
       <c r="L8" t="n">
         <v>3117436.9</v>
@@ -16578,7 +16578,7 @@
         <v>277081.75</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7402898</v>
       </c>
       <c r="L9" t="n">
         <v>3033004.5</v>
@@ -16616,7 +16616,7 @@
         <v>583330</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>6336198</v>
       </c>
       <c r="L10" t="n">
         <v>2769420.65</v>
@@ -16654,7 +16654,7 @@
         <v>291665</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>4181464</v>
       </c>
       <c r="L11" t="n">
         <v>1980460.8</v>
@@ -16692,7 +16692,7 @@
         <v>116666</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>2432076</v>
       </c>
       <c r="L12" t="n">
         <v>1481671.8</v>
@@ -16730,7 +16730,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1621384</v>
       </c>
       <c r="L13" t="n">
         <v>1168833.6</v>
@@ -16768,7 +16768,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>725356</v>
       </c>
       <c r="L14" t="n">
         <v>479572.2</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>341344</v>
       </c>
       <c r="L15" t="n">
         <v>237101.4</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L16" t="n">
         <v>95236.2</v>
@@ -16882,7 +16882,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L17" t="n">
         <v>35890.2</v>
@@ -16920,7 +16920,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L18" t="n">
         <v>17521.2</v>
@@ -17320,7 +17320,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="L4" t="n">
         <v>131970</v>
@@ -17358,7 +17358,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="L5" t="n">
         <v>161370</v>
@@ -17396,7 +17396,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="L6" t="n">
         <v>161820</v>
@@ -17434,7 +17434,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="L7" t="n">
         <v>177600</v>
@@ -17472,7 +17472,7 @@
         <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="L8" t="n">
         <v>211320</v>
@@ -17510,7 +17510,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="L9" t="n">
         <v>247980</v>
@@ -17548,7 +17548,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="L10" t="n">
         <v>225930</v>
@@ -17586,7 +17586,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="L11" t="n">
         <v>144150</v>
@@ -17624,7 +17624,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L12" t="n">
         <v>67620</v>
@@ -17662,7 +17662,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L13" t="n">
         <v>33840</v>
@@ -17700,7 +17700,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>9450</v>
@@ -17738,7 +17738,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>5280</v>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1050</v>
@@ -17814,7 +17814,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>390</v>
@@ -18290,7 +18290,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>61.74</v>
       </c>
       <c r="L5" t="n">
         <v>33887.7</v>
@@ -18328,7 +18328,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>82.55</v>
       </c>
       <c r="L6" t="n">
         <v>59873.4</v>
@@ -18366,7 +18366,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>122.18</v>
       </c>
       <c r="L7" t="n">
         <v>106560</v>
@@ -18404,7 +18404,7 @@
         <v>9.35</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>167.4</v>
       </c>
       <c r="L8" t="n">
         <v>150037.2</v>
@@ -18442,7 +18442,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>223</v>
       </c>
       <c r="L9" t="n">
         <v>200863.8</v>
@@ -18480,7 +18480,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="L10" t="n">
         <v>201077.7</v>
@@ -18518,7 +18518,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="L11" t="n">
         <v>144150</v>
@@ -18556,7 +18556,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L12" t="n">
         <v>67620</v>
@@ -18594,7 +18594,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="L13" t="n">
         <v>33840</v>
@@ -18632,7 +18632,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
         <v>9450</v>
@@ -18670,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>5280</v>
@@ -18708,7 +18708,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
         <v>1050</v>
@@ -18746,7 +18746,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
         <v>390</v>
@@ -19222,7 +19222,7 @@
         <v>34999.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1317161.16</v>
       </c>
       <c r="L5" t="n">
         <v>319222.13</v>
@@ -19260,7 +19260,7 @@
         <v>116666</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1761121.7</v>
       </c>
       <c r="L6" t="n">
         <v>564007.4300000001</v>
@@ -19298,7 +19298,7 @@
         <v>122499.3</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2606588.12</v>
       </c>
       <c r="L7" t="n">
         <v>1003795.2</v>
@@ -19336,7 +19336,7 @@
         <v>545413.55</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3571311.6</v>
       </c>
       <c r="L8" t="n">
         <v>1413350.42</v>
@@ -19374,7 +19374,7 @@
         <v>110832.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>4757482</v>
       </c>
       <c r="L9" t="n">
         <v>1892137</v>
@@ -19412,7 +19412,7 @@
         <v>174999</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>4480140</v>
       </c>
       <c r="L10" t="n">
         <v>1894151.93</v>
@@ -19450,7 +19450,7 @@
         <v>233332</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>3349438</v>
       </c>
       <c r="L11" t="n">
         <v>1357893</v>
@@ -19488,7 +19488,7 @@
         <v>58333</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1621384</v>
       </c>
       <c r="L12" t="n">
         <v>636980.4</v>
@@ -19526,7 +19526,7 @@
         <v>174999</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>746690</v>
       </c>
       <c r="L13" t="n">
         <v>318772.8</v>
@@ -19564,7 +19564,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L14" t="n">
         <v>89019</v>
@@ -19602,7 +19602,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L15" t="n">
         <v>49737.6</v>
@@ -19640,7 +19640,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L16" t="n">
         <v>9891</v>
@@ -19678,7 +19678,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L17" t="n">
         <v>3673.8</v>
@@ -20116,7 +20116,7 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>401</v>
       </c>
       <c r="L4" t="n">
         <v>406890</v>
@@ -20154,7 +20154,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="L5" t="n">
         <v>286440</v>
@@ -20192,7 +20192,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L6" t="n">
         <v>142170</v>
@@ -20230,7 +20230,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="L7" t="n">
         <v>95160</v>
@@ -20268,7 +20268,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L8" t="n">
         <v>37410</v>
@@ -20306,7 +20306,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>5880</v>
@@ -21086,7 +21086,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>87.78</v>
       </c>
       <c r="L5" t="n">
         <v>60152.4</v>
@@ -21124,7 +21124,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>71.5</v>
       </c>
       <c r="L6" t="n">
         <v>52602.9</v>
@@ -21162,7 +21162,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>70.52</v>
       </c>
       <c r="L7" t="n">
         <v>57096</v>
@@ -21200,7 +21200,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="L8" t="n">
         <v>26561.1</v>
@@ -21238,7 +21238,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>4762.8</v>
@@ -22018,7 +22018,7 @@
         <v>139999.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1872698.52</v>
       </c>
       <c r="L5" t="n">
         <v>566635.61</v>
@@ -22056,7 +22056,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1525381</v>
       </c>
       <c r="L6" t="n">
         <v>495519.32</v>
@@ -22094,7 +22094,7 @@
         <v>163332.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1504473.68</v>
       </c>
       <c r="L7" t="n">
         <v>537844.3199999999</v>
@@ -22132,7 +22132,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>460814.4</v>
       </c>
       <c r="L8" t="n">
         <v>250205.56</v>
@@ -22170,7 +22170,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L9" t="n">
         <v>44865.58</v>

--- a/risk/Risk_Analysis_T3_100yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_Breaches.xlsx
@@ -549,7 +549,7 @@
         <v>39</v>
       </c>
       <c r="K4" t="n">
-        <v>1157</v>
+        <v>452</v>
       </c>
       <c r="L4" t="n">
         <v>1463190</v>
@@ -590,7 +590,7 @@
         <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>637</v>
+        <v>266</v>
       </c>
       <c r="L5" t="n">
         <v>918210</v>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>391</v>
+        <v>149</v>
       </c>
       <c r="L6" t="n">
         <v>573810</v>
@@ -672,7 +672,7 @@
         <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>456</v>
+        <v>181</v>
       </c>
       <c r="L7" t="n">
         <v>533370</v>
@@ -713,7 +713,7 @@
         <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>388</v>
+        <v>106</v>
       </c>
       <c r="L8" t="n">
         <v>465390</v>
@@ -754,7 +754,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>347</v>
+        <v>106</v>
       </c>
       <c r="L9" t="n">
         <v>397140</v>
@@ -795,7 +795,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>297</v>
+        <v>81</v>
       </c>
       <c r="L10" t="n">
         <v>330240</v>
@@ -836,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>196</v>
+        <v>43</v>
       </c>
       <c r="L11" t="n">
         <v>209970</v>
@@ -877,7 +877,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>114</v>
+        <v>18</v>
       </c>
       <c r="L12" t="n">
         <v>157080</v>
@@ -918,7 +918,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="L13" t="n">
         <v>124080</v>
@@ -959,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>50910</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>25170</v>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>10110</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>3810</v>
@@ -1123,7 +1123,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>1860</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>17160</v>
@@ -1594,7 +1594,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L5" t="n">
         <v>19830</v>
@@ -1635,7 +1635,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>19200</v>
@@ -1676,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L7" t="n">
         <v>23520</v>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>34680</v>
@@ -1758,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L9" t="n">
         <v>41220</v>
@@ -1799,7 +1799,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>45990</v>
@@ -1840,7 +1840,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
         <v>48180</v>
@@ -1881,7 +1881,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
         <v>82410</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="L13" t="n">
         <v>86460</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>39630</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>19020</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>8730</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>3120</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>1260</v>
@@ -2598,7 +2598,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.32</v>
+        <v>0.99</v>
       </c>
       <c r="L5" t="n">
         <v>4164.3</v>
@@ -2639,7 +2639,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>9.130000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>7104</v>
@@ -2680,7 +2680,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>12.12</v>
+        <v>6.38</v>
       </c>
       <c r="L7" t="n">
         <v>14112</v>
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>12.51</v>
+        <v>6.62</v>
       </c>
       <c r="L8" t="n">
         <v>24622.8</v>
@@ -2762,7 +2762,7 @@
         <v>0.95</v>
       </c>
       <c r="K9" t="n">
-        <v>16.06</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L9" t="n">
         <v>33388.2</v>
@@ -2803,7 +2803,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>22.62</v>
+        <v>3.48</v>
       </c>
       <c r="L10" t="n">
         <v>40931.1</v>
@@ -2844,7 +2844,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>22.46</v>
+        <v>2.7</v>
       </c>
       <c r="L11" t="n">
         <v>48180</v>
@@ -2885,7 +2885,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>32.44</v>
+        <v>4.64</v>
       </c>
       <c r="L12" t="n">
         <v>82410</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>37.98</v>
+        <v>6.65</v>
       </c>
       <c r="L13" t="n">
         <v>86460</v>
@@ -2967,7 +2967,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>23.33</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>39630</v>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>12.82</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>19020</v>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>8730</v>
@@ -3090,7 +3090,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>3120</v>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>1260</v>
@@ -3602,7 +3602,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>112504.25</v>
+        <v>48216.11</v>
       </c>
       <c r="L5" t="n">
         <v>749574</v>
@@ -3643,7 +3643,7 @@
         <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>443122.06</v>
+        <v>172325.24</v>
       </c>
       <c r="L6" t="n">
         <v>1278720</v>
@@ -3684,7 +3684,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>588595.83</v>
+        <v>309787.28</v>
       </c>
       <c r="L7" t="n">
         <v>2540160</v>
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>607532.67</v>
+        <v>321634.94</v>
       </c>
       <c r="L8" t="n">
         <v>4432104</v>
@@ -3766,7 +3766,7 @@
         <v>23064.1</v>
       </c>
       <c r="K9" t="n">
-        <v>779809.36</v>
+        <v>467885.62</v>
       </c>
       <c r="L9" t="n">
         <v>6009876</v>
@@ -3807,7 +3807,7 @@
         <v>121390</v>
       </c>
       <c r="K10" t="n">
-        <v>1098336.72</v>
+        <v>168974.88</v>
       </c>
       <c r="L10" t="n">
         <v>7367598</v>
@@ -3848,7 +3848,7 @@
         <v>24278</v>
       </c>
       <c r="K11" t="n">
-        <v>1090689.15</v>
+        <v>130882.7</v>
       </c>
       <c r="L11" t="n">
         <v>8672400</v>
@@ -3889,7 +3889,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>1575399.42</v>
+        <v>225057.06</v>
       </c>
       <c r="L12" t="n">
         <v>14833800</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1844156.88</v>
+        <v>322727.45</v>
       </c>
       <c r="L13" t="n">
         <v>15562800</v>
@@ -3971,7 +3971,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1132714.37</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
         <v>7133400</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>622390.8100000001</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>3423600</v>
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1571400</v>
@@ -4094,7 +4094,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>561600</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>226800</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="L4" t="n">
         <v>153600</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="L5" t="n">
         <v>63600</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>12750</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>10.26</v>
+        <v>5.96</v>
       </c>
       <c r="L5" t="n">
         <v>13356</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>4717.5</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>498233.12</v>
+        <v>289296.65</v>
       </c>
       <c r="L5" t="n">
         <v>2404080</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>49235.78</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>849150</v>
@@ -7577,7 +7577,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>192</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
         <v>150330</v>
@@ -7618,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
         <v>54300</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>16920</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>4590</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>2520</v>
@@ -8622,7 +8622,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>18.87</v>
+        <v>4.3</v>
       </c>
       <c r="L5" t="n">
         <v>11403</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>5.07</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>6260.4</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>2754</v>
@@ -8745,7 +8745,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1789.2</v>
@@ -9626,7 +9626,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>916106.05</v>
+        <v>208936.47</v>
       </c>
       <c r="L5" t="n">
         <v>2052540</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>246178.92</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1126872</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>92936.17999999999</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>495720</v>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>71474.42999999999</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>322056</v>
@@ -10589,7 +10589,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>227</v>
+        <v>132</v>
       </c>
       <c r="L4" t="n">
         <v>177330</v>
@@ -10630,7 +10630,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>167</v>
+        <v>94</v>
       </c>
       <c r="L5" t="n">
         <v>151260</v>
@@ -10671,7 +10671,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="n">
-        <v>130</v>
+        <v>61</v>
       </c>
       <c r="L6" t="n">
         <v>146580</v>
@@ -10712,7 +10712,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>198</v>
+        <v>87</v>
       </c>
       <c r="L7" t="n">
         <v>188550</v>
@@ -10753,7 +10753,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>158</v>
+        <v>49</v>
       </c>
       <c r="L8" t="n">
         <v>160500</v>
@@ -10794,7 +10794,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="L9" t="n">
         <v>90810</v>
@@ -10835,7 +10835,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
         <v>46980</v>
@@ -10876,7 +10876,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>14760</v>
@@ -11163,7 +11163,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>480</v>
@@ -11634,7 +11634,7 @@
         <v>6.6</v>
       </c>
       <c r="K5" t="n">
-        <v>210.85</v>
+        <v>88.05</v>
       </c>
       <c r="L5" t="n">
         <v>192824.1</v>
@@ -11675,7 +11675,7 @@
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>198.24</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>212309.7</v>
@@ -11716,7 +11716,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>290.93</v>
+        <v>115.48</v>
       </c>
       <c r="L7" t="n">
         <v>320022</v>
@@ -11757,7 +11757,7 @@
         <v>10.2</v>
       </c>
       <c r="K8" t="n">
-        <v>285.57</v>
+        <v>78.02</v>
       </c>
       <c r="L8" t="n">
         <v>330426.9</v>
@@ -11798,7 +11798,7 @@
         <v>4.75</v>
       </c>
       <c r="K9" t="n">
-        <v>278.64</v>
+        <v>85.12</v>
       </c>
       <c r="L9" t="n">
         <v>321683.4</v>
@@ -11839,7 +11839,7 @@
         <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>258.39</v>
+        <v>70.47</v>
       </c>
       <c r="L10" t="n">
         <v>293913.6</v>
@@ -11880,7 +11880,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>176.11</v>
+        <v>38.64</v>
       </c>
       <c r="L11" t="n">
         <v>209970</v>
@@ -11921,7 +11921,7 @@
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>105.68</v>
+        <v>16.69</v>
       </c>
       <c r="L12" t="n">
         <v>157080</v>
@@ -11962,7 +11962,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>72.16</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>124080</v>
@@ -12003,7 +12003,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>33.05</v>
+        <v>0.97</v>
       </c>
       <c r="L14" t="n">
         <v>50910</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>15.78</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>25170</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>10110</v>
@@ -12126,7 +12126,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>3810</v>
@@ -12167,7 +12167,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>1860</v>
@@ -12638,7 +12638,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>55.28</v>
+        <v>31.11</v>
       </c>
       <c r="L5" t="n">
         <v>31764.6</v>
@@ -12679,7 +12679,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>65.91</v>
+        <v>30.93</v>
       </c>
       <c r="L6" t="n">
         <v>54234.6</v>
@@ -12720,7 +12720,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>126.32</v>
+        <v>55.51</v>
       </c>
       <c r="L7" t="n">
         <v>113130</v>
@@ -12761,7 +12761,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>116.29</v>
+        <v>36.06</v>
       </c>
       <c r="L8" t="n">
         <v>113955</v>
@@ -12802,7 +12802,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>79.5</v>
+        <v>25.7</v>
       </c>
       <c r="L9" t="n">
         <v>73556.10000000001</v>
@@ -12843,7 +12843,7 @@
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>53.07</v>
+        <v>14.79</v>
       </c>
       <c r="L10" t="n">
         <v>41812.2</v>
@@ -12884,7 +12884,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>12.58</v>
+        <v>1.8</v>
       </c>
       <c r="L11" t="n">
         <v>14760</v>
@@ -13171,7 +13171,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>480</v>
@@ -13642,7 +13642,7 @@
         <v>58267.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2684030.01</v>
+        <v>1510771.38</v>
       </c>
       <c r="L5" t="n">
         <v>5717628</v>
@@ -13683,7 +13683,7 @@
         <v>72834</v>
       </c>
       <c r="K6" t="n">
-        <v>3200325.96</v>
+        <v>1501691.41</v>
       </c>
       <c r="L6" t="n">
         <v>9762228</v>
@@ -13724,7 +13724,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>6133788.14</v>
+        <v>2695149.34</v>
       </c>
       <c r="L7" t="n">
         <v>20363400</v>
@@ -13765,7 +13765,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>5646480.13</v>
+        <v>1751123.58</v>
       </c>
       <c r="L8" t="n">
         <v>20511900</v>
@@ -13806,7 +13806,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3860056.33</v>
+        <v>1247694.98</v>
       </c>
       <c r="L9" t="n">
         <v>13240098</v>
@@ -13847,7 +13847,7 @@
         <v>48556</v>
       </c>
       <c r="K10" t="n">
-        <v>2576866.92</v>
+        <v>718143.24</v>
       </c>
       <c r="L10" t="n">
         <v>7526196</v>
@@ -13888,7 +13888,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>610785.92</v>
+        <v>87255.13</v>
       </c>
       <c r="L11" t="n">
         <v>2656800</v>
@@ -14175,7 +14175,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>86400</v>
@@ -14605,7 +14605,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="L4" t="n">
         <v>375150</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="L5" t="n">
         <v>126090</v>
@@ -14687,7 +14687,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>21360</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11.25</v>
+        <v>5.63</v>
       </c>
       <c r="L5" t="n">
         <v>26478.9</v>
@@ -15691,7 +15691,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.51</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>7903.2</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>546449.22</v>
+        <v>273224.61</v>
       </c>
       <c r="L5" t="n">
         <v>4766202</v>
@@ -16695,7 +16695,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>24617.89</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>1422576</v>
@@ -17658,7 +17658,7 @@
         <v>160234.8</v>
       </c>
       <c r="K5" t="n">
-        <v>10237886.93</v>
+        <v>4275161.58</v>
       </c>
       <c r="L5" t="n">
         <v>34708338</v>
@@ -17699,7 +17699,7 @@
         <v>182085</v>
       </c>
       <c r="K6" t="n">
-        <v>9625595.77</v>
+        <v>3668065.91</v>
       </c>
       <c r="L6" t="n">
         <v>38215746</v>
@@ -17740,7 +17740,7 @@
         <v>169946</v>
       </c>
       <c r="K7" t="n">
-        <v>14126299.97</v>
+        <v>5607149.77</v>
       </c>
       <c r="L7" t="n">
         <v>57603960</v>
@@ -17781,7 +17781,7 @@
         <v>247635.6</v>
       </c>
       <c r="K8" t="n">
-        <v>13866039.81</v>
+        <v>3788144.9</v>
       </c>
       <c r="L8" t="n">
         <v>59476842</v>
@@ -17822,7 +17822,7 @@
         <v>115320.5</v>
       </c>
       <c r="K9" t="n">
-        <v>13529692.4</v>
+        <v>4132989.61</v>
       </c>
       <c r="L9" t="n">
         <v>57903012</v>
@@ -17863,7 +17863,7 @@
         <v>242780</v>
       </c>
       <c r="K10" t="n">
-        <v>12546384.84</v>
+        <v>3421741.32</v>
       </c>
       <c r="L10" t="n">
         <v>52904448</v>
@@ -17904,7 +17904,7 @@
         <v>121390</v>
       </c>
       <c r="K11" t="n">
-        <v>8551002.939999999</v>
+        <v>1875985.34</v>
       </c>
       <c r="L11" t="n">
         <v>37794600</v>
@@ -17945,7 +17945,7 @@
         <v>48556</v>
       </c>
       <c r="K12" t="n">
-        <v>5131300.97</v>
+        <v>810205.42</v>
       </c>
       <c r="L12" t="n">
         <v>28274400</v>
@@ -17986,7 +17986,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>3503898.07</v>
+        <v>414935.3</v>
       </c>
       <c r="L13" t="n">
         <v>22334400</v>
@@ -18027,7 +18027,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1604678.69</v>
+        <v>47196.43</v>
       </c>
       <c r="L14" t="n">
         <v>9163800</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>766019.46</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>4530600</v>
@@ -18109,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1819800</v>
@@ -18150,7 +18150,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>145668</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>685800</v>
@@ -18191,7 +18191,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>97112</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>334800</v>
@@ -18621,7 +18621,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>119</v>
+        <v>73</v>
       </c>
       <c r="L4" t="n">
         <v>128790</v>
@@ -18662,7 +18662,7 @@
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>132</v>
+        <v>67</v>
       </c>
       <c r="L5" t="n">
         <v>159870</v>
@@ -18703,7 +18703,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="L6" t="n">
         <v>161130</v>
@@ -18744,7 +18744,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="L7" t="n">
         <v>176790</v>
@@ -18785,7 +18785,7 @@
         <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>186</v>
+        <v>47</v>
       </c>
       <c r="L8" t="n">
         <v>210720</v>
@@ -18826,7 +18826,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>223</v>
+        <v>61</v>
       </c>
       <c r="L9" t="n">
         <v>247590</v>
@@ -18867,7 +18867,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>210</v>
+        <v>60</v>
       </c>
       <c r="L10" t="n">
         <v>225900</v>
@@ -18908,7 +18908,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>157</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
         <v>143970</v>
@@ -18949,7 +18949,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
         <v>67440</v>
@@ -18990,7 +18990,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>33900</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>9480</v>
@@ -19072,7 +19072,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>5280</v>
@@ -19113,7 +19113,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1050</v>
@@ -19154,7 +19154,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>390</v>
@@ -19666,7 +19666,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>43.69</v>
+        <v>22.18</v>
       </c>
       <c r="L5" t="n">
         <v>33572.7</v>
@@ -19707,7 +19707,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>59.83</v>
+        <v>23.32</v>
       </c>
       <c r="L6" t="n">
         <v>59618.1</v>
@@ -19748,7 +19748,7 @@
         <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>94.42</v>
+        <v>41.47</v>
       </c>
       <c r="L7" t="n">
         <v>106074</v>
@@ -19789,7 +19789,7 @@
         <v>9.35</v>
       </c>
       <c r="K8" t="n">
-        <v>136.9</v>
+        <v>34.59</v>
       </c>
       <c r="L8" t="n">
         <v>149611.2</v>
@@ -19830,7 +19830,7 @@
         <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>179.07</v>
+        <v>48.98</v>
       </c>
       <c r="L9" t="n">
         <v>200547.9</v>
@@ -19871,7 +19871,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>182.7</v>
+        <v>52.2</v>
       </c>
       <c r="L10" t="n">
         <v>201051</v>
@@ -19912,7 +19912,7 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>141.06</v>
+        <v>34.14</v>
       </c>
       <c r="L11" t="n">
         <v>143970</v>
@@ -19953,7 +19953,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>70.45</v>
+        <v>9.27</v>
       </c>
       <c r="L12" t="n">
         <v>67440</v>
@@ -19994,7 +19994,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>34.18</v>
+        <v>1.9</v>
       </c>
       <c r="L13" t="n">
         <v>33900</v>
@@ -20035,7 +20035,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>9.720000000000001</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>9480</v>
@@ -20076,7 +20076,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>5280</v>
@@ -20117,7 +20117,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>1050</v>
@@ -20158,7 +20158,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>390</v>
@@ -20670,7 +20670,7 @@
         <v>14566.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2121508.75</v>
+        <v>1076826.41</v>
       </c>
       <c r="L5" t="n">
         <v>6043086</v>
@@ -20711,7 +20711,7 @@
         <v>48556</v>
       </c>
       <c r="K6" t="n">
-        <v>2904911.26</v>
+        <v>1132423.03</v>
       </c>
       <c r="L6" t="n">
         <v>10731258</v>
@@ -20752,7 +20752,7 @@
         <v>50983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4584851.74</v>
+        <v>2013617.32</v>
       </c>
       <c r="L7" t="n">
         <v>19093320</v>
@@ -20793,7 +20793,7 @@
         <v>226999.3</v>
       </c>
       <c r="K8" t="n">
-        <v>6647122.18</v>
+        <v>1679649.15</v>
       </c>
       <c r="L8" t="n">
         <v>26930016</v>
@@ -20834,7 +20834,7 @@
         <v>46128.2</v>
       </c>
       <c r="K9" t="n">
-        <v>8694874.359999999</v>
+        <v>2378418.55</v>
       </c>
       <c r="L9" t="n">
         <v>36098622</v>
@@ -20875,7 +20875,7 @@
         <v>72834</v>
       </c>
       <c r="K10" t="n">
-        <v>8871181.199999999</v>
+        <v>2534623.2</v>
       </c>
       <c r="L10" t="n">
         <v>36189180</v>
@@ -20916,7 +20916,7 @@
         <v>97112</v>
       </c>
       <c r="K11" t="n">
-        <v>6849527.86</v>
+        <v>1657847.51</v>
       </c>
       <c r="L11" t="n">
         <v>25914600</v>
@@ -20957,7 +20957,7 @@
         <v>24278</v>
       </c>
       <c r="K12" t="n">
-        <v>3420867.31</v>
+        <v>450114.12</v>
       </c>
       <c r="L12" t="n">
         <v>12139200</v>
@@ -20998,7 +20998,7 @@
         <v>72834</v>
       </c>
       <c r="K13" t="n">
-        <v>1659741.19</v>
+        <v>92207.84</v>
       </c>
       <c r="L13" t="n">
         <v>6102000</v>
@@ -21039,7 +21039,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>471964.32</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1706400</v>
@@ -21080,7 +21080,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>143628.65</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>950400</v>
@@ -21121,7 +21121,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>189000</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>48556</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>70200</v>
@@ -21633,7 +21633,7 @@
         <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>402</v>
+        <v>108</v>
       </c>
       <c r="L4" t="n">
         <v>405660</v>
@@ -21674,7 +21674,7 @@
         <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>209</v>
+        <v>54</v>
       </c>
       <c r="L5" t="n">
         <v>285360</v>
@@ -21715,7 +21715,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="L6" t="n">
         <v>142620</v>
@@ -21756,7 +21756,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="L7" t="n">
         <v>95130</v>
@@ -21797,7 +21797,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>37560</v>
@@ -21838,7 +21838,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>5850</v>
@@ -22678,7 +22678,7 @@
         <v>2.4</v>
       </c>
       <c r="K5" t="n">
-        <v>69.18000000000001</v>
+        <v>17.87</v>
       </c>
       <c r="L5" t="n">
         <v>59925.6</v>
@@ -22719,7 +22719,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>55.77</v>
+        <v>17.74</v>
       </c>
       <c r="L6" t="n">
         <v>52769.4</v>
@@ -22760,7 +22760,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>54.87</v>
+        <v>11.48</v>
       </c>
       <c r="L7" t="n">
         <v>57078</v>
@@ -22801,7 +22801,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>17.66</v>
+        <v>0.74</v>
       </c>
       <c r="L8" t="n">
         <v>26667.6</v>
@@ -22842,7 +22842,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>4738.5</v>
@@ -23682,7 +23682,7 @@
         <v>58267.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3359055.52</v>
+        <v>867889.9399999999</v>
       </c>
       <c r="L5" t="n">
         <v>10786608</v>
@@ -23723,7 +23723,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>2707968.12</v>
+        <v>861626.22</v>
       </c>
       <c r="L6" t="n">
         <v>9498492</v>
@@ -23764,7 +23764,7 @@
         <v>67978.39999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>2664170.61</v>
+        <v>557617.1</v>
       </c>
       <c r="L7" t="n">
         <v>10274040</v>
@@ -23805,7 +23805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>857693.1800000001</v>
+        <v>35737.22</v>
       </c>
       <c r="L8" t="n">
         <v>4800168</v>
@@ -23846,7 +23846,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>77980.94</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>852930</v>

--- a/risk/Risk_Analysis_T3_100yrs_Present_Breaches.xlsx
+++ b/risk/Risk_Analysis_T3_100yrs_Present_Breaches.xlsx
@@ -560,7 +560,7 @@
         <v>551550</v>
       </c>
       <c r="H4" t="n">
-        <v>63960</v>
+        <v>70260</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
@@ -572,22 +572,22 @@
         <v>452</v>
       </c>
       <c r="L4" t="n">
-        <v>1463190</v>
+        <v>1544160</v>
       </c>
       <c r="M4" t="n">
-        <v>69420</v>
+        <v>44250</v>
       </c>
       <c r="N4" t="n">
-        <v>77730</v>
+        <v>73680</v>
       </c>
       <c r="O4" t="n">
-        <v>214890</v>
+        <v>218700</v>
       </c>
       <c r="P4" t="n">
-        <v>41850</v>
+        <v>15090</v>
       </c>
       <c r="Q4" t="n">
-        <v>219349.02</v>
+        <v>2273092.65</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>376410</v>
       </c>
       <c r="H5" t="n">
-        <v>53340</v>
+        <v>57720</v>
       </c>
       <c r="I5" t="n">
         <v>7</v>
@@ -625,22 +625,22 @@
         <v>266</v>
       </c>
       <c r="L5" t="n">
-        <v>918210</v>
+        <v>984960</v>
       </c>
       <c r="M5" t="n">
-        <v>52410</v>
+        <v>42300</v>
       </c>
       <c r="N5" t="n">
-        <v>79920</v>
+        <v>89730</v>
       </c>
       <c r="O5" t="n">
-        <v>186840</v>
+        <v>213630</v>
       </c>
       <c r="P5" t="n">
-        <v>49890</v>
+        <v>34230</v>
       </c>
       <c r="Q5" t="n">
-        <v>144524.01</v>
+        <v>1497688.32</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>236220</v>
       </c>
       <c r="H6" t="n">
-        <v>43860</v>
+        <v>46380</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -678,22 +678,22 @@
         <v>149</v>
       </c>
       <c r="L6" t="n">
-        <v>573810</v>
+        <v>571680</v>
       </c>
       <c r="M6" t="n">
-        <v>35460</v>
+        <v>23790</v>
       </c>
       <c r="N6" t="n">
-        <v>33510</v>
+        <v>45570</v>
       </c>
       <c r="O6" t="n">
-        <v>117330</v>
+        <v>125490</v>
       </c>
       <c r="P6" t="n">
-        <v>49320</v>
+        <v>36720</v>
       </c>
       <c r="Q6" t="n">
-        <v>95790.41</v>
+        <v>992666.74</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>206040</v>
       </c>
       <c r="H7" t="n">
-        <v>47820</v>
+        <v>50160</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -731,22 +731,22 @@
         <v>181</v>
       </c>
       <c r="L7" t="n">
-        <v>533370</v>
+        <v>530130</v>
       </c>
       <c r="M7" t="n">
-        <v>24990</v>
+        <v>24660</v>
       </c>
       <c r="N7" t="n">
-        <v>12360</v>
+        <v>17250</v>
       </c>
       <c r="O7" t="n">
-        <v>85230</v>
+        <v>91350</v>
       </c>
       <c r="P7" t="n">
-        <v>60210</v>
+        <v>43980</v>
       </c>
       <c r="Q7" t="n">
-        <v>90155.06</v>
+        <v>934268.12</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>187140</v>
       </c>
       <c r="H8" t="n">
-        <v>30030</v>
+        <v>29220</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -784,22 +784,22 @@
         <v>106</v>
       </c>
       <c r="L8" t="n">
-        <v>465390</v>
+        <v>456450</v>
       </c>
       <c r="M8" t="n">
-        <v>20670</v>
+        <v>26100</v>
       </c>
       <c r="N8" t="n">
-        <v>3120</v>
+        <v>5820</v>
       </c>
       <c r="O8" t="n">
-        <v>60360</v>
+        <v>68850</v>
       </c>
       <c r="P8" t="n">
-        <v>66120</v>
+        <v>50100</v>
       </c>
       <c r="Q8" t="n">
-        <v>83657.37</v>
+        <v>866933.22</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>152760</v>
       </c>
       <c r="H9" t="n">
-        <v>13500</v>
+        <v>16620</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
@@ -837,22 +837,22 @@
         <v>106</v>
       </c>
       <c r="L9" t="n">
-        <v>397140</v>
+        <v>412410</v>
       </c>
       <c r="M9" t="n">
-        <v>12360</v>
+        <v>33540</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O9" t="n">
-        <v>56940</v>
+        <v>61830</v>
       </c>
       <c r="P9" t="n">
-        <v>67200</v>
+        <v>57990</v>
       </c>
       <c r="Q9" t="n">
-        <v>74701.69</v>
+        <v>774126.41</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>164040</v>
       </c>
       <c r="H10" t="n">
-        <v>3960</v>
+        <v>4530</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -890,22 +890,22 @@
         <v>81</v>
       </c>
       <c r="L10" t="n">
-        <v>330240</v>
+        <v>354090</v>
       </c>
       <c r="M10" t="n">
-        <v>10080</v>
+        <v>24330</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>43140</v>
+        <v>54990</v>
       </c>
       <c r="P10" t="n">
-        <v>74580</v>
+        <v>72840</v>
       </c>
       <c r="Q10" t="n">
-        <v>68964.11</v>
+        <v>714668.4300000001</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>88350</v>
       </c>
       <c r="H11" t="n">
-        <v>4140</v>
+        <v>4350</v>
       </c>
       <c r="I11" t="n">
         <v>2</v>
@@ -943,22 +943,22 @@
         <v>43</v>
       </c>
       <c r="L11" t="n">
-        <v>209970</v>
+        <v>247860</v>
       </c>
       <c r="M11" t="n">
-        <v>6750</v>
+        <v>24930</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>16080</v>
+        <v>28530</v>
       </c>
       <c r="P11" t="n">
-        <v>73890</v>
+        <v>86220</v>
       </c>
       <c r="Q11" t="n">
-        <v>45318.53</v>
+        <v>469631.52</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>65160</v>
       </c>
       <c r="H12" t="n">
-        <v>5790</v>
+        <v>5880</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -996,22 +996,22 @@
         <v>18</v>
       </c>
       <c r="L12" t="n">
-        <v>157080</v>
+        <v>201240</v>
       </c>
       <c r="M12" t="n">
-        <v>4650</v>
+        <v>22860</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6540</v>
+        <v>16650</v>
       </c>
       <c r="P12" t="n">
-        <v>65400</v>
+        <v>101520</v>
       </c>
       <c r="Q12" t="n">
-        <v>30294.82</v>
+        <v>313942.33</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>53250</v>
       </c>
       <c r="H13" t="n">
-        <v>2250</v>
+        <v>3060</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,22 +1049,22 @@
         <v>9</v>
       </c>
       <c r="L13" t="n">
-        <v>124080</v>
+        <v>163950</v>
       </c>
       <c r="M13" t="n">
-        <v>3240</v>
+        <v>16410</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2610</v>
+        <v>3930</v>
       </c>
       <c r="P13" t="n">
-        <v>45450</v>
+        <v>75180</v>
       </c>
       <c r="Q13" t="n">
-        <v>21759.54</v>
+        <v>225492.06</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>30330</v>
       </c>
       <c r="H14" t="n">
-        <v>780</v>
+        <v>840</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -1102,22 +1102,22 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>50910</v>
+        <v>74190</v>
       </c>
       <c r="M14" t="n">
-        <v>2100</v>
+        <v>19830</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1680</v>
+        <v>2340</v>
       </c>
       <c r="P14" t="n">
-        <v>31680</v>
+        <v>48210</v>
       </c>
       <c r="Q14" t="n">
-        <v>11836.3</v>
+        <v>122658.39</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>9810</v>
       </c>
       <c r="H15" t="n">
-        <v>510</v>
+        <v>780</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,22 +1155,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>25170</v>
+        <v>38460</v>
       </c>
       <c r="M15" t="n">
-        <v>1050</v>
+        <v>7020</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2880</v>
+        <v>3090</v>
       </c>
       <c r="P15" t="n">
-        <v>26490</v>
+        <v>26550</v>
       </c>
       <c r="Q15" t="n">
-        <v>4226.07</v>
+        <v>43794.34</v>
       </c>
     </row>
     <row r="16">
@@ -1196,7 +1196,7 @@
         <v>4410</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1208,22 +1208,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10110</v>
+        <v>26070</v>
       </c>
       <c r="M16" t="n">
-        <v>360</v>
+        <v>3510</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="P16" t="n">
-        <v>36840</v>
+        <v>45810</v>
       </c>
       <c r="Q16" t="n">
-        <v>2649.61</v>
+        <v>27457.62</v>
       </c>
     </row>
     <row r="17">
@@ -1249,7 +1249,7 @@
         <v>1860</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1261,22 +1261,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3810</v>
+        <v>12960</v>
       </c>
       <c r="M17" t="n">
-        <v>780</v>
+        <v>2850</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P17" t="n">
-        <v>27090</v>
+        <v>44070</v>
       </c>
       <c r="Q17" t="n">
-        <v>1404.71</v>
+        <v>14556.87</v>
       </c>
     </row>
     <row r="18">
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1860</v>
+        <v>7800</v>
       </c>
       <c r="M18" t="n">
-        <v>1110</v>
+        <v>1890</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>20490</v>
+        <v>30000</v>
       </c>
       <c r="Q18" t="n">
-        <v>669.8200000000001</v>
+        <v>6941.31</v>
       </c>
     </row>
     <row r="19">
@@ -1355,7 +1355,7 @@
         <v>330</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1367,22 +1367,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>4020</v>
+        <v>7200</v>
       </c>
       <c r="M19" t="n">
-        <v>2490</v>
+        <v>3420</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P19" t="n">
-        <v>19950</v>
+        <v>29730</v>
       </c>
       <c r="Q19" t="n">
-        <v>300.99</v>
+        <v>3119.08</v>
       </c>
     </row>
     <row r="20">
@@ -1420,10 +1420,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1110</v>
+        <v>3390</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>2160</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -1432,10 +1432,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>7860</v>
+        <v>18420</v>
       </c>
       <c r="Q20" t="n">
-        <v>152.56</v>
+        <v>1580.94</v>
       </c>
     </row>
     <row r="21">
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1473,10 +1473,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>1200</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1485,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.65</v>
+        <v>234.77</v>
       </c>
     </row>
     <row r="22">
@@ -1526,10 +1526,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.02</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="23">
@@ -1579,10 +1579,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.15</v>
+        <v>84.42</v>
       </c>
     </row>
     <row r="24">
@@ -1852,7 +1852,7 @@
         <v>8190</v>
       </c>
       <c r="H4" t="n">
-        <v>3480</v>
+        <v>3270</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>17160</v>
+        <v>17370</v>
       </c>
       <c r="M4" t="n">
-        <v>3210</v>
+        <v>1260</v>
       </c>
       <c r="N4" t="n">
-        <v>1080</v>
+        <v>270</v>
       </c>
       <c r="O4" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>105.14</v>
+        <v>11915.64</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>8970</v>
       </c>
       <c r="H5" t="n">
-        <v>4170</v>
+        <v>4860</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>3</v>
       </c>
       <c r="L5" t="n">
-        <v>19830</v>
+        <v>17370</v>
       </c>
       <c r="M5" t="n">
-        <v>6060</v>
+        <v>4590</v>
       </c>
       <c r="N5" t="n">
-        <v>240</v>
+        <v>930</v>
       </c>
       <c r="O5" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>197.88</v>
+        <v>22426.74</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>8610</v>
       </c>
       <c r="H6" t="n">
-        <v>2700</v>
+        <v>3660</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1970,13 +1970,13 @@
         <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>19200</v>
+        <v>17130</v>
       </c>
       <c r="M6" t="n">
-        <v>8040</v>
+        <v>4770</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="O6" t="n">
         <v>30</v>
@@ -1985,7 +1985,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>493.78</v>
+        <v>55961.28</v>
       </c>
     </row>
     <row r="7">
@@ -2023,22 +2023,22 @@
         <v>10</v>
       </c>
       <c r="L7" t="n">
-        <v>23520</v>
+        <v>18300</v>
       </c>
       <c r="M7" t="n">
-        <v>7440</v>
+        <v>4110</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>720</v>
+        <v>390</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>866.86</v>
+        <v>98244.36</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>11850</v>
       </c>
       <c r="H8" t="n">
-        <v>4050</v>
+        <v>3510</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -2076,22 +2076,22 @@
         <v>9</v>
       </c>
       <c r="L8" t="n">
-        <v>34680</v>
+        <v>27630</v>
       </c>
       <c r="M8" t="n">
-        <v>6990</v>
+        <v>2190</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>420</v>
+        <v>660</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1173.66</v>
+        <v>133015.14</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>19110</v>
       </c>
       <c r="H9" t="n">
-        <v>4290</v>
+        <v>5040</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,22 +2129,22 @@
         <v>12</v>
       </c>
       <c r="L9" t="n">
-        <v>41220</v>
+        <v>37980</v>
       </c>
       <c r="M9" t="n">
-        <v>3960</v>
+        <v>2250</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>300</v>
+        <v>360</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1207.9</v>
+        <v>136895.22</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>20430</v>
       </c>
       <c r="H10" t="n">
-        <v>2910</v>
+        <v>2760</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -2182,22 +2182,22 @@
         <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>45990</v>
+        <v>47670</v>
       </c>
       <c r="M10" t="n">
-        <v>2790</v>
+        <v>1110</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1288.82</v>
+        <v>146066.04</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>16590</v>
       </c>
       <c r="H11" t="n">
-        <v>3570</v>
+        <v>3510</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -2235,22 +2235,22 @@
         <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>48180</v>
+        <v>47310</v>
       </c>
       <c r="M11" t="n">
-        <v>1770</v>
+        <v>2160</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1187.7</v>
+        <v>134606.34</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>27420</v>
       </c>
       <c r="H12" t="n">
-        <v>5730</v>
+        <v>5400</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -2288,22 +2288,22 @@
         <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>82410</v>
+        <v>77460</v>
       </c>
       <c r="M12" t="n">
-        <v>1470</v>
+        <v>3360</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1530.77</v>
+        <v>173486.7</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>32220</v>
       </c>
       <c r="H13" t="n">
-        <v>2250</v>
+        <v>3000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
         <v>7</v>
       </c>
       <c r="L13" t="n">
-        <v>86460</v>
+        <v>97320</v>
       </c>
       <c r="M13" t="n">
-        <v>510</v>
+        <v>3630</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2006.29</v>
+        <v>227379.42</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>20250</v>
       </c>
       <c r="H14" t="n">
-        <v>780</v>
+        <v>840</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -2394,10 +2394,10 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>39630</v>
+        <v>47190</v>
       </c>
       <c r="M14" t="n">
-        <v>420</v>
+        <v>3750</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1290.76</v>
+        <v>146286.36</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>7080</v>
       </c>
       <c r="H15" t="n">
-        <v>510</v>
+        <v>780</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>19020</v>
+        <v>25050</v>
       </c>
       <c r="M15" t="n">
-        <v>300</v>
+        <v>3480</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>497.77</v>
+        <v>56414.16</v>
       </c>
     </row>
     <row r="16">
@@ -2488,7 +2488,7 @@
         <v>3690</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8730</v>
+        <v>13470</v>
       </c>
       <c r="M16" t="n">
-        <v>270</v>
+        <v>1950</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>371.33</v>
+        <v>42084.18</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2541,7 @@
         <v>900</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3120</v>
+        <v>6750</v>
       </c>
       <c r="M17" t="n">
-        <v>690</v>
+        <v>1830</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>142.29</v>
+        <v>16126.2</v>
       </c>
     </row>
     <row r="18">
@@ -2606,10 +2606,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1260</v>
+        <v>2490</v>
       </c>
       <c r="M18" t="n">
-        <v>330</v>
+        <v>720</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>64.09999999999999</v>
+        <v>7264.44</v>
       </c>
     </row>
     <row r="19">
@@ -2647,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2659,10 +2659,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>3150</v>
+        <v>3840</v>
       </c>
       <c r="M19" t="n">
-        <v>2310</v>
+        <v>3210</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>29.62</v>
+        <v>3356.82</v>
       </c>
     </row>
     <row r="20">
@@ -2712,10 +2712,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1110</v>
+        <v>3030</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2130</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.96</v>
+        <v>1695.24</v>
       </c>
     </row>
     <row r="21">
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2765,10 +2765,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>1200</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -2780,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.75</v>
+        <v>312.12</v>
       </c>
     </row>
     <row r="22">
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.84</v>
+        <v>94.86</v>
       </c>
     </row>
     <row r="23">
@@ -2871,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1501.2</v>
+        <v>1749.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>0.99</v>
       </c>
       <c r="L5" t="n">
-        <v>4164.3</v>
+        <v>3647.7</v>
       </c>
       <c r="M5" t="n">
-        <v>121.2</v>
+        <v>91.8</v>
       </c>
       <c r="N5" t="n">
-        <v>2.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.890000000000001</v>
+        <v>1121.34</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>430.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1539</v>
+        <v>2086.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3262,13 +3262,13 @@
         <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>7104</v>
+        <v>6338.1</v>
       </c>
       <c r="M6" t="n">
-        <v>643.2</v>
+        <v>381.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
         <v>7.5</v>
@@ -3277,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>370.33</v>
+        <v>41970.96</v>
       </c>
     </row>
     <row r="7">
@@ -3315,22 +3315,22 @@
         <v>6.38</v>
       </c>
       <c r="L7" t="n">
-        <v>14112</v>
+        <v>10980</v>
       </c>
       <c r="M7" t="n">
-        <v>2604</v>
+        <v>1438.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>252</v>
+        <v>136.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>693.49</v>
+        <v>78595.49000000001</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>7702.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3442.5</v>
+        <v>2983.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3368,22 +3368,22 @@
         <v>6.62</v>
       </c>
       <c r="L8" t="n">
-        <v>24622.8</v>
+        <v>19617.3</v>
       </c>
       <c r="M8" t="n">
-        <v>3844.5</v>
+        <v>1204.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>189</v>
+        <v>297</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1114.98</v>
+        <v>126364.38</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>16243.5</v>
       </c>
       <c r="H9" t="n">
-        <v>4290</v>
+        <v>5040</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>9.640000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>33388.2</v>
+        <v>30763.8</v>
       </c>
       <c r="M9" t="n">
-        <v>2772</v>
+        <v>1575</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1171.66</v>
+        <v>132788.36</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>20430</v>
       </c>
       <c r="H10" t="n">
-        <v>2910</v>
+        <v>2760</v>
       </c>
       <c r="I10" t="n">
         <v>0.87</v>
@@ -3474,22 +3474,22 @@
         <v>3.48</v>
       </c>
       <c r="L10" t="n">
-        <v>40931.1</v>
+        <v>42426.3</v>
       </c>
       <c r="M10" t="n">
-        <v>2371.5</v>
+        <v>943.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>126</v>
+        <v>168</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1288.82</v>
+        <v>146066.04</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>16590</v>
       </c>
       <c r="H11" t="n">
-        <v>3570</v>
+        <v>3510</v>
       </c>
       <c r="I11" t="n">
         <v>0.9</v>
@@ -3527,22 +3527,22 @@
         <v>2.7</v>
       </c>
       <c r="L11" t="n">
-        <v>48180</v>
+        <v>47310</v>
       </c>
       <c r="M11" t="n">
-        <v>1593</v>
+        <v>1944</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>51</v>
+        <v>25.5</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1187.7</v>
+        <v>134606.34</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>27420</v>
       </c>
       <c r="H12" t="n">
-        <v>5730</v>
+        <v>5400</v>
       </c>
       <c r="I12" t="n">
         <v>0.93</v>
@@ -3580,22 +3580,22 @@
         <v>4.64</v>
       </c>
       <c r="L12" t="n">
-        <v>82410</v>
+        <v>77460</v>
       </c>
       <c r="M12" t="n">
-        <v>1396.5</v>
+        <v>3192</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1530.76</v>
+        <v>173486.7</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>32220</v>
       </c>
       <c r="H13" t="n">
-        <v>2250</v>
+        <v>3000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,22 +3633,22 @@
         <v>6.65</v>
       </c>
       <c r="L13" t="n">
-        <v>86460</v>
+        <v>97320</v>
       </c>
       <c r="M13" t="n">
-        <v>510</v>
+        <v>3630</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2006.29</v>
+        <v>227379.42</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>20250</v>
       </c>
       <c r="H14" t="n">
-        <v>780</v>
+        <v>840</v>
       </c>
       <c r="I14" t="n">
         <v>0.97</v>
@@ -3686,10 +3686,10 @@
         <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>39630</v>
+        <v>47190</v>
       </c>
       <c r="M14" t="n">
-        <v>420</v>
+        <v>3750</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1290.76</v>
+        <v>146286.36</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>7080</v>
       </c>
       <c r="H15" t="n">
-        <v>510</v>
+        <v>780</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>19020</v>
+        <v>25050</v>
       </c>
       <c r="M15" t="n">
-        <v>300</v>
+        <v>3480</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>497.77</v>
+        <v>56414.16</v>
       </c>
     </row>
     <row r="16">
@@ -3780,7 +3780,7 @@
         <v>3690</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>8730</v>
+        <v>13470</v>
       </c>
       <c r="M16" t="n">
-        <v>270</v>
+        <v>1950</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>371.33</v>
+        <v>42084.18</v>
       </c>
     </row>
     <row r="17">
@@ -3833,7 +3833,7 @@
         <v>900</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3120</v>
+        <v>6750</v>
       </c>
       <c r="M17" t="n">
-        <v>690</v>
+        <v>1830</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>142.29</v>
+        <v>16126.2</v>
       </c>
     </row>
     <row r="18">
@@ -3898,10 +3898,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1260</v>
+        <v>2490</v>
       </c>
       <c r="M18" t="n">
-        <v>330</v>
+        <v>720</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>64.09999999999999</v>
+        <v>7264.44</v>
       </c>
     </row>
     <row r="19">
@@ -3939,7 +3939,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -3951,10 +3951,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>3150</v>
+        <v>3840</v>
       </c>
       <c r="M19" t="n">
-        <v>2310</v>
+        <v>3210</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>29.62</v>
+        <v>3356.82</v>
       </c>
     </row>
     <row r="20">
@@ -4004,10 +4004,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1110</v>
+        <v>3030</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2130</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>14.96</v>
+        <v>1695.24</v>
       </c>
     </row>
     <row r="21">
@@ -4045,7 +4045,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -4057,10 +4057,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>1200</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.75</v>
+        <v>312.12</v>
       </c>
     </row>
     <row r="22">
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -4125,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.84</v>
+        <v>94.86</v>
       </c>
     </row>
     <row r="23">
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8556840</v>
+        <v>9972720</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>48216.11</v>
       </c>
       <c r="L5" t="n">
-        <v>749574</v>
+        <v>656586</v>
       </c>
       <c r="M5" t="n">
-        <v>42420</v>
+        <v>32130</v>
       </c>
       <c r="N5" t="n">
-        <v>408</v>
+        <v>1581</v>
       </c>
       <c r="O5" t="n">
-        <v>255</v>
+        <v>510</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>5936.49</v>
+        <v>672802.2</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>23247</v>
       </c>
       <c r="H6" t="n">
-        <v>8772300</v>
+        <v>11891340</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -4554,13 +4554,13 @@
         <v>172325.24</v>
       </c>
       <c r="L6" t="n">
-        <v>1278720</v>
+        <v>1140858</v>
       </c>
       <c r="M6" t="n">
-        <v>225120</v>
+        <v>133560</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1530</v>
       </c>
       <c r="O6" t="n">
         <v>1275</v>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>222199.2</v>
+        <v>25182576</v>
       </c>
     </row>
     <row r="7">
@@ -4607,22 +4607,22 @@
         <v>309787.28</v>
       </c>
       <c r="L7" t="n">
-        <v>2540160</v>
+        <v>1976400</v>
       </c>
       <c r="M7" t="n">
-        <v>911400</v>
+        <v>503475</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>42840</v>
+        <v>23205</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>416093.76</v>
+        <v>47157292.8</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>415935</v>
       </c>
       <c r="H8" t="n">
-        <v>19622250</v>
+        <v>17005950</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4660,22 +4660,22 @@
         <v>321634.94</v>
       </c>
       <c r="L8" t="n">
-        <v>4432104</v>
+        <v>3531114</v>
       </c>
       <c r="M8" t="n">
-        <v>1345575</v>
+        <v>421575</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>32130</v>
+        <v>50490</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>668987.91</v>
+        <v>75818629.8</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>877149</v>
       </c>
       <c r="H9" t="n">
-        <v>24453000</v>
+        <v>28728000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>467885.62</v>
       </c>
       <c r="L9" t="n">
-        <v>6009876</v>
+        <v>5537484</v>
       </c>
       <c r="M9" t="n">
-        <v>970200</v>
+        <v>551250</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>28050</v>
+        <v>33660</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>702997.22</v>
+        <v>79673018.04000001</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>1103220</v>
       </c>
       <c r="H10" t="n">
-        <v>16587000</v>
+        <v>15732000</v>
       </c>
       <c r="I10" t="n">
         <v>168974.88</v>
@@ -4766,22 +4766,22 @@
         <v>168974.88</v>
       </c>
       <c r="L10" t="n">
-        <v>7367598</v>
+        <v>7636734</v>
       </c>
       <c r="M10" t="n">
-        <v>830025</v>
+        <v>330225</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>21420</v>
+        <v>28560</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>773290.8</v>
+        <v>87639624</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>895860</v>
       </c>
       <c r="H11" t="n">
-        <v>20349000</v>
+        <v>20007000</v>
       </c>
       <c r="I11" t="n">
         <v>174510.26</v>
@@ -4819,22 +4819,22 @@
         <v>130882.7</v>
       </c>
       <c r="L11" t="n">
-        <v>8672400</v>
+        <v>8515800</v>
       </c>
       <c r="M11" t="n">
-        <v>557550</v>
+        <v>680400</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>8670</v>
+        <v>4335</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>712621.8</v>
+        <v>80763804</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>1480680</v>
       </c>
       <c r="H12" t="n">
-        <v>32661000</v>
+        <v>30780000</v>
       </c>
       <c r="I12" t="n">
         <v>180045.65</v>
@@ -4872,22 +4872,22 @@
         <v>225057.06</v>
       </c>
       <c r="L12" t="n">
-        <v>14833800</v>
+        <v>13942800</v>
       </c>
       <c r="M12" t="n">
-        <v>488775</v>
+        <v>1117200</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>40800</v>
+        <v>25500</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>918459</v>
+        <v>104092020</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>1739880</v>
       </c>
       <c r="H13" t="n">
-        <v>12825000</v>
+        <v>17100000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,22 +4925,22 @@
         <v>322727.45</v>
       </c>
       <c r="L13" t="n">
-        <v>15562800</v>
+        <v>17517600</v>
       </c>
       <c r="M13" t="n">
-        <v>178500</v>
+        <v>1270500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1203773.4</v>
+        <v>136427652</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>1093500</v>
       </c>
       <c r="H14" t="n">
-        <v>4446000</v>
+        <v>4788000</v>
       </c>
       <c r="I14" t="n">
         <v>188785.73</v>
@@ -4978,10 +4978,10 @@
         <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>7133400</v>
+        <v>8494200</v>
       </c>
       <c r="M14" t="n">
-        <v>147000</v>
+        <v>1312500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>774457.2</v>
+        <v>87771816</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>382320</v>
       </c>
       <c r="H15" t="n">
-        <v>2907000</v>
+        <v>4446000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3423600</v>
+        <v>4509000</v>
       </c>
       <c r="M15" t="n">
-        <v>105000</v>
+        <v>1218000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>298663.2</v>
+        <v>33848496</v>
       </c>
     </row>
     <row r="16">
@@ -5072,7 +5072,7 @@
         <v>199260</v>
       </c>
       <c r="H16" t="n">
-        <v>1026000</v>
+        <v>1197000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1571400</v>
+        <v>2424600</v>
       </c>
       <c r="M16" t="n">
-        <v>94500</v>
+        <v>682500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>222798.6</v>
+        <v>25250508</v>
       </c>
     </row>
     <row r="17">
@@ -5125,7 +5125,7 @@
         <v>48600</v>
       </c>
       <c r="H17" t="n">
-        <v>171000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>561600</v>
+        <v>1215000</v>
       </c>
       <c r="M17" t="n">
-        <v>241500</v>
+        <v>640500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>85374</v>
+        <v>9675720</v>
       </c>
     </row>
     <row r="18">
@@ -5190,10 +5190,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>226800</v>
+        <v>448200</v>
       </c>
       <c r="M18" t="n">
-        <v>115500</v>
+        <v>252000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>38458.8</v>
+        <v>4358664</v>
       </c>
     </row>
     <row r="19">
@@ -5231,7 +5231,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -5243,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>567000</v>
+        <v>691200</v>
       </c>
       <c r="M19" t="n">
-        <v>808500</v>
+        <v>1123500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>17771.4</v>
+        <v>2014092</v>
       </c>
     </row>
     <row r="20">
@@ -5296,10 +5296,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>199800</v>
+        <v>545400</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>745500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8974.799999999999</v>
+        <v>1017144</v>
       </c>
     </row>
     <row r="21">
@@ -5337,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -5349,10 +5349,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5400</v>
+        <v>216000</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>136500</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -5364,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1652.4</v>
+        <v>187272</v>
       </c>
     </row>
     <row r="22">
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -5417,7 +5417,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>502.2</v>
+        <v>56916</v>
       </c>
     </row>
     <row r="23">
@@ -5455,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -5728,7 +5728,7 @@
         <v>50220</v>
       </c>
       <c r="H4" t="n">
-        <v>8910</v>
+        <v>9990</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>41</v>
       </c>
       <c r="L4" t="n">
-        <v>153600</v>
+        <v>171480</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>11340</v>
+        <v>9510</v>
       </c>
       <c r="O4" t="n">
-        <v>20550</v>
+        <v>22020</v>
       </c>
       <c r="P4" t="n">
-        <v>12900</v>
+        <v>9120</v>
       </c>
       <c r="Q4" t="n">
-        <v>29382.38</v>
+        <v>154644.12</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>22170</v>
       </c>
       <c r="H5" t="n">
-        <v>5760</v>
+        <v>6120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>18</v>
       </c>
       <c r="L5" t="n">
-        <v>63600</v>
+        <v>83820</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>15390</v>
+        <v>17280</v>
       </c>
       <c r="O5" t="n">
-        <v>10320</v>
+        <v>14550</v>
       </c>
       <c r="P5" t="n">
-        <v>10320</v>
+        <v>14280</v>
       </c>
       <c r="Q5" t="n">
-        <v>13675.96</v>
+        <v>71978.75999999999</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>3090</v>
       </c>
       <c r="H6" t="n">
-        <v>780</v>
+        <v>2550</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,22 +5846,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12750</v>
+        <v>18060</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1770</v>
+        <v>3360</v>
       </c>
       <c r="O6" t="n">
-        <v>480</v>
+        <v>1830</v>
       </c>
       <c r="P6" t="n">
-        <v>6090</v>
+        <v>9540</v>
       </c>
       <c r="Q6" t="n">
-        <v>1698.03</v>
+        <v>8937</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>840</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>3270</v>
+        <v>5370</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5820</v>
+        <v>8970</v>
       </c>
       <c r="Q7" t="n">
-        <v>136.87</v>
+        <v>720.36</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>480</v>
+        <v>1830</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>5070</v>
+        <v>9390</v>
       </c>
       <c r="Q8" t="n">
-        <v>56.43</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>210</v>
+        <v>1230</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4350</v>
+        <v>10260</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.03</v>
+        <v>131.76</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2250</v>
+        <v>5910</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.36</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2073.6</v>
+        <v>2203.2</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>5.96</v>
       </c>
       <c r="L5" t="n">
-        <v>13356</v>
+        <v>17602.2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>153.9</v>
+        <v>172.8</v>
       </c>
       <c r="O5" t="n">
-        <v>516</v>
+        <v>727.5</v>
       </c>
       <c r="P5" t="n">
-        <v>206.4</v>
+        <v>285.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>683.8</v>
+        <v>3598.94</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>154.5</v>
       </c>
       <c r="H6" t="n">
-        <v>444.6</v>
+        <v>1453.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,22 +7138,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>4717.5</v>
+        <v>6682.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>88.5</v>
+        <v>168</v>
       </c>
       <c r="O6" t="n">
-        <v>120</v>
+        <v>457.5</v>
       </c>
       <c r="P6" t="n">
-        <v>913.5</v>
+        <v>1431</v>
       </c>
       <c r="Q6" t="n">
-        <v>1273.52</v>
+        <v>6702.75</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>126</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>262.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0.64</v>
       </c>
       <c r="L7" t="n">
-        <v>1962</v>
+        <v>3222</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1455</v>
+        <v>2242.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>109.49</v>
+        <v>576.29</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>340.8</v>
+        <v>1299.3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1926.6</v>
+        <v>3568.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>53.61</v>
+        <v>282.15</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>170.1</v>
+        <v>996.3</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2175</v>
+        <v>5130</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.28</v>
+        <v>127.81</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>213.6</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1912.5</v>
+        <v>5023.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.36</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -7415,7 +7415,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>11819520</v>
+        <v>12558240</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>289296.65</v>
       </c>
       <c r="L5" t="n">
-        <v>2404080</v>
+        <v>3168396</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>26163</v>
+        <v>29376</v>
       </c>
       <c r="O5" t="n">
-        <v>87720</v>
+        <v>123675</v>
       </c>
       <c r="P5" t="n">
-        <v>13416</v>
+        <v>18564</v>
       </c>
       <c r="Q5" t="n">
-        <v>410278.93</v>
+        <v>2159362.8</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>8343</v>
       </c>
       <c r="H6" t="n">
-        <v>2534220</v>
+        <v>8284950</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,22 +8430,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>849150</v>
+        <v>1202796</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>15045</v>
+        <v>28560</v>
       </c>
       <c r="O6" t="n">
-        <v>20400</v>
+        <v>77775</v>
       </c>
       <c r="P6" t="n">
-        <v>59377.5</v>
+        <v>93015</v>
       </c>
       <c r="Q6" t="n">
-        <v>764113.5</v>
+        <v>4021650</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>6804</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1497960</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>30978.73</v>
       </c>
       <c r="L7" t="n">
-        <v>353160</v>
+        <v>579960</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>94575</v>
+        <v>145762.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>65696.83</v>
+        <v>345772.8</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>61344</v>
+        <v>233874</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>125229</v>
+        <v>231933</v>
       </c>
       <c r="Q8" t="n">
-        <v>32165.1</v>
+        <v>169290</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>30618</v>
+        <v>179334</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>141375</v>
+        <v>333450</v>
       </c>
       <c r="Q9" t="n">
-        <v>14570.02</v>
+        <v>76684.32000000001</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>38448</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>124312.5</v>
+        <v>326527.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>8618.4</v>
+        <v>45360</v>
       </c>
     </row>
     <row r="11">
@@ -8707,7 +8707,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1755</v>
+        <v>7020</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -9604,7 +9604,7 @@
         <v>91710</v>
       </c>
       <c r="H4" t="n">
-        <v>6210</v>
+        <v>7170</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>150330</v>
+        <v>170070</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>22410</v>
+        <v>23220</v>
       </c>
       <c r="O4" t="n">
-        <v>32940</v>
+        <v>33630</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>35195.83</v>
+        <v>190985.13</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>28710</v>
       </c>
       <c r="H5" t="n">
-        <v>4020</v>
+        <v>4290</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>13</v>
       </c>
       <c r="L5" t="n">
-        <v>54300</v>
+        <v>63780</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>9810</v>
+        <v>12000</v>
       </c>
       <c r="O5" t="n">
-        <v>29790</v>
+        <v>30150</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>11291.77</v>
+        <v>61273.17</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>9540</v>
       </c>
       <c r="H6" t="n">
-        <v>1530</v>
+        <v>2160</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>16920</v>
+        <v>24180</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>4860</v>
+        <v>5460</v>
       </c>
       <c r="O6" t="n">
-        <v>25170</v>
+        <v>25530</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2149.71</v>
+        <v>11665.08</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>3030</v>
       </c>
       <c r="H7" t="n">
-        <v>240</v>
+        <v>570</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>4590</v>
+        <v>9210</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2430</v>
+        <v>3660</v>
       </c>
       <c r="O7" t="n">
-        <v>13650</v>
+        <v>17190</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>366.18</v>
+        <v>1987.02</v>
       </c>
     </row>
     <row r="8">
@@ -9816,7 +9816,7 @@
         <v>990</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -9828,22 +9828,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2520</v>
+        <v>4680</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>330</v>
+        <v>1440</v>
       </c>
       <c r="O8" t="n">
-        <v>3480</v>
+        <v>6360</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>138.39</v>
+        <v>750.96</v>
       </c>
     </row>
     <row r="9">
@@ -9881,22 +9881,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="O9" t="n">
-        <v>570</v>
+        <v>1110</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1447.2</v>
+        <v>1544.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>4.3</v>
       </c>
       <c r="L5" t="n">
-        <v>11403</v>
+        <v>13393.8</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>98.09999999999999</v>
+        <v>120</v>
       </c>
       <c r="O5" t="n">
-        <v>1489.5</v>
+        <v>1507.5</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>564.59</v>
+        <v>3063.66</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>477</v>
       </c>
       <c r="H6" t="n">
-        <v>872.1</v>
+        <v>1231.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>6260.4</v>
+        <v>8946.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="O6" t="n">
-        <v>6292.5</v>
+        <v>6382.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1612.28</v>
+        <v>8748.809999999999</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>454.5</v>
       </c>
       <c r="H7" t="n">
-        <v>175.2</v>
+        <v>416.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2754</v>
+        <v>5526</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>170.1</v>
+        <v>256.2</v>
       </c>
       <c r="O7" t="n">
-        <v>4777.5</v>
+        <v>6016.5</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>292.94</v>
+        <v>1589.62</v>
       </c>
     </row>
     <row r="8">
@@ -11108,7 +11108,7 @@
         <v>643.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -11120,22 +11120,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1789.2</v>
+        <v>3322.8</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>66</v>
+        <v>288</v>
       </c>
       <c r="O8" t="n">
-        <v>1566</v>
+        <v>2862</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>131.47</v>
+        <v>713.41</v>
       </c>
     </row>
     <row r="9">
@@ -11173,22 +11173,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>24.3</v>
+        <v>194.4</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O9" t="n">
-        <v>313.5</v>
+        <v>610.5</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>11.26</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8249040</v>
+        <v>8803080</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>208936.47</v>
       </c>
       <c r="L5" t="n">
-        <v>2052540</v>
+        <v>2410884</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>16677</v>
+        <v>20400</v>
       </c>
       <c r="O5" t="n">
-        <v>253215</v>
+        <v>256275</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>338753.1</v>
+        <v>1838195.1</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>25758</v>
       </c>
       <c r="H6" t="n">
-        <v>4970970</v>
+        <v>7017840</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1126872</v>
+        <v>1610388</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>41310</v>
+        <v>46410</v>
       </c>
       <c r="O6" t="n">
-        <v>1069725</v>
+        <v>1085025</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>967368.42</v>
+        <v>5249286</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>24543</v>
       </c>
       <c r="H7" t="n">
-        <v>998640</v>
+        <v>2371770</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>495720</v>
+        <v>994680</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>28917</v>
+        <v>43554</v>
       </c>
       <c r="O7" t="n">
-        <v>812175</v>
+        <v>1022805</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>175766.11</v>
+        <v>953769.6</v>
       </c>
     </row>
     <row r="8">
@@ -12400,7 +12400,7 @@
         <v>34749</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>436050</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -12412,22 +12412,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>322056</v>
+        <v>598104</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>11220</v>
+        <v>48960</v>
       </c>
       <c r="O8" t="n">
-        <v>266220</v>
+        <v>486540</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>78882.98</v>
+        <v>428047.2</v>
       </c>
     </row>
     <row r="9">
@@ -12465,22 +12465,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4374</v>
+        <v>34992</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6120</v>
       </c>
       <c r="O9" t="n">
-        <v>53295</v>
+        <v>103785</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>6757.02</v>
+        <v>36666</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>84240</v>
       </c>
       <c r="H4" t="n">
-        <v>7470</v>
+        <v>8130</v>
       </c>
       <c r="I4" t="n">
         <v>6</v>
@@ -13492,19 +13492,19 @@
         <v>132</v>
       </c>
       <c r="L4" t="n">
-        <v>177330</v>
+        <v>183120</v>
       </c>
       <c r="M4" t="n">
-        <v>9960</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>33030</v>
+        <v>36300</v>
       </c>
       <c r="P4" t="n">
-        <v>16800</v>
+        <v>2730</v>
       </c>
       <c r="Q4" t="n">
         <v>35065.5</v>
@@ -13533,7 +13533,7 @@
         <v>68430</v>
       </c>
       <c r="H5" t="n">
-        <v>5100</v>
+        <v>5760</v>
       </c>
       <c r="I5" t="n">
         <v>5</v>
@@ -13545,19 +13545,19 @@
         <v>94</v>
       </c>
       <c r="L5" t="n">
-        <v>151260</v>
+        <v>148710</v>
       </c>
       <c r="M5" t="n">
-        <v>17640</v>
+        <v>990</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>31410</v>
+        <v>37260</v>
       </c>
       <c r="P5" t="n">
-        <v>25500</v>
+        <v>9450</v>
       </c>
       <c r="Q5" t="n">
         <v>30169.94</v>
@@ -13586,7 +13586,7 @@
         <v>62100</v>
       </c>
       <c r="H6" t="n">
-        <v>7530</v>
+        <v>7140</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -13598,19 +13598,19 @@
         <v>61</v>
       </c>
       <c r="L6" t="n">
-        <v>146580</v>
+        <v>126210</v>
       </c>
       <c r="M6" t="n">
-        <v>14910</v>
+        <v>1440</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>22260</v>
+        <v>24090</v>
       </c>
       <c r="P6" t="n">
-        <v>29370</v>
+        <v>16020</v>
       </c>
       <c r="Q6" t="n">
         <v>27173.6</v>
@@ -13639,7 +13639,7 @@
         <v>81090</v>
       </c>
       <c r="H7" t="n">
-        <v>12360</v>
+        <v>12660</v>
       </c>
       <c r="I7" t="n">
         <v>2</v>
@@ -13651,19 +13651,19 @@
         <v>87</v>
       </c>
       <c r="L7" t="n">
-        <v>188550</v>
+        <v>168660</v>
       </c>
       <c r="M7" t="n">
-        <v>10350</v>
+        <v>3930</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>17670</v>
+        <v>16530</v>
       </c>
       <c r="P7" t="n">
-        <v>33600</v>
+        <v>22620</v>
       </c>
       <c r="Q7" t="n">
         <v>38516.51</v>
@@ -13692,7 +13692,7 @@
         <v>72900</v>
       </c>
       <c r="H8" t="n">
-        <v>4260</v>
+        <v>4650</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -13704,19 +13704,19 @@
         <v>49</v>
       </c>
       <c r="L8" t="n">
-        <v>160500</v>
+        <v>152610</v>
       </c>
       <c r="M8" t="n">
-        <v>7200</v>
+        <v>5490</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>18390</v>
+        <v>19080</v>
       </c>
       <c r="P8" t="n">
-        <v>34080</v>
+        <v>27930</v>
       </c>
       <c r="Q8" t="n">
         <v>37958.28</v>
@@ -13745,7 +13745,7 @@
         <v>35850</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>720</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -13757,19 +13757,19 @@
         <v>32</v>
       </c>
       <c r="L9" t="n">
-        <v>90810</v>
+        <v>99660</v>
       </c>
       <c r="M9" t="n">
-        <v>3900</v>
+        <v>12960</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>23430</v>
+        <v>21750</v>
       </c>
       <c r="P9" t="n">
-        <v>33030</v>
+        <v>29850</v>
       </c>
       <c r="Q9" t="n">
         <v>30795.91</v>
@@ -13798,7 +13798,7 @@
         <v>32640</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -13810,19 +13810,19 @@
         <v>17</v>
       </c>
       <c r="L10" t="n">
-        <v>46980</v>
+        <v>52380</v>
       </c>
       <c r="M10" t="n">
-        <v>2250</v>
+        <v>9570</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>19230</v>
+        <v>23670</v>
       </c>
       <c r="P10" t="n">
-        <v>35370</v>
+        <v>38820</v>
       </c>
       <c r="Q10" t="n">
         <v>22143.23</v>
@@ -13863,19 +13863,19 @@
         <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>14760</v>
+        <v>26310</v>
       </c>
       <c r="M11" t="n">
-        <v>1080</v>
+        <v>9930</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2580</v>
+        <v>4950</v>
       </c>
       <c r="P11" t="n">
-        <v>32970</v>
+        <v>36510</v>
       </c>
       <c r="Q11" t="n">
         <v>4109.67</v>
@@ -13904,7 +13904,7 @@
         <v>1650</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,19 +13916,19 @@
         <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>6360</v>
+        <v>34920</v>
       </c>
       <c r="M12" t="n">
-        <v>450</v>
+        <v>10800</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P12" t="n">
-        <v>33330</v>
+        <v>47190</v>
       </c>
       <c r="Q12" t="n">
         <v>651.3</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3660</v>
+        <v>22200</v>
       </c>
       <c r="M13" t="n">
-        <v>330</v>
+        <v>5430</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>25470</v>
+        <v>42840</v>
       </c>
       <c r="Q13" t="n">
         <v>235.25</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1350</v>
+        <v>9840</v>
       </c>
       <c r="M14" t="n">
-        <v>330</v>
+        <v>10230</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>16290</v>
+        <v>32070</v>
       </c>
       <c r="Q14" t="n">
         <v>197.09</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>930</v>
+        <v>3600</v>
       </c>
       <c r="M15" t="n">
-        <v>180</v>
+        <v>1290</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10980</v>
+        <v>9900</v>
       </c>
       <c r="Q15" t="n">
         <v>20.42</v>
@@ -14128,10 +14128,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>330</v>
+        <v>5220</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>11640</v>
+        <v>17130</v>
       </c>
       <c r="Q16" t="n">
         <v>19.2</v>
@@ -14181,10 +14181,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>3510</v>
       </c>
       <c r="M17" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>12270</v>
+        <v>24900</v>
       </c>
       <c r="Q17" t="n">
         <v>16.41</v>
@@ -14234,10 +14234,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>480</v>
+        <v>3690</v>
       </c>
       <c r="M18" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -14246,7 +14246,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>4620</v>
+        <v>13320</v>
       </c>
       <c r="Q18" t="n">
         <v>7.37</v>
@@ -14287,10 +14287,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>630</v>
+        <v>1650</v>
       </c>
       <c r="M19" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -14299,7 +14299,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1860</v>
+        <v>3630</v>
       </c>
       <c r="Q19" t="n">
         <v>4.46</v>
@@ -14340,7 +14340,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -14352,7 +14352,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Q20" t="n">
         <v>0.5600000000000001</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>19202.4</v>
+        <v>20779.2</v>
       </c>
       <c r="I5" t="n">
         <v>2.32</v>
@@ -14837,22 +14837,22 @@
         <v>88.05</v>
       </c>
       <c r="L5" t="n">
-        <v>192824.1</v>
+        <v>206841.6</v>
       </c>
       <c r="M5" t="n">
-        <v>1048.2</v>
+        <v>846</v>
       </c>
       <c r="N5" t="n">
-        <v>799.2</v>
+        <v>897.3</v>
       </c>
       <c r="O5" t="n">
-        <v>9342</v>
+        <v>10681.5</v>
       </c>
       <c r="P5" t="n">
-        <v>997.8</v>
+        <v>684.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>7226.2</v>
+        <v>74884.42</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>11811</v>
       </c>
       <c r="H6" t="n">
-        <v>25000.2</v>
+        <v>26436.6</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -14890,22 +14890,22 @@
         <v>75.54000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>212309.7</v>
+        <v>211521.6</v>
       </c>
       <c r="M6" t="n">
-        <v>2836.8</v>
+        <v>1903.2</v>
       </c>
       <c r="N6" t="n">
-        <v>1675.5</v>
+        <v>2278.5</v>
       </c>
       <c r="O6" t="n">
-        <v>29332.5</v>
+        <v>31372.5</v>
       </c>
       <c r="P6" t="n">
-        <v>7398</v>
+        <v>5508</v>
       </c>
       <c r="Q6" t="n">
-        <v>71842.81</v>
+        <v>744500.0600000001</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>30906</v>
       </c>
       <c r="H7" t="n">
-        <v>34908.6</v>
+        <v>36616.8</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -14943,22 +14943,22 @@
         <v>115.48</v>
       </c>
       <c r="L7" t="n">
-        <v>320022</v>
+        <v>318078</v>
       </c>
       <c r="M7" t="n">
-        <v>8746.5</v>
+        <v>8631</v>
       </c>
       <c r="N7" t="n">
-        <v>865.2</v>
+        <v>1207.5</v>
       </c>
       <c r="O7" t="n">
-        <v>29830.5</v>
+        <v>31972.5</v>
       </c>
       <c r="P7" t="n">
-        <v>15052.5</v>
+        <v>10995</v>
       </c>
       <c r="Q7" t="n">
-        <v>72124.03999999999</v>
+        <v>747414.49</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>121641</v>
       </c>
       <c r="H8" t="n">
-        <v>25525.5</v>
+        <v>24837</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -14996,22 +14996,22 @@
         <v>78.02</v>
       </c>
       <c r="L8" t="n">
-        <v>330426.9</v>
+        <v>324079.5</v>
       </c>
       <c r="M8" t="n">
-        <v>11368.5</v>
+        <v>14355</v>
       </c>
       <c r="N8" t="n">
-        <v>624</v>
+        <v>1164</v>
       </c>
       <c r="O8" t="n">
-        <v>27162</v>
+        <v>30982.5</v>
       </c>
       <c r="P8" t="n">
-        <v>25125.6</v>
+        <v>19038</v>
       </c>
       <c r="Q8" t="n">
-        <v>79474.5</v>
+        <v>823586.5600000001</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>129846</v>
       </c>
       <c r="H9" t="n">
-        <v>13500</v>
+        <v>16620</v>
       </c>
       <c r="I9" t="n">
         <v>1.61</v>
@@ -15049,22 +15049,22 @@
         <v>85.12</v>
       </c>
       <c r="L9" t="n">
-        <v>321683.4</v>
+        <v>334052.1</v>
       </c>
       <c r="M9" t="n">
-        <v>8652</v>
+        <v>23478</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="O9" t="n">
-        <v>31317</v>
+        <v>34006.5</v>
       </c>
       <c r="P9" t="n">
-        <v>33600</v>
+        <v>28995</v>
       </c>
       <c r="Q9" t="n">
-        <v>72460.64</v>
+        <v>750902.61</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>164040</v>
       </c>
       <c r="H10" t="n">
-        <v>3960</v>
+        <v>4530</v>
       </c>
       <c r="I10" t="n">
         <v>0.87</v>
@@ -15102,22 +15102,22 @@
         <v>70.47</v>
       </c>
       <c r="L10" t="n">
-        <v>293913.6</v>
+        <v>315140.1</v>
       </c>
       <c r="M10" t="n">
-        <v>8568</v>
+        <v>20680.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>30198</v>
+        <v>38493</v>
       </c>
       <c r="P10" t="n">
-        <v>63393</v>
+        <v>61914</v>
       </c>
       <c r="Q10" t="n">
-        <v>68964.11</v>
+        <v>714668.4300000001</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>88350</v>
       </c>
       <c r="H11" t="n">
-        <v>4140</v>
+        <v>4350</v>
       </c>
       <c r="I11" t="n">
         <v>1.8</v>
@@ -15155,22 +15155,22 @@
         <v>38.64</v>
       </c>
       <c r="L11" t="n">
-        <v>209970</v>
+        <v>247860</v>
       </c>
       <c r="M11" t="n">
-        <v>6075</v>
+        <v>22437</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>13668</v>
+        <v>24250.5</v>
       </c>
       <c r="P11" t="n">
-        <v>66501</v>
+        <v>77598</v>
       </c>
       <c r="Q11" t="n">
-        <v>45318.53</v>
+        <v>469631.52</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>65160</v>
       </c>
       <c r="H12" t="n">
-        <v>5790</v>
+        <v>5880</v>
       </c>
       <c r="I12" t="n">
         <v>0.93</v>
@@ -15208,22 +15208,22 @@
         <v>16.69</v>
       </c>
       <c r="L12" t="n">
-        <v>157080</v>
+        <v>201240</v>
       </c>
       <c r="M12" t="n">
-        <v>4417.5</v>
+        <v>21717</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6540</v>
+        <v>16650</v>
       </c>
       <c r="P12" t="n">
-        <v>65400</v>
+        <v>101520</v>
       </c>
       <c r="Q12" t="n">
-        <v>30294.82</v>
+        <v>313942.33</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>53250</v>
       </c>
       <c r="H13" t="n">
-        <v>2250</v>
+        <v>3060</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,22 +15261,22 @@
         <v>8.550000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>124080</v>
+        <v>163950</v>
       </c>
       <c r="M13" t="n">
-        <v>3240</v>
+        <v>16410</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2610</v>
+        <v>3930</v>
       </c>
       <c r="P13" t="n">
-        <v>45450</v>
+        <v>75180</v>
       </c>
       <c r="Q13" t="n">
-        <v>21759.54</v>
+        <v>225492.06</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>30330</v>
       </c>
       <c r="H14" t="n">
-        <v>780</v>
+        <v>840</v>
       </c>
       <c r="I14" t="n">
         <v>0.97</v>
@@ -15314,22 +15314,22 @@
         <v>0.97</v>
       </c>
       <c r="L14" t="n">
-        <v>50910</v>
+        <v>74190</v>
       </c>
       <c r="M14" t="n">
-        <v>2100</v>
+        <v>19830</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1680</v>
+        <v>2340</v>
       </c>
       <c r="P14" t="n">
-        <v>31680</v>
+        <v>48210</v>
       </c>
       <c r="Q14" t="n">
-        <v>11836.3</v>
+        <v>122658.39</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>9810</v>
       </c>
       <c r="H15" t="n">
-        <v>510</v>
+        <v>780</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,22 +15367,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>25170</v>
+        <v>38460</v>
       </c>
       <c r="M15" t="n">
-        <v>1050</v>
+        <v>7020</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2880</v>
+        <v>3090</v>
       </c>
       <c r="P15" t="n">
-        <v>26490</v>
+        <v>26550</v>
       </c>
       <c r="Q15" t="n">
-        <v>4226.07</v>
+        <v>43794.34</v>
       </c>
     </row>
     <row r="16">
@@ -15408,7 +15408,7 @@
         <v>4410</v>
       </c>
       <c r="H16" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -15420,22 +15420,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10110</v>
+        <v>26070</v>
       </c>
       <c r="M16" t="n">
-        <v>360</v>
+        <v>3510</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="P16" t="n">
-        <v>36840</v>
+        <v>45810</v>
       </c>
       <c r="Q16" t="n">
-        <v>2649.61</v>
+        <v>27457.62</v>
       </c>
     </row>
     <row r="17">
@@ -15461,7 +15461,7 @@
         <v>1860</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15473,22 +15473,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>3810</v>
+        <v>12960</v>
       </c>
       <c r="M17" t="n">
-        <v>780</v>
+        <v>2850</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P17" t="n">
-        <v>27090</v>
+        <v>44070</v>
       </c>
       <c r="Q17" t="n">
-        <v>1404.71</v>
+        <v>14556.87</v>
       </c>
     </row>
     <row r="18">
@@ -15526,10 +15526,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>1860</v>
+        <v>7800</v>
       </c>
       <c r="M18" t="n">
-        <v>1110</v>
+        <v>1890</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -15538,10 +15538,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>20490</v>
+        <v>30000</v>
       </c>
       <c r="Q18" t="n">
-        <v>669.8200000000001</v>
+        <v>6941.31</v>
       </c>
     </row>
     <row r="19">
@@ -15567,7 +15567,7 @@
         <v>330</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -15579,22 +15579,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>4020</v>
+        <v>7200</v>
       </c>
       <c r="M19" t="n">
-        <v>2490</v>
+        <v>3420</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P19" t="n">
-        <v>19950</v>
+        <v>29730</v>
       </c>
       <c r="Q19" t="n">
-        <v>300.99</v>
+        <v>3119.08</v>
       </c>
     </row>
     <row r="20">
@@ -15632,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>1110</v>
+        <v>3390</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>2160</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -15644,10 +15644,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>7860</v>
+        <v>18420</v>
       </c>
       <c r="Q20" t="n">
-        <v>152.56</v>
+        <v>1580.94</v>
       </c>
     </row>
     <row r="21">
@@ -15673,7 +15673,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -15685,10 +15685,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>1200</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -15697,10 +15697,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>22.65</v>
+        <v>234.77</v>
       </c>
     </row>
     <row r="22">
@@ -15738,10 +15738,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -15753,7 +15753,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.02</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="23">
@@ -15791,10 +15791,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M23" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -15806,7 +15806,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.15</v>
+        <v>84.42</v>
       </c>
     </row>
     <row r="24">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1836</v>
+        <v>2073.6</v>
       </c>
       <c r="I5" t="n">
         <v>1.66</v>
@@ -16129,19 +16129,19 @@
         <v>31.11</v>
       </c>
       <c r="L5" t="n">
-        <v>31764.6</v>
+        <v>31229.1</v>
       </c>
       <c r="M5" t="n">
-        <v>352.8</v>
+        <v>19.8</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>1570.5</v>
+        <v>1863</v>
       </c>
       <c r="P5" t="n">
-        <v>510</v>
+        <v>189</v>
       </c>
       <c r="Q5" t="n">
         <v>1508.5</v>
@@ -16170,7 +16170,7 @@
         <v>3105</v>
       </c>
       <c r="H6" t="n">
-        <v>4292.1</v>
+        <v>4069.8</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -16182,19 +16182,19 @@
         <v>30.93</v>
       </c>
       <c r="L6" t="n">
-        <v>54234.6</v>
+        <v>46697.7</v>
       </c>
       <c r="M6" t="n">
-        <v>1192.8</v>
+        <v>115.2</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5565</v>
+        <v>6022.5</v>
       </c>
       <c r="P6" t="n">
-        <v>4405.5</v>
+        <v>2403</v>
       </c>
       <c r="Q6" t="n">
         <v>20380.2</v>
@@ -16223,7 +16223,7 @@
         <v>12163.5</v>
       </c>
       <c r="H7" t="n">
-        <v>9022.799999999999</v>
+        <v>9241.799999999999</v>
       </c>
       <c r="I7" t="n">
         <v>1.28</v>
@@ -16235,19 +16235,19 @@
         <v>55.51</v>
       </c>
       <c r="L7" t="n">
-        <v>113130</v>
+        <v>101196</v>
       </c>
       <c r="M7" t="n">
-        <v>3622.5</v>
+        <v>1375.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>6184.5</v>
+        <v>5785.5</v>
       </c>
       <c r="P7" t="n">
-        <v>8400</v>
+        <v>5655</v>
       </c>
       <c r="Q7" t="n">
         <v>30813.21</v>
@@ -16276,7 +16276,7 @@
         <v>47385</v>
       </c>
       <c r="H8" t="n">
-        <v>3621</v>
+        <v>3952.5</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -16288,19 +16288,19 @@
         <v>36.06</v>
       </c>
       <c r="L8" t="n">
-        <v>113955</v>
+        <v>108353.1</v>
       </c>
       <c r="M8" t="n">
-        <v>3960</v>
+        <v>3019.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8275.5</v>
+        <v>8586</v>
       </c>
       <c r="P8" t="n">
-        <v>12950.4</v>
+        <v>10613.4</v>
       </c>
       <c r="Q8" t="n">
         <v>36060.37</v>
@@ -16329,7 +16329,7 @@
         <v>30472.5</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>720</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -16341,19 +16341,19 @@
         <v>25.7</v>
       </c>
       <c r="L9" t="n">
-        <v>73556.10000000001</v>
+        <v>80724.60000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>2730</v>
+        <v>9072</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>12886.5</v>
+        <v>11962.5</v>
       </c>
       <c r="P9" t="n">
-        <v>16515</v>
+        <v>14925</v>
       </c>
       <c r="Q9" t="n">
         <v>29872.03</v>
@@ -16382,7 +16382,7 @@
         <v>32640</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16394,19 +16394,19 @@
         <v>14.79</v>
       </c>
       <c r="L10" t="n">
-        <v>41812.2</v>
+        <v>46618.2</v>
       </c>
       <c r="M10" t="n">
-        <v>1912.5</v>
+        <v>8134.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>13461</v>
+        <v>16569</v>
       </c>
       <c r="P10" t="n">
-        <v>30064.5</v>
+        <v>32997</v>
       </c>
       <c r="Q10" t="n">
         <v>22143.23</v>
@@ -16447,19 +16447,19 @@
         <v>1.8</v>
       </c>
       <c r="L11" t="n">
-        <v>14760</v>
+        <v>26310</v>
       </c>
       <c r="M11" t="n">
-        <v>972</v>
+        <v>8937</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2193</v>
+        <v>4207.5</v>
       </c>
       <c r="P11" t="n">
-        <v>29673</v>
+        <v>32859</v>
       </c>
       <c r="Q11" t="n">
         <v>4109.67</v>
@@ -16488,7 +16488,7 @@
         <v>1650</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,19 +16500,19 @@
         <v>2.78</v>
       </c>
       <c r="L12" t="n">
-        <v>6360</v>
+        <v>34920</v>
       </c>
       <c r="M12" t="n">
-        <v>427.5</v>
+        <v>10260</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P12" t="n">
-        <v>33330</v>
+        <v>47190</v>
       </c>
       <c r="Q12" t="n">
         <v>651.3</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3660</v>
+        <v>22200</v>
       </c>
       <c r="M13" t="n">
-        <v>330</v>
+        <v>5430</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>25470</v>
+        <v>42840</v>
       </c>
       <c r="Q13" t="n">
         <v>235.25</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1350</v>
+        <v>9840</v>
       </c>
       <c r="M14" t="n">
-        <v>330</v>
+        <v>10230</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>16290</v>
+        <v>32070</v>
       </c>
       <c r="Q14" t="n">
         <v>197.09</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>930</v>
+        <v>3600</v>
       </c>
       <c r="M15" t="n">
-        <v>180</v>
+        <v>1290</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>10980</v>
+        <v>9900</v>
       </c>
       <c r="Q15" t="n">
         <v>20.42</v>
@@ -16712,10 +16712,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>330</v>
+        <v>5220</v>
       </c>
       <c r="M16" t="n">
-        <v>30</v>
+        <v>720</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>11640</v>
+        <v>17130</v>
       </c>
       <c r="Q16" t="n">
         <v>19.2</v>
@@ -16765,10 +16765,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>300</v>
+        <v>3510</v>
       </c>
       <c r="M17" t="n">
-        <v>30</v>
+        <v>240</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>12270</v>
+        <v>24900</v>
       </c>
       <c r="Q17" t="n">
         <v>16.41</v>
@@ -16818,10 +16818,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>480</v>
+        <v>3690</v>
       </c>
       <c r="M18" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -16830,7 +16830,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>4620</v>
+        <v>13320</v>
       </c>
       <c r="Q18" t="n">
         <v>7.37</v>
@@ -16871,10 +16871,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>630</v>
+        <v>1650</v>
       </c>
       <c r="M19" t="n">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -16883,7 +16883,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1860</v>
+        <v>3630</v>
       </c>
       <c r="Q19" t="n">
         <v>4.46</v>
@@ -16924,7 +16924,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -16936,7 +16936,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="Q20" t="n">
         <v>0.5600000000000001</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>10465200</v>
+        <v>11819520</v>
       </c>
       <c r="I5" t="n">
         <v>321440.72</v>
@@ -17421,19 +17421,19 @@
         <v>1510771.38</v>
       </c>
       <c r="L5" t="n">
-        <v>5717628</v>
+        <v>5621238</v>
       </c>
       <c r="M5" t="n">
-        <v>123480</v>
+        <v>6930</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>266985</v>
+        <v>316710</v>
       </c>
       <c r="P5" t="n">
-        <v>33150</v>
+        <v>12285</v>
       </c>
       <c r="Q5" t="n">
         <v>905098.3199999999</v>
@@ -17462,7 +17462,7 @@
         <v>167670</v>
       </c>
       <c r="H6" t="n">
-        <v>24464970</v>
+        <v>23197860</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -17474,19 +17474,19 @@
         <v>1501691.41</v>
       </c>
       <c r="L6" t="n">
-        <v>9762228</v>
+        <v>8405586</v>
       </c>
       <c r="M6" t="n">
-        <v>417480</v>
+        <v>40320</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>946050</v>
+        <v>1023825</v>
       </c>
       <c r="P6" t="n">
-        <v>286357.5</v>
+        <v>156195</v>
       </c>
       <c r="Q6" t="n">
         <v>12228118.02</v>
@@ -17515,7 +17515,7 @@
         <v>656829</v>
       </c>
       <c r="H7" t="n">
-        <v>51429960</v>
+        <v>52678260</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -17527,19 +17527,19 @@
         <v>2695149.34</v>
       </c>
       <c r="L7" t="n">
-        <v>20363400</v>
+        <v>18215280</v>
       </c>
       <c r="M7" t="n">
-        <v>1267875</v>
+        <v>481425</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1051365</v>
+        <v>983535</v>
       </c>
       <c r="P7" t="n">
-        <v>546000</v>
+        <v>367575</v>
       </c>
       <c r="Q7" t="n">
         <v>18487923.84</v>
@@ -17568,7 +17568,7 @@
         <v>2558790</v>
       </c>
       <c r="H8" t="n">
-        <v>20639700</v>
+        <v>22529250</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -17580,19 +17580,19 @@
         <v>1751123.58</v>
       </c>
       <c r="L8" t="n">
-        <v>20511900</v>
+        <v>19503558</v>
       </c>
       <c r="M8" t="n">
-        <v>1386000</v>
+        <v>1056825</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1406835</v>
+        <v>1459620</v>
       </c>
       <c r="P8" t="n">
-        <v>841776</v>
+        <v>689871</v>
       </c>
       <c r="Q8" t="n">
         <v>21636222.34</v>
@@ -17621,7 +17621,7 @@
         <v>1645515</v>
       </c>
       <c r="H9" t="n">
-        <v>2907000</v>
+        <v>4104000</v>
       </c>
       <c r="I9" t="n">
         <v>155961.87</v>
@@ -17633,19 +17633,19 @@
         <v>1247694.98</v>
       </c>
       <c r="L9" t="n">
-        <v>13240098</v>
+        <v>14530428</v>
       </c>
       <c r="M9" t="n">
-        <v>955500</v>
+        <v>3175200</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2190705</v>
+        <v>2033625</v>
       </c>
       <c r="P9" t="n">
-        <v>1073475</v>
+        <v>970125</v>
       </c>
       <c r="Q9" t="n">
         <v>17923218.69</v>
@@ -17674,7 +17674,7 @@
         <v>1762560</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -17686,19 +17686,19 @@
         <v>718143.24</v>
       </c>
       <c r="L10" t="n">
-        <v>7526196</v>
+        <v>8391276</v>
       </c>
       <c r="M10" t="n">
-        <v>669375</v>
+        <v>2847075</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2288370</v>
+        <v>2816730</v>
       </c>
       <c r="P10" t="n">
-        <v>1954192.5</v>
+        <v>2144805</v>
       </c>
       <c r="Q10" t="n">
         <v>13285935.36</v>
@@ -17739,19 +17739,19 @@
         <v>87255.13</v>
       </c>
       <c r="L11" t="n">
-        <v>2656800</v>
+        <v>4735800</v>
       </c>
       <c r="M11" t="n">
-        <v>340200</v>
+        <v>3127950</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>372810</v>
+        <v>715275</v>
       </c>
       <c r="P11" t="n">
-        <v>1928745</v>
+        <v>2135835</v>
       </c>
       <c r="Q11" t="n">
         <v>2465802</v>
@@ -17780,7 +17780,7 @@
         <v>89100</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,19 +17792,19 @@
         <v>135034.24</v>
       </c>
       <c r="L12" t="n">
-        <v>1144800</v>
+        <v>6285600</v>
       </c>
       <c r="M12" t="n">
-        <v>149625</v>
+        <v>3591000</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="P12" t="n">
-        <v>2166450</v>
+        <v>3067350</v>
       </c>
       <c r="Q12" t="n">
         <v>390778.56</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>658800</v>
+        <v>3996000</v>
       </c>
       <c r="M13" t="n">
-        <v>115500</v>
+        <v>1900500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1655550</v>
+        <v>2784600</v>
       </c>
       <c r="Q13" t="n">
         <v>141151.68</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>243000</v>
+        <v>1771200</v>
       </c>
       <c r="M14" t="n">
-        <v>115500</v>
+        <v>3580500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1058850</v>
+        <v>2084550</v>
       </c>
       <c r="Q14" t="n">
         <v>118251.36</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>167400</v>
+        <v>648000</v>
       </c>
       <c r="M15" t="n">
-        <v>63000</v>
+        <v>451500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>713700</v>
+        <v>643500</v>
       </c>
       <c r="Q15" t="n">
         <v>12253.68</v>
@@ -18004,10 +18004,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>59400</v>
+        <v>939600</v>
       </c>
       <c r="M16" t="n">
-        <v>10500</v>
+        <v>252000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>756600</v>
+        <v>1113450</v>
       </c>
       <c r="Q16" t="n">
         <v>11517.12</v>
@@ -18057,10 +18057,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>54000</v>
+        <v>631800</v>
       </c>
       <c r="M17" t="n">
-        <v>10500</v>
+        <v>84000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>797550</v>
+        <v>1618500</v>
       </c>
       <c r="Q17" t="n">
         <v>9843.120000000001</v>
@@ -18110,10 +18110,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>86400</v>
+        <v>664200</v>
       </c>
       <c r="M18" t="n">
-        <v>73500</v>
+        <v>94500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -18122,7 +18122,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>300300</v>
+        <v>865800</v>
       </c>
       <c r="Q18" t="n">
         <v>4419.36</v>
@@ -18163,10 +18163,10 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>113400</v>
+        <v>297000</v>
       </c>
       <c r="M19" t="n">
-        <v>31500</v>
+        <v>52500</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -18175,7 +18175,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>120900</v>
+        <v>235950</v>
       </c>
       <c r="Q19" t="n">
         <v>2678.4</v>
@@ -18216,7 +18216,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>43200</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -18228,7 +18228,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>3900</v>
+        <v>7800</v>
       </c>
       <c r="Q20" t="n">
         <v>334.8</v>
@@ -18648,7 +18648,7 @@
         <v>117270</v>
       </c>
       <c r="H4" t="n">
-        <v>14880</v>
+        <v>16440</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>50</v>
       </c>
       <c r="L4" t="n">
-        <v>375150</v>
+        <v>414720</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>16380</v>
+        <v>13380</v>
       </c>
       <c r="O4" t="n">
-        <v>54660</v>
+        <v>52920</v>
       </c>
       <c r="P4" t="n">
-        <v>7740</v>
+        <v>2520</v>
       </c>
       <c r="Q4" t="n">
-        <v>37057.56</v>
+        <v>424617.93</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>35520</v>
       </c>
       <c r="H5" t="n">
-        <v>3180</v>
+        <v>5790</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>17</v>
       </c>
       <c r="L5" t="n">
-        <v>126090</v>
+        <v>156810</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>25830</v>
+        <v>29250</v>
       </c>
       <c r="O5" t="n">
-        <v>36750</v>
+        <v>50400</v>
       </c>
       <c r="P5" t="n">
-        <v>6510</v>
+        <v>8310</v>
       </c>
       <c r="Q5" t="n">
-        <v>13085.11</v>
+        <v>149933.52</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>4980</v>
       </c>
       <c r="H6" t="n">
-        <v>390</v>
+        <v>540</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>21360</v>
+        <v>32880</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>7320</v>
+        <v>12450</v>
       </c>
       <c r="O6" t="n">
-        <v>7620</v>
+        <v>10380</v>
       </c>
       <c r="P6" t="n">
-        <v>4140</v>
+        <v>7980</v>
       </c>
       <c r="Q6" t="n">
-        <v>1299.54</v>
+        <v>14890.59</v>
       </c>
     </row>
     <row r="7">
@@ -18819,22 +18819,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3720</v>
+        <v>9030</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>210</v>
+        <v>510</v>
       </c>
       <c r="O7" t="n">
-        <v>2520</v>
+        <v>3450</v>
       </c>
       <c r="P7" t="n">
-        <v>3600</v>
+        <v>8880</v>
       </c>
       <c r="Q7" t="n">
-        <v>167.18</v>
+        <v>1915.65</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>720</v>
+        <v>1860</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18881,13 +18881,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>720</v>
+        <v>1410</v>
       </c>
       <c r="P8" t="n">
-        <v>1980</v>
+        <v>6450</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.95</v>
+        <v>171.27</v>
       </c>
     </row>
     <row r="9">
@@ -18925,7 +18925,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -18937,10 +18937,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -18978,7 +18978,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1144.8</v>
+        <v>2084.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>5.63</v>
       </c>
       <c r="L5" t="n">
-        <v>26478.9</v>
+        <v>32930.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>258.3</v>
+        <v>292.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1837.5</v>
+        <v>2520</v>
       </c>
       <c r="P5" t="n">
-        <v>130.2</v>
+        <v>166.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>654.26</v>
+        <v>7496.68</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>249</v>
       </c>
       <c r="H6" t="n">
-        <v>222.3</v>
+        <v>307.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7903.2</v>
+        <v>12165.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>366</v>
+        <v>622.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1905</v>
+        <v>2595</v>
       </c>
       <c r="P6" t="n">
-        <v>621</v>
+        <v>1197</v>
       </c>
       <c r="Q6" t="n">
-        <v>974.66</v>
+        <v>11167.94</v>
       </c>
     </row>
     <row r="7">
@@ -20111,22 +20111,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>2232</v>
+        <v>5418</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>14.7</v>
+        <v>35.7</v>
       </c>
       <c r="O7" t="n">
-        <v>882</v>
+        <v>1207.5</v>
       </c>
       <c r="P7" t="n">
-        <v>900</v>
+        <v>2220</v>
       </c>
       <c r="Q7" t="n">
-        <v>133.75</v>
+        <v>1532.52</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>511.2</v>
+        <v>1320.6</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20173,13 +20173,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>324</v>
+        <v>634.5</v>
       </c>
       <c r="P8" t="n">
-        <v>752.4</v>
+        <v>2451</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.2</v>
+        <v>162.71</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>48.6</v>
+        <v>121.5</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20270,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>160.2</v>
+        <v>133.5</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6525360</v>
+        <v>11881080</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>273224.61</v>
       </c>
       <c r="L5" t="n">
-        <v>4766202</v>
+        <v>5927418</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>43911</v>
+        <v>49725</v>
       </c>
       <c r="O5" t="n">
-        <v>312375</v>
+        <v>428400</v>
       </c>
       <c r="P5" t="n">
-        <v>8463</v>
+        <v>10803</v>
       </c>
       <c r="Q5" t="n">
-        <v>392553.22</v>
+        <v>4498005.6</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>13446</v>
       </c>
       <c r="H6" t="n">
-        <v>1267110</v>
+        <v>1754460</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1422576</v>
+        <v>2189808</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>62220</v>
+        <v>105825</v>
       </c>
       <c r="O6" t="n">
-        <v>323850</v>
+        <v>441150</v>
       </c>
       <c r="P6" t="n">
-        <v>40365</v>
+        <v>77805</v>
       </c>
       <c r="Q6" t="n">
-        <v>584794.08</v>
+        <v>6700765.5</v>
       </c>
     </row>
     <row r="7">
@@ -21403,22 +21403,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>401760</v>
+        <v>975240</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2499</v>
+        <v>6069</v>
       </c>
       <c r="O7" t="n">
-        <v>149940</v>
+        <v>205275</v>
       </c>
       <c r="P7" t="n">
-        <v>58500</v>
+        <v>144300</v>
       </c>
       <c r="Q7" t="n">
-        <v>80248.32000000001</v>
+        <v>919512</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>92016</v>
+        <v>237708</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21465,13 +21465,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>55080</v>
+        <v>107865</v>
       </c>
       <c r="P8" t="n">
-        <v>48906</v>
+        <v>159315</v>
       </c>
       <c r="Q8" t="n">
-        <v>8519.9</v>
+        <v>97623.89999999999</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8748</v>
+        <v>21870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21562,7 +21562,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>28836</v>
+        <v>24030</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>16200</v>
+        <v>32400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>109453680</v>
+        <v>118441440</v>
       </c>
       <c r="I5" t="n">
         <v>450017.01</v>
@@ -22589,22 +22589,22 @@
         <v>4275161.58</v>
       </c>
       <c r="L5" t="n">
-        <v>34708338</v>
+        <v>37231488</v>
       </c>
       <c r="M5" t="n">
-        <v>366870</v>
+        <v>296100</v>
       </c>
       <c r="N5" t="n">
-        <v>135864</v>
+        <v>152541</v>
       </c>
       <c r="O5" t="n">
-        <v>1588140</v>
+        <v>1815855</v>
       </c>
       <c r="P5" t="n">
-        <v>64857</v>
+        <v>44499</v>
       </c>
       <c r="Q5" t="n">
-        <v>4335720.26</v>
+        <v>44930649.51</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>637794</v>
       </c>
       <c r="H6" t="n">
-        <v>142501140</v>
+        <v>150688620</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -22642,22 +22642,22 @@
         <v>3668065.91</v>
       </c>
       <c r="L6" t="n">
-        <v>38215746</v>
+        <v>38073888</v>
       </c>
       <c r="M6" t="n">
-        <v>992880</v>
+        <v>666120</v>
       </c>
       <c r="N6" t="n">
-        <v>284835</v>
+        <v>387345</v>
       </c>
       <c r="O6" t="n">
-        <v>4986525</v>
+        <v>5333325</v>
       </c>
       <c r="P6" t="n">
-        <v>480870</v>
+        <v>358020</v>
       </c>
       <c r="Q6" t="n">
-        <v>43105684.14</v>
+        <v>446700033.22</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1668924</v>
       </c>
       <c r="H7" t="n">
-        <v>198979020</v>
+        <v>208715760</v>
       </c>
       <c r="I7" t="n">
         <v>247829.82</v>
@@ -22695,22 +22695,22 @@
         <v>5607149.77</v>
       </c>
       <c r="L7" t="n">
-        <v>57603960</v>
+        <v>57254040</v>
       </c>
       <c r="M7" t="n">
-        <v>3061275</v>
+        <v>3020850</v>
       </c>
       <c r="N7" t="n">
-        <v>147084</v>
+        <v>205275</v>
       </c>
       <c r="O7" t="n">
-        <v>5071185</v>
+        <v>5435325</v>
       </c>
       <c r="P7" t="n">
-        <v>978412.5</v>
+        <v>714675</v>
       </c>
       <c r="Q7" t="n">
-        <v>43274426.69</v>
+        <v>448448695.92</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>6568614</v>
       </c>
       <c r="H8" t="n">
-        <v>145495350</v>
+        <v>141570900</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -22748,22 +22748,22 @@
         <v>3788144.9</v>
       </c>
       <c r="L8" t="n">
-        <v>59476842</v>
+        <v>58334310</v>
       </c>
       <c r="M8" t="n">
-        <v>3978975</v>
+        <v>5024250</v>
       </c>
       <c r="N8" t="n">
-        <v>106080</v>
+        <v>197880</v>
       </c>
       <c r="O8" t="n">
-        <v>4617540</v>
+        <v>5267025</v>
       </c>
       <c r="P8" t="n">
-        <v>1633164</v>
+        <v>1237470</v>
       </c>
       <c r="Q8" t="n">
-        <v>47684700.22</v>
+        <v>494151933.69</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>7011684</v>
       </c>
       <c r="H9" t="n">
-        <v>76950000</v>
+        <v>94734000</v>
       </c>
       <c r="I9" t="n">
         <v>311923.74</v>
@@ -22801,22 +22801,22 @@
         <v>4132989.61</v>
       </c>
       <c r="L9" t="n">
-        <v>57903012</v>
+        <v>60129378</v>
       </c>
       <c r="M9" t="n">
-        <v>3028200</v>
+        <v>8217300</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>6120</v>
       </c>
       <c r="O9" t="n">
-        <v>5323890</v>
+        <v>5781105</v>
       </c>
       <c r="P9" t="n">
-        <v>2184000</v>
+        <v>1884675</v>
       </c>
       <c r="Q9" t="n">
-        <v>43476384.74</v>
+        <v>450541567.71</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>8858160</v>
       </c>
       <c r="H10" t="n">
-        <v>22572000</v>
+        <v>25821000</v>
       </c>
       <c r="I10" t="n">
         <v>168974.88</v>
@@ -22854,22 +22854,22 @@
         <v>3421741.32</v>
       </c>
       <c r="L10" t="n">
-        <v>52904448</v>
+        <v>56725218</v>
       </c>
       <c r="M10" t="n">
-        <v>2998800</v>
+        <v>7238175</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>5133660</v>
+        <v>6543810</v>
       </c>
       <c r="P10" t="n">
-        <v>4120545</v>
+        <v>4024410</v>
       </c>
       <c r="Q10" t="n">
-        <v>41378467.68</v>
+        <v>428801056.2</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>4770900</v>
       </c>
       <c r="H11" t="n">
-        <v>23598000</v>
+        <v>24795000</v>
       </c>
       <c r="I11" t="n">
         <v>349020.53</v>
@@ -22907,22 +22907,22 @@
         <v>1875985.34</v>
       </c>
       <c r="L11" t="n">
-        <v>37794600</v>
+        <v>44614800</v>
       </c>
       <c r="M11" t="n">
-        <v>2126250</v>
+        <v>7852950</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2323560</v>
+        <v>4122585</v>
       </c>
       <c r="P11" t="n">
-        <v>4322565</v>
+        <v>5043870</v>
       </c>
       <c r="Q11" t="n">
-        <v>27191116.8</v>
+        <v>281778912</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>3518640</v>
       </c>
       <c r="H12" t="n">
-        <v>33003000</v>
+        <v>33516000</v>
       </c>
       <c r="I12" t="n">
         <v>180045.65</v>
@@ -22960,22 +22960,22 @@
         <v>810205.42</v>
       </c>
       <c r="L12" t="n">
-        <v>28274400</v>
+        <v>36223200</v>
       </c>
       <c r="M12" t="n">
-        <v>1546125</v>
+        <v>7600950</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1111800</v>
+        <v>2830500</v>
       </c>
       <c r="P12" t="n">
-        <v>4251000</v>
+        <v>6598800</v>
       </c>
       <c r="Q12" t="n">
-        <v>18176894.64</v>
+        <v>188365400.1</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>2875500</v>
       </c>
       <c r="H13" t="n">
-        <v>12825000</v>
+        <v>17442000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,22 +23013,22 @@
         <v>414935.3</v>
       </c>
       <c r="L13" t="n">
-        <v>22334400</v>
+        <v>29511000</v>
       </c>
       <c r="M13" t="n">
-        <v>1134000</v>
+        <v>5743500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>443700</v>
+        <v>668100</v>
       </c>
       <c r="P13" t="n">
-        <v>2954250</v>
+        <v>4886700</v>
       </c>
       <c r="Q13" t="n">
-        <v>13055726.88</v>
+        <v>135295234.2</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>1637820</v>
       </c>
       <c r="H14" t="n">
-        <v>4446000</v>
+        <v>4788000</v>
       </c>
       <c r="I14" t="n">
         <v>188785.73</v>
@@ -23066,22 +23066,22 @@
         <v>47196.43</v>
       </c>
       <c r="L14" t="n">
-        <v>9163800</v>
+        <v>13354200</v>
       </c>
       <c r="M14" t="n">
-        <v>735000</v>
+        <v>6940500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>285600</v>
+        <v>397800</v>
       </c>
       <c r="P14" t="n">
-        <v>2059200</v>
+        <v>3133650</v>
       </c>
       <c r="Q14" t="n">
-        <v>7101777.6</v>
+        <v>73595034</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>529740</v>
       </c>
       <c r="H15" t="n">
-        <v>2907000</v>
+        <v>4446000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,22 +23119,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>4530600</v>
+        <v>6922800</v>
       </c>
       <c r="M15" t="n">
-        <v>367500</v>
+        <v>2457000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>489600</v>
+        <v>525300</v>
       </c>
       <c r="P15" t="n">
-        <v>1721850</v>
+        <v>1725750</v>
       </c>
       <c r="Q15" t="n">
-        <v>2535641.28</v>
+        <v>26276605.2</v>
       </c>
     </row>
     <row r="16">
@@ -23160,7 +23160,7 @@
         <v>238140</v>
       </c>
       <c r="H16" t="n">
-        <v>1026000</v>
+        <v>1197000</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -23172,22 +23172,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1819800</v>
+        <v>4692600</v>
       </c>
       <c r="M16" t="n">
-        <v>126000</v>
+        <v>1228500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>20400</v>
+        <v>86700</v>
       </c>
       <c r="P16" t="n">
-        <v>2394600</v>
+        <v>2977650</v>
       </c>
       <c r="Q16" t="n">
-        <v>1589764.32</v>
+        <v>16474573.8</v>
       </c>
     </row>
     <row r="17">
@@ -23213,7 +23213,7 @@
         <v>100440</v>
       </c>
       <c r="H17" t="n">
-        <v>171000</v>
+        <v>684000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23225,22 +23225,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>685800</v>
+        <v>2332800</v>
       </c>
       <c r="M17" t="n">
-        <v>273000</v>
+        <v>997500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P17" t="n">
-        <v>1760850</v>
+        <v>2864550</v>
       </c>
       <c r="Q17" t="n">
-        <v>842825.52</v>
+        <v>8734119.300000001</v>
       </c>
     </row>
     <row r="18">
@@ -23278,10 +23278,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>334800</v>
+        <v>1404000</v>
       </c>
       <c r="M18" t="n">
-        <v>388500</v>
+        <v>661500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -23290,10 +23290,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1331850</v>
+        <v>1950000</v>
       </c>
       <c r="Q18" t="n">
-        <v>401893.92</v>
+        <v>4164787.8</v>
       </c>
     </row>
     <row r="19">
@@ -23319,7 +23319,7 @@
         <v>17820</v>
       </c>
       <c r="H19" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -23331,22 +23331,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>723600</v>
+        <v>1296000</v>
       </c>
       <c r="M19" t="n">
-        <v>871500</v>
+        <v>1197000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P19" t="n">
-        <v>1296750</v>
+        <v>1932450</v>
       </c>
       <c r="Q19" t="n">
-        <v>180591.12</v>
+        <v>1871448.3</v>
       </c>
     </row>
     <row r="20">
@@ -23384,10 +23384,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>199800</v>
+        <v>610200</v>
       </c>
       <c r="M20" t="n">
-        <v>21000</v>
+        <v>756000</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -23396,10 +23396,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>510900</v>
+        <v>1197300</v>
       </c>
       <c r="Q20" t="n">
-        <v>91534.32000000001</v>
+        <v>948561.3</v>
       </c>
     </row>
     <row r="21">
@@ -23425,7 +23425,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>342000</v>
+        <v>684000</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -23437,10 +23437,10 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>5400</v>
+        <v>216000</v>
       </c>
       <c r="M21" t="n">
-        <v>10500</v>
+        <v>168000</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -23449,10 +23449,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q21" t="n">
-        <v>13592.88</v>
+        <v>140861.7</v>
       </c>
     </row>
     <row r="22">
@@ -23490,10 +23490,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M22" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -23505,7 +23505,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3013.2</v>
+        <v>31225.5</v>
       </c>
     </row>
     <row r="23">
@@ -23543,10 +23543,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>5400</v>
       </c>
       <c r="M23" t="n">
-        <v>73500</v>
+        <v>115500</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -23558,7 +23558,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4888.08</v>
+        <v>50654.7</v>
       </c>
     </row>
     <row r="24">
@@ -23816,7 +23816,7 @@
         <v>44760</v>
       </c>
       <c r="H4" t="n">
-        <v>2640</v>
+        <v>2280</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -23828,22 +23828,22 @@
         <v>73</v>
       </c>
       <c r="L4" t="n">
-        <v>128790</v>
+        <v>107970</v>
       </c>
       <c r="M4" t="n">
-        <v>45210</v>
+        <v>40860</v>
       </c>
       <c r="N4" t="n">
-        <v>10320</v>
+        <v>8640</v>
       </c>
       <c r="O4" t="n">
-        <v>16080</v>
+        <v>19260</v>
       </c>
       <c r="P4" t="n">
-        <v>1920</v>
+        <v>390</v>
       </c>
       <c r="Q4" t="n">
-        <v>9089.85</v>
+        <v>89116.2</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>61260</v>
       </c>
       <c r="H5" t="n">
-        <v>5220</v>
+        <v>4470</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -23881,22 +23881,22 @@
         <v>67</v>
       </c>
       <c r="L5" t="n">
-        <v>159870</v>
+        <v>146130</v>
       </c>
       <c r="M5" t="n">
-        <v>21330</v>
+        <v>33120</v>
       </c>
       <c r="N5" t="n">
-        <v>19860</v>
+        <v>19020</v>
       </c>
       <c r="O5" t="n">
-        <v>19200</v>
+        <v>20160</v>
       </c>
       <c r="P5" t="n">
-        <v>2520</v>
+        <v>840</v>
       </c>
       <c r="Q5" t="n">
-        <v>17532.06</v>
+        <v>171882.9</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>63990</v>
       </c>
       <c r="H6" t="n">
-        <v>13710</v>
+        <v>13740</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>46</v>
       </c>
       <c r="L6" t="n">
-        <v>161130</v>
+        <v>150870</v>
       </c>
       <c r="M6" t="n">
-        <v>9180</v>
+        <v>14760</v>
       </c>
       <c r="N6" t="n">
-        <v>17070</v>
+        <v>19620</v>
       </c>
       <c r="O6" t="n">
-        <v>20430</v>
+        <v>22170</v>
       </c>
       <c r="P6" t="n">
-        <v>2970</v>
+        <v>990</v>
       </c>
       <c r="Q6" t="n">
-        <v>21017.52</v>
+        <v>206054.1</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>57750</v>
       </c>
       <c r="H7" t="n">
-        <v>13170</v>
+        <v>13530</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -23987,22 +23987,22 @@
         <v>65</v>
       </c>
       <c r="L7" t="n">
-        <v>176790</v>
+        <v>178830</v>
       </c>
       <c r="M7" t="n">
-        <v>4920</v>
+        <v>13050</v>
       </c>
       <c r="N7" t="n">
-        <v>8400</v>
+        <v>10740</v>
       </c>
       <c r="O7" t="n">
-        <v>19110</v>
+        <v>18930</v>
       </c>
       <c r="P7" t="n">
-        <v>4170</v>
+        <v>1680</v>
       </c>
       <c r="Q7" t="n">
-        <v>22473.19</v>
+        <v>220325.4</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>76800</v>
       </c>
       <c r="H8" t="n">
-        <v>19110</v>
+        <v>17640</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -24040,22 +24040,22 @@
         <v>47</v>
       </c>
       <c r="L8" t="n">
-        <v>210720</v>
+        <v>204060</v>
       </c>
       <c r="M8" t="n">
-        <v>4560</v>
+        <v>12900</v>
       </c>
       <c r="N8" t="n">
-        <v>2640</v>
+        <v>3570</v>
       </c>
       <c r="O8" t="n">
-        <v>22260</v>
+        <v>23670</v>
       </c>
       <c r="P8" t="n">
-        <v>5250</v>
+        <v>2910</v>
       </c>
       <c r="Q8" t="n">
-        <v>22758.69</v>
+        <v>223124.4</v>
       </c>
     </row>
     <row r="9">
@@ -24081,7 +24081,7 @@
         <v>91560</v>
       </c>
       <c r="H9" t="n">
-        <v>8280</v>
+        <v>10350</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -24093,22 +24093,22 @@
         <v>61</v>
       </c>
       <c r="L9" t="n">
-        <v>247590</v>
+        <v>253770</v>
       </c>
       <c r="M9" t="n">
-        <v>4140</v>
+        <v>11190</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>20760</v>
+        <v>22170</v>
       </c>
       <c r="P9" t="n">
-        <v>8340</v>
+        <v>6210</v>
       </c>
       <c r="Q9" t="n">
-        <v>26776.32</v>
+        <v>262512.9</v>
       </c>
     </row>
     <row r="10">
@@ -24134,7 +24134,7 @@
         <v>106260</v>
       </c>
       <c r="H10" t="n">
-        <v>990</v>
+        <v>1650</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -24146,22 +24146,22 @@
         <v>60</v>
       </c>
       <c r="L10" t="n">
-        <v>225900</v>
+        <v>238830</v>
       </c>
       <c r="M10" t="n">
-        <v>4740</v>
+        <v>8610</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>21300</v>
+        <v>23490</v>
       </c>
       <c r="P10" t="n">
-        <v>11430</v>
+        <v>6540</v>
       </c>
       <c r="Q10" t="n">
-        <v>30362.57</v>
+        <v>297672.3</v>
       </c>
     </row>
     <row r="11">
@@ -24187,7 +24187,7 @@
         <v>65640</v>
       </c>
       <c r="H11" t="n">
-        <v>510</v>
+        <v>600</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -24199,22 +24199,22 @@
         <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>143970</v>
+        <v>165360</v>
       </c>
       <c r="M11" t="n">
-        <v>3720</v>
+        <v>7650</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>13230</v>
+        <v>21000</v>
       </c>
       <c r="P11" t="n">
-        <v>14730</v>
+        <v>6810</v>
       </c>
       <c r="Q11" t="n">
-        <v>27293.98</v>
+        <v>267588</v>
       </c>
     </row>
     <row r="12">
@@ -24240,7 +24240,7 @@
         <v>35700</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -24252,22 +24252,22 @@
         <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>67440</v>
+        <v>83760</v>
       </c>
       <c r="M12" t="n">
-        <v>2700</v>
+        <v>4740</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6420</v>
+        <v>16290</v>
       </c>
       <c r="P12" t="n">
-        <v>15360</v>
+        <v>15030</v>
       </c>
       <c r="Q12" t="n">
-        <v>17721.53</v>
+        <v>173740.5</v>
       </c>
     </row>
     <row r="13">
@@ -24305,22 +24305,22 @@
         <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>33900</v>
+        <v>42990</v>
       </c>
       <c r="M13" t="n">
-        <v>2370</v>
+        <v>4740</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2610</v>
+        <v>3930</v>
       </c>
       <c r="P13" t="n">
-        <v>12630</v>
+        <v>13710</v>
       </c>
       <c r="Q13" t="n">
-        <v>10008.86</v>
+        <v>98126.10000000001</v>
       </c>
     </row>
     <row r="14">
@@ -24358,22 +24358,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>9480</v>
+        <v>16320</v>
       </c>
       <c r="M14" t="n">
-        <v>1320</v>
+        <v>5400</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1680</v>
+        <v>2340</v>
       </c>
       <c r="P14" t="n">
-        <v>13140</v>
+        <v>12330</v>
       </c>
       <c r="Q14" t="n">
-        <v>4569.62</v>
+        <v>44800.2</v>
       </c>
     </row>
     <row r="15">
@@ -24411,22 +24411,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>5280</v>
+        <v>9840</v>
       </c>
       <c r="M15" t="n">
-        <v>570</v>
+        <v>2280</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2880</v>
+        <v>3090</v>
       </c>
       <c r="P15" t="n">
-        <v>14790</v>
+        <v>15270</v>
       </c>
       <c r="Q15" t="n">
-        <v>1396.74</v>
+        <v>13693.5</v>
       </c>
     </row>
     <row r="16">
@@ -24464,22 +24464,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1050</v>
+        <v>7380</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>810</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="P16" t="n">
-        <v>25200</v>
+        <v>28680</v>
       </c>
       <c r="Q16" t="n">
-        <v>583.11</v>
+        <v>5716.8</v>
       </c>
     </row>
     <row r="17">
@@ -24517,22 +24517,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>2700</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>780</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P17" t="n">
-        <v>14820</v>
+        <v>19170</v>
       </c>
       <c r="Q17" t="n">
-        <v>242.08</v>
+        <v>2373.3</v>
       </c>
     </row>
     <row r="18">
@@ -24570,10 +24570,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>120</v>
+        <v>1620</v>
       </c>
       <c r="M18" t="n">
-        <v>570</v>
+        <v>900</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -24582,10 +24582,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>15870</v>
+        <v>16680</v>
       </c>
       <c r="Q18" t="n">
-        <v>139.08</v>
+        <v>1363.5</v>
       </c>
     </row>
     <row r="19">
@@ -24623,22 +24623,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>240</v>
+        <v>1710</v>
       </c>
       <c r="M19" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P19" t="n">
-        <v>18120</v>
+        <v>26130</v>
       </c>
       <c r="Q19" t="n">
-        <v>102.54</v>
+        <v>1005.3</v>
       </c>
     </row>
     <row r="20">
@@ -24676,10 +24676,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -24688,10 +24688,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>7800</v>
+        <v>18300</v>
       </c>
       <c r="Q20" t="n">
-        <v>52.14</v>
+        <v>511.2</v>
       </c>
     </row>
     <row r="21">
@@ -24732,7 +24732,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -24741,10 +24741,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.27</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -24785,7 +24785,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -24797,7 +24797,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.29</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="23">
@@ -24838,7 +24838,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -24850,7 +24850,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="24">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1879.2</v>
+        <v>1609.2</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -25173,22 +25173,22 @@
         <v>22.18</v>
       </c>
       <c r="L5" t="n">
-        <v>33572.7</v>
+        <v>30687.3</v>
       </c>
       <c r="M5" t="n">
-        <v>426.6</v>
+        <v>662.4</v>
       </c>
       <c r="N5" t="n">
-        <v>198.6</v>
+        <v>190.2</v>
       </c>
       <c r="O5" t="n">
-        <v>960</v>
+        <v>1008</v>
       </c>
       <c r="P5" t="n">
-        <v>50.4</v>
+        <v>16.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>876.6</v>
+        <v>8594.15</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>3199.5</v>
       </c>
       <c r="H6" t="n">
-        <v>7814.7</v>
+        <v>7831.8</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>23.32</v>
       </c>
       <c r="L6" t="n">
-        <v>59618.1</v>
+        <v>55821.9</v>
       </c>
       <c r="M6" t="n">
-        <v>734.4</v>
+        <v>1180.8</v>
       </c>
       <c r="N6" t="n">
-        <v>853.5</v>
+        <v>981</v>
       </c>
       <c r="O6" t="n">
-        <v>5107.5</v>
+        <v>5542.5</v>
       </c>
       <c r="P6" t="n">
-        <v>445.5</v>
+        <v>148.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>15763.14</v>
+        <v>154540.58</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>8662.5</v>
       </c>
       <c r="H7" t="n">
-        <v>9614.1</v>
+        <v>9876.9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -25279,22 +25279,22 @@
         <v>41.47</v>
       </c>
       <c r="L7" t="n">
-        <v>106074</v>
+        <v>107298</v>
       </c>
       <c r="M7" t="n">
-        <v>1722</v>
+        <v>4567.5</v>
       </c>
       <c r="N7" t="n">
-        <v>588</v>
+        <v>751.8</v>
       </c>
       <c r="O7" t="n">
-        <v>6688.5</v>
+        <v>6625.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1042.5</v>
+        <v>420</v>
       </c>
       <c r="Q7" t="n">
-        <v>17978.55</v>
+        <v>176260.32</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>49920</v>
       </c>
       <c r="H8" t="n">
-        <v>16243.5</v>
+        <v>14994</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -25332,22 +25332,22 @@
         <v>34.59</v>
       </c>
       <c r="L8" t="n">
-        <v>149611.2</v>
+        <v>144882.6</v>
       </c>
       <c r="M8" t="n">
-        <v>2508</v>
+        <v>7095</v>
       </c>
       <c r="N8" t="n">
-        <v>528</v>
+        <v>714</v>
       </c>
       <c r="O8" t="n">
-        <v>10017</v>
+        <v>10651.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1995</v>
+        <v>1105.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>21620.75</v>
+        <v>211968.18</v>
       </c>
     </row>
     <row r="9">
@@ -25373,7 +25373,7 @@
         <v>77826</v>
       </c>
       <c r="H9" t="n">
-        <v>8280</v>
+        <v>10350</v>
       </c>
       <c r="I9" t="n">
         <v>0.8</v>
@@ -25385,22 +25385,22 @@
         <v>48.98</v>
       </c>
       <c r="L9" t="n">
-        <v>200547.9</v>
+        <v>205553.7</v>
       </c>
       <c r="M9" t="n">
-        <v>2898</v>
+        <v>7833</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>11418</v>
+        <v>12193.5</v>
       </c>
       <c r="P9" t="n">
-        <v>4170</v>
+        <v>3105</v>
       </c>
       <c r="Q9" t="n">
-        <v>25973.03</v>
+        <v>254637.51</v>
       </c>
     </row>
     <row r="10">
@@ -25426,7 +25426,7 @@
         <v>106260</v>
       </c>
       <c r="H10" t="n">
-        <v>990</v>
+        <v>1650</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -25438,22 +25438,22 @@
         <v>52.2</v>
       </c>
       <c r="L10" t="n">
-        <v>201051</v>
+        <v>212558.7</v>
       </c>
       <c r="M10" t="n">
-        <v>4029</v>
+        <v>7318.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>14910</v>
+        <v>16443</v>
       </c>
       <c r="P10" t="n">
-        <v>9715.5</v>
+        <v>5559</v>
       </c>
       <c r="Q10" t="n">
-        <v>30362.57</v>
+        <v>297672.3</v>
       </c>
     </row>
     <row r="11">
@@ -25479,7 +25479,7 @@
         <v>65640</v>
       </c>
       <c r="H11" t="n">
-        <v>510</v>
+        <v>600</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -25491,22 +25491,22 @@
         <v>34.14</v>
       </c>
       <c r="L11" t="n">
-        <v>143970</v>
+        <v>165360</v>
       </c>
       <c r="M11" t="n">
-        <v>3348</v>
+        <v>6885</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>11245.5</v>
+        <v>17850</v>
       </c>
       <c r="P11" t="n">
-        <v>13257</v>
+        <v>6129</v>
       </c>
       <c r="Q11" t="n">
-        <v>27293.98</v>
+        <v>267588</v>
       </c>
     </row>
     <row r="12">
@@ -25532,7 +25532,7 @@
         <v>35700</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -25544,22 +25544,22 @@
         <v>9.27</v>
       </c>
       <c r="L12" t="n">
-        <v>67440</v>
+        <v>83760</v>
       </c>
       <c r="M12" t="n">
-        <v>2565</v>
+        <v>4503</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>6420</v>
+        <v>16290</v>
       </c>
       <c r="P12" t="n">
-        <v>15360</v>
+        <v>15030</v>
       </c>
       <c r="Q12" t="n">
-        <v>17721.53</v>
+        <v>173740.5</v>
       </c>
     </row>
     <row r="13">
@@ -25597,22 +25597,22 @@
         <v>1.9</v>
       </c>
       <c r="L13" t="n">
-        <v>33900</v>
+        <v>42990</v>
       </c>
       <c r="M13" t="n">
-        <v>2370</v>
+        <v>4740</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2610</v>
+        <v>3930</v>
       </c>
       <c r="P13" t="n">
-        <v>12630</v>
+        <v>13710</v>
       </c>
       <c r="Q13" t="n">
-        <v>10008.86</v>
+        <v>98126.10000000001</v>
       </c>
     </row>
     <row r="14">
@@ -25650,22 +25650,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>9480</v>
+        <v>16320</v>
       </c>
       <c r="M14" t="n">
-        <v>1320</v>
+        <v>5400</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1680</v>
+        <v>2340</v>
       </c>
       <c r="P14" t="n">
-        <v>13140</v>
+        <v>12330</v>
       </c>
       <c r="Q14" t="n">
-        <v>4569.62</v>
+        <v>44800.2</v>
       </c>
     </row>
     <row r="15">
@@ -25703,22 +25703,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>5280</v>
+        <v>9840</v>
       </c>
       <c r="M15" t="n">
-        <v>570</v>
+        <v>2280</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2880</v>
+        <v>3090</v>
       </c>
       <c r="P15" t="n">
-        <v>14790</v>
+        <v>15270</v>
       </c>
       <c r="Q15" t="n">
-        <v>1396.74</v>
+        <v>13693.5</v>
       </c>
     </row>
     <row r="16">
@@ -25756,22 +25756,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1050</v>
+        <v>7380</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>810</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>120</v>
+        <v>510</v>
       </c>
       <c r="P16" t="n">
-        <v>25200</v>
+        <v>28680</v>
       </c>
       <c r="Q16" t="n">
-        <v>583.11</v>
+        <v>5716.8</v>
       </c>
     </row>
     <row r="17">
@@ -25809,22 +25809,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>390</v>
+        <v>2700</v>
       </c>
       <c r="M17" t="n">
-        <v>60</v>
+        <v>780</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="P17" t="n">
-        <v>14820</v>
+        <v>19170</v>
       </c>
       <c r="Q17" t="n">
-        <v>242.08</v>
+        <v>2373.3</v>
       </c>
     </row>
     <row r="18">
@@ -25862,10 +25862,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>120</v>
+        <v>1620</v>
       </c>
       <c r="M18" t="n">
-        <v>570</v>
+        <v>900</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -25874,10 +25874,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>15870</v>
+        <v>16680</v>
       </c>
       <c r="Q18" t="n">
-        <v>139.08</v>
+        <v>1363.5</v>
       </c>
     </row>
     <row r="19">
@@ -25915,22 +25915,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>240</v>
+        <v>1710</v>
       </c>
       <c r="M19" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="P19" t="n">
-        <v>18120</v>
+        <v>26130</v>
       </c>
       <c r="Q19" t="n">
-        <v>102.54</v>
+        <v>1005.3</v>
       </c>
     </row>
     <row r="20">
@@ -25968,10 +25968,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M20" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -25980,10 +25980,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>7800</v>
+        <v>18300</v>
       </c>
       <c r="Q20" t="n">
-        <v>52.14</v>
+        <v>511.2</v>
       </c>
     </row>
     <row r="21">
@@ -26024,7 +26024,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -26033,10 +26033,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.27</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -26077,7 +26077,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -26089,7 +26089,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.29</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="23">
@@ -26130,7 +26130,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>210</v>
+        <v>330</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -26142,7 +26142,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.7</v>
+        <v>65.7</v>
       </c>
     </row>
     <row r="24">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>10711440</v>
+        <v>9172440</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -26465,22 +26465,22 @@
         <v>1076826.41</v>
       </c>
       <c r="L5" t="n">
-        <v>6043086</v>
+        <v>5523714</v>
       </c>
       <c r="M5" t="n">
-        <v>149310</v>
+        <v>231840</v>
       </c>
       <c r="N5" t="n">
-        <v>33762</v>
+        <v>32334</v>
       </c>
       <c r="O5" t="n">
-        <v>163200</v>
+        <v>171360</v>
       </c>
       <c r="P5" t="n">
-        <v>3276</v>
+        <v>1092</v>
       </c>
       <c r="Q5" t="n">
-        <v>525961.67</v>
+        <v>5156487</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>172773</v>
       </c>
       <c r="H6" t="n">
-        <v>44543790</v>
+        <v>44641260</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>1132423.03</v>
       </c>
       <c r="L6" t="n">
-        <v>10731258</v>
+        <v>10047942</v>
       </c>
       <c r="M6" t="n">
-        <v>257040</v>
+        <v>413280</v>
       </c>
       <c r="N6" t="n">
-        <v>145095</v>
+        <v>166770</v>
       </c>
       <c r="O6" t="n">
-        <v>868275</v>
+        <v>942225</v>
       </c>
       <c r="P6" t="n">
-        <v>28957.5</v>
+        <v>9652.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>9457883.189999999</v>
+        <v>92724345</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>467775</v>
       </c>
       <c r="H7" t="n">
-        <v>54800370</v>
+        <v>56298330</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -26571,22 +26571,22 @@
         <v>2013617.32</v>
       </c>
       <c r="L7" t="n">
-        <v>19093320</v>
+        <v>19313640</v>
       </c>
       <c r="M7" t="n">
-        <v>602700</v>
+        <v>1598625</v>
       </c>
       <c r="N7" t="n">
-        <v>99960</v>
+        <v>127806</v>
       </c>
       <c r="O7" t="n">
-        <v>1137045</v>
+        <v>1126335</v>
       </c>
       <c r="P7" t="n">
-        <v>67762.5</v>
+        <v>27300</v>
       </c>
       <c r="Q7" t="n">
-        <v>10787131.58</v>
+        <v>105756192</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>2695680</v>
       </c>
       <c r="H8" t="n">
-        <v>92587950</v>
+        <v>85465800</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -26624,22 +26624,22 @@
         <v>1679649.15</v>
       </c>
       <c r="L8" t="n">
-        <v>26930016</v>
+        <v>26078868</v>
       </c>
       <c r="M8" t="n">
-        <v>877800</v>
+        <v>2483250</v>
       </c>
       <c r="N8" t="n">
-        <v>89760</v>
+        <v>121380</v>
       </c>
       <c r="O8" t="n">
-        <v>1702890</v>
+        <v>1810755</v>
       </c>
       <c r="P8" t="n">
-        <v>129675</v>
+        <v>71877</v>
       </c>
       <c r="Q8" t="n">
-        <v>12972452.62</v>
+        <v>127180908</v>
       </c>
     </row>
     <row r="9">
@@ -26665,7 +26665,7 @@
         <v>4202604</v>
       </c>
       <c r="H9" t="n">
-        <v>47196000</v>
+        <v>58995000</v>
       </c>
       <c r="I9" t="n">
         <v>155961.87</v>
@@ -26677,22 +26677,22 @@
         <v>2378418.55</v>
       </c>
       <c r="L9" t="n">
-        <v>36098622</v>
+        <v>36999666</v>
       </c>
       <c r="M9" t="n">
-        <v>1014300</v>
+        <v>2741550</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1941060</v>
+        <v>2072895</v>
       </c>
       <c r="P9" t="n">
-        <v>271050</v>
+        <v>201825</v>
       </c>
       <c r="Q9" t="n">
-        <v>15583815.8</v>
+        <v>152782507.8</v>
       </c>
     </row>
     <row r="10">
@@ -26718,7 +26718,7 @@
         <v>5738040</v>
       </c>
       <c r="H10" t="n">
-        <v>5643000</v>
+        <v>9405000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -26730,22 +26730,22 @@
         <v>2534623.2</v>
       </c>
       <c r="L10" t="n">
-        <v>36189180</v>
+        <v>38260566</v>
       </c>
       <c r="M10" t="n">
-        <v>1410150</v>
+        <v>2561475</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2534700</v>
+        <v>2795310</v>
       </c>
       <c r="P10" t="n">
-        <v>631507.5</v>
+        <v>361335</v>
       </c>
       <c r="Q10" t="n">
-        <v>18217544.76</v>
+        <v>178603380</v>
       </c>
     </row>
     <row r="11">
@@ -26771,7 +26771,7 @@
         <v>3544560</v>
       </c>
       <c r="H11" t="n">
-        <v>2907000</v>
+        <v>3420000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -26783,22 +26783,22 @@
         <v>1657847.51</v>
       </c>
       <c r="L11" t="n">
-        <v>25914600</v>
+        <v>29764800</v>
       </c>
       <c r="M11" t="n">
-        <v>1171800</v>
+        <v>2409750</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1911735</v>
+        <v>3034500</v>
       </c>
       <c r="P11" t="n">
-        <v>861705</v>
+        <v>398385</v>
       </c>
       <c r="Q11" t="n">
-        <v>16376385.6</v>
+        <v>160552800</v>
       </c>
     </row>
     <row r="12">
@@ -26824,7 +26824,7 @@
         <v>1927800</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -26836,22 +26836,22 @@
         <v>450114.12</v>
       </c>
       <c r="L12" t="n">
-        <v>12139200</v>
+        <v>15076800</v>
       </c>
       <c r="M12" t="n">
-        <v>897750</v>
+        <v>1576050</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1091400</v>
+        <v>2769300</v>
       </c>
       <c r="P12" t="n">
-        <v>998400</v>
+        <v>976950</v>
       </c>
       <c r="Q12" t="n">
-        <v>10632918.6</v>
+        <v>104244300</v>
       </c>
     </row>
     <row r="13">
@@ -26889,22 +26889,22 @@
         <v>92207.84</v>
       </c>
       <c r="L13" t="n">
-        <v>6102000</v>
+        <v>7738200</v>
       </c>
       <c r="M13" t="n">
-        <v>829500</v>
+        <v>1659000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>443700</v>
+        <v>668100</v>
       </c>
       <c r="P13" t="n">
-        <v>820950</v>
+        <v>891150</v>
       </c>
       <c r="Q13" t="n">
-        <v>6005317.32</v>
+        <v>58875660</v>
       </c>
     </row>
     <row r="14">
@@ -26942,22 +26942,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1706400</v>
+        <v>2937600</v>
       </c>
       <c r="M14" t="n">
-        <v>462000</v>
+        <v>1890000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>285600</v>
+        <v>397800</v>
       </c>
       <c r="P14" t="n">
-        <v>854100</v>
+        <v>801450</v>
       </c>
       <c r="Q14" t="n">
-        <v>2741772.24</v>
+        <v>26880120</v>
       </c>
     </row>
     <row r="15">
@@ -26995,22 +26995,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>950400</v>
+        <v>1771200</v>
       </c>
       <c r="M15" t="n">
-        <v>199500</v>
+        <v>798000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>489600</v>
+        <v>525300</v>
       </c>
       <c r="P15" t="n">
-        <v>961350</v>
+        <v>992550</v>
       </c>
       <c r="Q15" t="n">
-        <v>838042.2</v>
+        <v>8216100</v>
       </c>
     </row>
     <row r="16">
@@ -27048,22 +27048,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>189000</v>
+        <v>1328400</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>283500</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>20400</v>
+        <v>86700</v>
       </c>
       <c r="P16" t="n">
-        <v>1638000</v>
+        <v>1864200</v>
       </c>
       <c r="Q16" t="n">
-        <v>349868.16</v>
+        <v>3430080</v>
       </c>
     </row>
     <row r="17">
@@ -27101,22 +27101,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>70200</v>
+        <v>486000</v>
       </c>
       <c r="M17" t="n">
-        <v>21000</v>
+        <v>273000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>10200</v>
+        <v>20400</v>
       </c>
       <c r="P17" t="n">
-        <v>963300</v>
+        <v>1246050</v>
       </c>
       <c r="Q17" t="n">
-        <v>145245.96</v>
+        <v>1423980</v>
       </c>
     </row>
     <row r="18">
@@ -27154,10 +27154,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>21600</v>
+        <v>291600</v>
       </c>
       <c r="M18" t="n">
-        <v>199500</v>
+        <v>315000</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -27166,10 +27166,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1031550</v>
+        <v>1084200</v>
       </c>
       <c r="Q18" t="n">
-        <v>83446.2</v>
+        <v>818100</v>
       </c>
     </row>
     <row r="19">
@@ -27207,22 +27207,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>43200</v>
+        <v>307800</v>
       </c>
       <c r="M19" t="n">
-        <v>31500</v>
+        <v>21000</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>10200</v>
+        <v>25500</v>
       </c>
       <c r="P19" t="n">
-        <v>1177800</v>
+        <v>1698450</v>
       </c>
       <c r="Q19" t="n">
-        <v>61524.36</v>
+        <v>603180</v>
       </c>
     </row>
     <row r="20">
@@ -27260,10 +27260,10 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>21600</v>
       </c>
       <c r="M20" t="n">
-        <v>21000</v>
+        <v>10500</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -27272,10 +27272,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>507000</v>
+        <v>1189500</v>
       </c>
       <c r="Q20" t="n">
-        <v>31285.44</v>
+        <v>306720</v>
       </c>
     </row>
     <row r="21">
@@ -27316,7 +27316,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>10500</v>
+        <v>31500</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -27325,10 +27325,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q21" t="n">
-        <v>5563.08</v>
+        <v>54540</v>
       </c>
     </row>
     <row r="22">
@@ -27369,7 +27369,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>21000</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -27381,7 +27381,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>771.12</v>
+        <v>7560</v>
       </c>
     </row>
     <row r="23">
@@ -27422,7 +27422,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>73500</v>
+        <v>115500</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -27434,7 +27434,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>4020.84</v>
+        <v>39420</v>
       </c>
     </row>
     <row r="24">
@@ -27692,7 +27692,7 @@
         <v>129990</v>
       </c>
       <c r="H4" t="n">
-        <v>16170</v>
+        <v>17850</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -27704,7 +27704,7 @@
         <v>108</v>
       </c>
       <c r="L4" t="n">
-        <v>405660</v>
+        <v>424980</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>57030</v>
+        <v>54300</v>
       </c>
       <c r="P4" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>43423.05</v>
+        <v>604624.6800000001</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>118590</v>
       </c>
       <c r="H5" t="n">
-        <v>22860</v>
+        <v>23130</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -27757,7 +27757,7 @@
         <v>54</v>
       </c>
       <c r="L5" t="n">
-        <v>285360</v>
+        <v>309210</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>56610</v>
+        <v>58590</v>
       </c>
       <c r="P5" t="n">
-        <v>570</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>29899.9</v>
+        <v>416327.67</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>59070</v>
       </c>
       <c r="H6" t="n">
-        <v>15510</v>
+        <v>15000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>35</v>
       </c>
       <c r="L6" t="n">
-        <v>142620</v>
+        <v>148020</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>34260</v>
+        <v>34800</v>
       </c>
       <c r="P6" t="n">
-        <v>1530</v>
+        <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>16506.72</v>
+        <v>229840.38</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>39450</v>
       </c>
       <c r="H7" t="n">
-        <v>17640</v>
+        <v>18480</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>18</v>
       </c>
       <c r="L7" t="n">
-        <v>95130</v>
+        <v>99750</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>28830</v>
+        <v>31740</v>
       </c>
       <c r="P7" t="n">
-        <v>2280</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7321.66</v>
+        <v>101947.23</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>15690</v>
       </c>
       <c r="H8" t="n">
-        <v>2730</v>
+        <v>3120</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>37560</v>
+        <v>42510</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>11400</v>
+        <v>13410</v>
       </c>
       <c r="P8" t="n">
-        <v>3840</v>
+        <v>480</v>
       </c>
       <c r="Q8" t="n">
-        <v>3630.58</v>
+        <v>50552.37</v>
       </c>
     </row>
     <row r="9">
@@ -27957,7 +27957,7 @@
         <v>480</v>
       </c>
       <c r="H9" t="n">
-        <v>420</v>
+        <v>570</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>5850</v>
+        <v>7710</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5700</v>
+        <v>9720</v>
       </c>
       <c r="P9" t="n">
-        <v>4350</v>
+        <v>1290</v>
       </c>
       <c r="Q9" t="n">
-        <v>187.06</v>
+        <v>2604.69</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>150</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,7 +28022,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1050</v>
+        <v>1830</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -28031,13 +28031,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2070</v>
+        <v>7230</v>
       </c>
       <c r="P10" t="n">
-        <v>5520</v>
+        <v>4980</v>
       </c>
       <c r="Q10" t="n">
-        <v>32.99</v>
+        <v>459.36</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>390</v>
+        <v>2550</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28084,13 +28084,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>240</v>
+        <v>2610</v>
       </c>
       <c r="P11" t="n">
-        <v>5100</v>
+        <v>9030</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.5</v>
+        <v>215.82</v>
       </c>
     </row>
     <row r="12">
@@ -28116,7 +28116,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>1620</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28137,13 +28137,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P12" t="n">
-        <v>2520</v>
+        <v>6210</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="13">
@@ -28169,7 +28169,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,10 +28193,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1440</v>
+        <v>4950</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.28</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="14">
@@ -28234,7 +28234,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -28246,10 +28246,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>180</v>
+        <v>1020</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.14</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="15">
@@ -28287,7 +28287,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -28299,7 +28299,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8229.6</v>
+        <v>8326.799999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -29049,7 +29049,7 @@
         <v>17.87</v>
       </c>
       <c r="L5" t="n">
-        <v>59925.6</v>
+        <v>64934.1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2830.5</v>
+        <v>2929.5</v>
       </c>
       <c r="P5" t="n">
-        <v>11.4</v>
+        <v>0.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1494.99</v>
+        <v>20816.38</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>2953.5</v>
       </c>
       <c r="H6" t="n">
-        <v>8840.700000000001</v>
+        <v>8550</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>17.74</v>
       </c>
       <c r="L6" t="n">
-        <v>52769.4</v>
+        <v>54767.4</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8565</v>
+        <v>8700</v>
       </c>
       <c r="P6" t="n">
-        <v>229.5</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>12380.04</v>
+        <v>172380.28</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>5917.5</v>
       </c>
       <c r="H7" t="n">
-        <v>12877.2</v>
+        <v>13490.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>11.48</v>
       </c>
       <c r="L7" t="n">
-        <v>57078</v>
+        <v>59850</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>10090.5</v>
+        <v>11109</v>
       </c>
       <c r="P7" t="n">
-        <v>570</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>5857.33</v>
+        <v>81557.78</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>10198.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2320.5</v>
+        <v>2652</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0.74</v>
       </c>
       <c r="L8" t="n">
-        <v>26667.6</v>
+        <v>30182.1</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5130</v>
+        <v>6034.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1459.2</v>
+        <v>182.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>3449.05</v>
+        <v>48024.75</v>
       </c>
     </row>
     <row r="9">
@@ -29249,7 +29249,7 @@
         <v>408</v>
       </c>
       <c r="H9" t="n">
-        <v>420</v>
+        <v>570</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4738.5</v>
+        <v>6245.1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3135</v>
+        <v>5346</v>
       </c>
       <c r="P9" t="n">
-        <v>2175</v>
+        <v>645</v>
       </c>
       <c r="Q9" t="n">
-        <v>181.45</v>
+        <v>2526.55</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>150</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>934.5</v>
+        <v>1628.7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1449</v>
+        <v>5061</v>
       </c>
       <c r="P10" t="n">
-        <v>4692</v>
+        <v>4233</v>
       </c>
       <c r="Q10" t="n">
-        <v>32.99</v>
+        <v>459.36</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>390</v>
+        <v>2550</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29376,13 +29376,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>204</v>
+        <v>2218.5</v>
       </c>
       <c r="P11" t="n">
-        <v>4590</v>
+        <v>8127</v>
       </c>
       <c r="Q11" t="n">
-        <v>15.5</v>
+        <v>215.82</v>
       </c>
     </row>
     <row r="12">
@@ -29408,7 +29408,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>1620</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29429,13 +29429,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="P12" t="n">
-        <v>2520</v>
+        <v>6210</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.7</v>
+        <v>51.48</v>
       </c>
     </row>
     <row r="13">
@@ -29461,7 +29461,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,10 +29485,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1440</v>
+        <v>4950</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.28</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="14">
@@ -29526,7 +29526,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -29538,10 +29538,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>180</v>
+        <v>1020</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.14</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="15">
@@ -29579,7 +29579,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -29591,7 +29591,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>46908720</v>
+        <v>47462760</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -30341,7 +30341,7 @@
         <v>867889.9399999999</v>
       </c>
       <c r="L5" t="n">
-        <v>10786608</v>
+        <v>11688138</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>481185</v>
+        <v>498015</v>
       </c>
       <c r="P5" t="n">
-        <v>741</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>896996.89</v>
+        <v>12489830.1</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>159489</v>
       </c>
       <c r="H6" t="n">
-        <v>50391990</v>
+        <v>48735000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>861626.22</v>
       </c>
       <c r="L6" t="n">
-        <v>9498492</v>
+        <v>9858132</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1456050</v>
+        <v>1479000</v>
       </c>
       <c r="P6" t="n">
-        <v>14917.5</v>
+        <v>292.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>7428023.19</v>
+        <v>103428171</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>319545</v>
       </c>
       <c r="H7" t="n">
-        <v>73400040</v>
+        <v>76895280</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>557617.1</v>
       </c>
       <c r="L7" t="n">
-        <v>10274040</v>
+        <v>10773000</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1715385</v>
+        <v>1888530</v>
       </c>
       <c r="P7" t="n">
-        <v>37050</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3514399.06</v>
+        <v>48934670.4</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>550719</v>
       </c>
       <c r="H8" t="n">
-        <v>13226850</v>
+        <v>15116400</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>35737.22</v>
       </c>
       <c r="L8" t="n">
-        <v>4800168</v>
+        <v>5432778</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>872100</v>
+        <v>1025865</v>
       </c>
       <c r="P8" t="n">
-        <v>94848</v>
+        <v>11856</v>
       </c>
       <c r="Q8" t="n">
-        <v>2069430.2</v>
+        <v>28814850.9</v>
       </c>
     </row>
     <row r="9">
@@ -30541,7 +30541,7 @@
         <v>22032</v>
       </c>
       <c r="H9" t="n">
-        <v>2394000</v>
+        <v>3249000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>852930</v>
+        <v>1124118</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>532950</v>
+        <v>908820</v>
       </c>
       <c r="P9" t="n">
-        <v>141375</v>
+        <v>41925</v>
       </c>
       <c r="Q9" t="n">
-        <v>108871.31</v>
+        <v>1515929.58</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>8100</v>
       </c>
       <c r="H10" t="n">
-        <v>342000</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>168210</v>
+        <v>293166</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>246330</v>
+        <v>860370</v>
       </c>
       <c r="P10" t="n">
-        <v>304980</v>
+        <v>275145</v>
       </c>
       <c r="Q10" t="n">
-        <v>19794.24</v>
+        <v>275616</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>855000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>70200</v>
+        <v>459000</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30668,13 +30668,13 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>34680</v>
+        <v>377145</v>
       </c>
       <c r="P11" t="n">
-        <v>298350</v>
+        <v>528255</v>
       </c>
       <c r="Q11" t="n">
-        <v>9299.879999999999</v>
+        <v>129492</v>
       </c>
     </row>
     <row r="12">
@@ -30700,7 +30700,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>171000</v>
+        <v>1710000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16200</v>
+        <v>291600</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30721,13 +30721,13 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>10200</v>
       </c>
       <c r="P12" t="n">
-        <v>163800</v>
+        <v>403650</v>
       </c>
       <c r="Q12" t="n">
-        <v>2218.32</v>
+        <v>30888</v>
       </c>
     </row>
     <row r="13">
@@ -30753,7 +30753,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>342000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>183600</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,10 +30777,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>93600</v>
+        <v>321750</v>
       </c>
       <c r="Q13" t="n">
-        <v>170.64</v>
+        <v>2376</v>
       </c>
     </row>
     <row r="14">
@@ -30818,7 +30818,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>48600</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -30830,10 +30830,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>11700</v>
+        <v>66300</v>
       </c>
       <c r="Q14" t="n">
-        <v>85.31999999999999</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="15">
@@ -30871,7 +30871,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>10800</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -30883,7 +30883,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1950</v>
+        <v>9750</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
